--- a/output/2024-07-10.xlsx
+++ b/output/2024-07-10.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.53</v>
+        <v>2.88</v>
       </c>
       <c r="F14" t="n">
-        <v>8.23</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>15.2</v>
+        <v>17.6</v>
       </c>
       <c r="H14" t="n">
-        <v>24</v>
+        <v>16.4</v>
       </c>
       <c r="I14" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J14" t="n">
-        <v>24.33</v>
+        <v>-61.7</v>
       </c>
       <c r="K14" t="n">
-        <v>-88.52</v>
+        <v>-44.6</v>
       </c>
       <c r="L14" t="n">
-        <v>91.8</v>
+        <v>76.13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:46:25</t>
+          <t>04:46:29</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.66</v>
+        <v>2.71</v>
       </c>
       <c r="F15" t="n">
-        <v>8.630000000000001</v>
+        <v>8.44</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1</v>
+        <v>8</v>
       </c>
       <c r="H15" t="n">
-        <v>16.8</v>
+        <v>26.4</v>
       </c>
       <c r="I15" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J15" t="n">
-        <v>44.17</v>
+        <v>163.93</v>
       </c>
       <c r="K15" t="n">
-        <v>-36.41</v>
+        <v>131.99</v>
       </c>
       <c r="L15" t="n">
-        <v>57.24</v>
+        <v>210.47</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:48:11</t>
+          <t>04:48:24</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.77</v>
+        <v>2.17</v>
       </c>
       <c r="F16" t="n">
-        <v>8.449999999999999</v>
+        <v>9.01</v>
       </c>
       <c r="G16" t="n">
-        <v>12.1</v>
+        <v>5.9</v>
       </c>
       <c r="H16" t="n">
-        <v>24.7</v>
+        <v>21.6</v>
       </c>
       <c r="I16" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>-53.84</v>
+        <v>-74.06999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>-11.67</v>
+        <v>-13.32</v>
       </c>
       <c r="L16" t="n">
-        <v>55.09</v>
+        <v>75.26000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:52:25</t>
+          <t>04:52:38</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.76</v>
+        <v>2.45</v>
       </c>
       <c r="F17" t="n">
-        <v>8.380000000000001</v>
+        <v>7.25</v>
       </c>
       <c r="G17" t="n">
-        <v>6.2</v>
+        <v>2.8</v>
       </c>
       <c r="H17" t="n">
-        <v>18.5</v>
+        <v>23.4</v>
       </c>
       <c r="I17" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>3.35</v>
+        <v>-120.54</v>
       </c>
       <c r="K17" t="n">
-        <v>67.26000000000001</v>
+        <v>-73.43000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>67.34</v>
+        <v>141.14</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:54:08</t>
+          <t>04:54:32</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="F18" t="n">
-        <v>8.85</v>
+        <v>7.85</v>
       </c>
       <c r="G18" t="n">
-        <v>21.9</v>
+        <v>2.5</v>
       </c>
       <c r="H18" t="n">
-        <v>24.1</v>
+        <v>14.8</v>
       </c>
       <c r="I18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>108.53</v>
+        <v>-73.38</v>
       </c>
       <c r="K18" t="n">
-        <v>133.97</v>
+        <v>88.95</v>
       </c>
       <c r="L18" t="n">
-        <v>172.41</v>
+        <v>115.31</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:56:25</t>
+          <t>04:56:23</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="F19" t="n">
-        <v>7.99</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>358.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>27</v>
+        <v>22.8</v>
       </c>
       <c r="I19" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.42</v>
+        <v>-5.21</v>
       </c>
       <c r="K19" t="n">
-        <v>19.96</v>
+        <v>-63.46</v>
       </c>
       <c r="L19" t="n">
-        <v>20.25</v>
+        <v>63.68</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:01:08</t>
+          <t>05:00:22</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.82</v>
+        <v>3.15</v>
       </c>
       <c r="F20" t="n">
-        <v>7.96</v>
+        <v>7.78</v>
       </c>
       <c r="G20" t="n">
-        <v>13</v>
+        <v>8.9</v>
       </c>
       <c r="H20" t="n">
-        <v>21.1</v>
+        <v>16.2</v>
       </c>
       <c r="I20" t="n">
         <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>285.67</v>
+        <v>-169.42</v>
       </c>
       <c r="K20" t="n">
-        <v>82.19</v>
+        <v>-81.59999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>297.26</v>
+        <v>188.05</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:03:03</t>
+          <t>05:02:30</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.77</v>
+        <v>2.57</v>
       </c>
       <c r="F21" t="n">
-        <v>7.79</v>
+        <v>7.76</v>
       </c>
       <c r="G21" t="n">
-        <v>8.9</v>
+        <v>13.9</v>
       </c>
       <c r="H21" t="n">
         <v>17.1</v>
       </c>
       <c r="I21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J21" t="n">
-        <v>62.81</v>
+        <v>54.56</v>
       </c>
       <c r="K21" t="n">
-        <v>-84.95</v>
+        <v>-127.67</v>
       </c>
       <c r="L21" t="n">
-        <v>105.65</v>
+        <v>138.84</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:03:51</t>
+          <t>05:04:20</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.41</v>
+        <v>2.77</v>
       </c>
       <c r="F22" t="n">
-        <v>8.390000000000001</v>
+        <v>8.32</v>
       </c>
       <c r="G22" t="n">
-        <v>359.7</v>
+        <v>12.8</v>
       </c>
       <c r="H22" t="n">
-        <v>15.6</v>
+        <v>23.2</v>
       </c>
       <c r="I22" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J22" t="n">
-        <v>-90.64</v>
+        <v>-56.23</v>
       </c>
       <c r="K22" t="n">
-        <v>-57.81</v>
+        <v>-98.67</v>
       </c>
       <c r="L22" t="n">
-        <v>107.5</v>
+        <v>113.57</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:10:08</t>
+          <t>05:08:31</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.12</v>
+        <v>3.05</v>
       </c>
       <c r="F23" t="n">
-        <v>8.619999999999999</v>
+        <v>8.27</v>
       </c>
       <c r="G23" t="n">
-        <v>18.9</v>
+        <v>18.3</v>
       </c>
       <c r="H23" t="n">
-        <v>17.2</v>
+        <v>19.1</v>
       </c>
       <c r="I23" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J23" t="n">
-        <v>410.17</v>
+        <v>189.67</v>
       </c>
       <c r="K23" t="n">
-        <v>-274.68</v>
+        <v>-105.88</v>
       </c>
       <c r="L23" t="n">
-        <v>493.65</v>
+        <v>217.22</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:12:24</t>
+          <t>05:09:40</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.49</v>
+        <v>2.8</v>
       </c>
       <c r="F24" t="n">
-        <v>8.68</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>9.800000000000001</v>
+        <v>2</v>
       </c>
       <c r="H24" t="n">
-        <v>18</v>
+        <v>14.7</v>
       </c>
       <c r="I24" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J24" t="n">
-        <v>136</v>
+        <v>213.3</v>
       </c>
       <c r="K24" t="n">
-        <v>-360.68</v>
+        <v>188.6</v>
       </c>
       <c r="L24" t="n">
-        <v>385.47</v>
+        <v>284.72</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:14:05</t>
+          <t>05:10:59</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.99</v>
+        <v>2.81</v>
       </c>
       <c r="F25" t="n">
-        <v>8.49</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>9.300000000000001</v>
+        <v>12.1</v>
       </c>
       <c r="H25" t="n">
-        <v>21</v>
+        <v>21.3</v>
       </c>
       <c r="I25" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>178.43</v>
+        <v>-308.83</v>
       </c>
       <c r="K25" t="n">
-        <v>98.19</v>
+        <v>-153.85</v>
       </c>
       <c r="L25" t="n">
-        <v>203.66</v>
+        <v>345.03</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:19:02</t>
+          <t>05:15:16</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.9</v>
+        <v>2.43</v>
       </c>
       <c r="F26" t="n">
-        <v>8.35</v>
+        <v>8.93</v>
       </c>
       <c r="G26" t="n">
-        <v>1.2</v>
+        <v>352.5</v>
       </c>
       <c r="H26" t="n">
-        <v>28.3</v>
+        <v>26.2</v>
       </c>
       <c r="I26" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J26" t="n">
-        <v>-250.33</v>
+        <v>275.44</v>
       </c>
       <c r="K26" t="n">
-        <v>371.53</v>
+        <v>172.67</v>
       </c>
       <c r="L26" t="n">
-        <v>448</v>
+        <v>325.09</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:19:48</t>
+          <t>05:17:36</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="F27" t="n">
-        <v>8.24</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>14.2</v>
+        <v>14</v>
       </c>
       <c r="H27" t="n">
-        <v>18.1</v>
+        <v>19.2</v>
       </c>
       <c r="I27" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>141.04</v>
+        <v>-12.99</v>
       </c>
       <c r="K27" t="n">
-        <v>71.40000000000001</v>
+        <v>-201.98</v>
       </c>
       <c r="L27" t="n">
-        <v>158.09</v>
+        <v>202.4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:21:47</t>
+          <t>05:19:33</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.62</v>
+        <v>2.43</v>
       </c>
       <c r="F28" t="n">
-        <v>8.32</v>
+        <v>7.99</v>
       </c>
       <c r="G28" t="n">
-        <v>355.9</v>
+        <v>354.2</v>
       </c>
       <c r="H28" t="n">
-        <v>18.3</v>
+        <v>20.4</v>
       </c>
       <c r="I28" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J28" t="n">
-        <v>33.9</v>
+        <v>-174.52</v>
       </c>
       <c r="K28" t="n">
-        <v>538.75</v>
+        <v>365.13</v>
       </c>
       <c r="L28" t="n">
-        <v>539.8200000000001</v>
+        <v>404.69</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:34:10</t>
+          <t>05:28:19</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.49</v>
+        <v>2.43</v>
       </c>
       <c r="F29" t="n">
-        <v>8.539999999999999</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="G29" t="n">
-        <v>354.7</v>
+        <v>11</v>
       </c>
       <c r="H29" t="n">
-        <v>20.6</v>
+        <v>25.4</v>
       </c>
       <c r="I29" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>-45.55</v>
+        <v>-139.62</v>
       </c>
       <c r="K29" t="n">
-        <v>-22.72</v>
+        <v>4.12</v>
       </c>
       <c r="L29" t="n">
-        <v>50.9</v>
+        <v>139.68</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:36:46</t>
+          <t>05:29:15</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.41</v>
+        <v>2.85</v>
       </c>
       <c r="F30" t="n">
-        <v>7.44</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="G30" t="n">
-        <v>12</v>
+        <v>11.4</v>
       </c>
       <c r="H30" t="n">
-        <v>26.6</v>
+        <v>17.3</v>
       </c>
       <c r="I30" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J30" t="n">
-        <v>23.72</v>
+        <v>-7.03</v>
       </c>
       <c r="K30" t="n">
-        <v>56.95</v>
+        <v>-85.81999999999999</v>
       </c>
       <c r="L30" t="n">
-        <v>61.69</v>
+        <v>86.11</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:38:19</t>
+          <t>05:30:48</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.59</v>
+        <v>2.82</v>
       </c>
       <c r="F31" t="n">
-        <v>8.09</v>
+        <v>8.57</v>
       </c>
       <c r="G31" t="n">
-        <v>8.699999999999999</v>
+        <v>18.1</v>
       </c>
       <c r="H31" t="n">
-        <v>16.9</v>
+        <v>22.3</v>
       </c>
       <c r="I31" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>11.67</v>
+        <v>11.91</v>
       </c>
       <c r="K31" t="n">
-        <v>43.06</v>
+        <v>-100.08</v>
       </c>
       <c r="L31" t="n">
-        <v>44.62</v>
+        <v>100.78</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:42:55</t>
+          <t>05:34:32</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.61</v>
+        <v>2.78</v>
       </c>
       <c r="F32" t="n">
-        <v>7.48</v>
+        <v>8.76</v>
       </c>
       <c r="G32" t="n">
-        <v>5.2</v>
+        <v>16.2</v>
       </c>
       <c r="H32" t="n">
-        <v>17.5</v>
+        <v>24.7</v>
       </c>
       <c r="I32" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J32" t="n">
-        <v>46.86</v>
+        <v>-35.19</v>
       </c>
       <c r="K32" t="n">
-        <v>14.11</v>
+        <v>-52.94</v>
       </c>
       <c r="L32" t="n">
-        <v>48.94</v>
+        <v>63.57</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:44:26</t>
+          <t>05:36:43</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3.17</v>
+        <v>3.23</v>
       </c>
       <c r="F33" t="n">
-        <v>8.029999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="G33" t="n">
-        <v>10.1</v>
+        <v>11.1</v>
       </c>
       <c r="H33" t="n">
-        <v>24.1</v>
+        <v>23.6</v>
       </c>
       <c r="I33" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J33" t="n">
-        <v>-92.94</v>
+        <v>-1.5</v>
       </c>
       <c r="K33" t="n">
-        <v>29.63</v>
+        <v>190.71</v>
       </c>
       <c r="L33" t="n">
-        <v>97.55</v>
+        <v>190.71</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:46:36</t>
+          <t>05:38:45</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.84</v>
+        <v>2.36</v>
       </c>
       <c r="F34" t="n">
-        <v>8.880000000000001</v>
+        <v>8.65</v>
       </c>
       <c r="G34" t="n">
-        <v>7.4</v>
+        <v>352.3</v>
       </c>
       <c r="H34" t="n">
-        <v>18.4</v>
+        <v>16.1</v>
       </c>
       <c r="I34" t="n">
         <v>27</v>
       </c>
       <c r="J34" t="n">
-        <v>-68.79000000000001</v>
+        <v>99.13</v>
       </c>
       <c r="K34" t="n">
-        <v>-96.56999999999999</v>
+        <v>45.95</v>
       </c>
       <c r="L34" t="n">
-        <v>118.56</v>
+        <v>109.26</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:51:49</t>
+          <t>05:42:16</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.81</v>
+        <v>2.94</v>
       </c>
       <c r="F35" t="n">
-        <v>8.4</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="G35" t="n">
-        <v>0.6</v>
+        <v>17.3</v>
       </c>
       <c r="H35" t="n">
-        <v>13.3</v>
+        <v>20</v>
       </c>
       <c r="I35" t="n">
         <v>25</v>
       </c>
       <c r="J35" t="n">
-        <v>-62.26</v>
+        <v>-229.54</v>
       </c>
       <c r="K35" t="n">
-        <v>201.68</v>
+        <v>53.27</v>
       </c>
       <c r="L35" t="n">
-        <v>211.08</v>
+        <v>235.64</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:54:18</t>
+          <t>05:43:34</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.31</v>
+        <v>2.63</v>
       </c>
       <c r="F36" t="n">
-        <v>8.550000000000001</v>
+        <v>8.42</v>
       </c>
       <c r="G36" t="n">
-        <v>3.2</v>
+        <v>6.3</v>
       </c>
       <c r="H36" t="n">
-        <v>18.9</v>
+        <v>18.6</v>
       </c>
       <c r="I36" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>-124.34</v>
+        <v>344.2</v>
       </c>
       <c r="K36" t="n">
-        <v>1.74</v>
+        <v>143.5</v>
       </c>
       <c r="L36" t="n">
-        <v>124.35</v>
+        <v>372.91</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:56:18</t>
+          <t>05:45:41</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.18</v>
+        <v>3.21</v>
       </c>
       <c r="F37" t="n">
-        <v>7.57</v>
+        <v>8.58</v>
       </c>
       <c r="G37" t="n">
-        <v>7.7</v>
+        <v>16.8</v>
       </c>
       <c r="H37" t="n">
-        <v>18.2</v>
+        <v>19.5</v>
       </c>
       <c r="I37" t="n">
         <v>24</v>
       </c>
       <c r="J37" t="n">
-        <v>-240.14</v>
+        <v>-498.32</v>
       </c>
       <c r="K37" t="n">
-        <v>151.99</v>
+        <v>263.39</v>
       </c>
       <c r="L37" t="n">
-        <v>284.2</v>
+        <v>563.65</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06:00:15</t>
+          <t>05:50:30</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>4.18</v>
+        <v>2.89</v>
       </c>
       <c r="F38" t="n">
-        <v>8.34</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="G38" t="n">
-        <v>10.7</v>
+        <v>11.3</v>
       </c>
       <c r="H38" t="n">
-        <v>15.3</v>
+        <v>22.5</v>
       </c>
       <c r="I38" t="n">
         <v>28</v>
       </c>
       <c r="J38" t="n">
-        <v>-474.12</v>
+        <v>101.97</v>
       </c>
       <c r="K38" t="n">
-        <v>-62.07</v>
+        <v>-309.23</v>
       </c>
       <c r="L38" t="n">
-        <v>478.17</v>
+        <v>325.61</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06:01:14</t>
+          <t>05:52:21</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.95</v>
+        <v>2.77</v>
       </c>
       <c r="F39" t="n">
-        <v>8.130000000000001</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>360</v>
       </c>
       <c r="H39" t="n">
-        <v>25.6</v>
+        <v>25.2</v>
       </c>
       <c r="I39" t="n">
         <v>28</v>
       </c>
       <c r="J39" t="n">
-        <v>250.94</v>
+        <v>-111</v>
       </c>
       <c r="K39" t="n">
-        <v>269.74</v>
+        <v>125.87</v>
       </c>
       <c r="L39" t="n">
-        <v>368.42</v>
+        <v>167.82</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06:02:20</t>
+          <t>05:54:28</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3</v>
+        <v>2.69</v>
       </c>
       <c r="F40" t="n">
-        <v>7.82</v>
+        <v>7.85</v>
       </c>
       <c r="G40" t="n">
-        <v>20.9</v>
+        <v>18.7</v>
       </c>
       <c r="H40" t="n">
-        <v>15.4</v>
+        <v>23.9</v>
       </c>
       <c r="I40" t="n">
         <v>25</v>
       </c>
       <c r="J40" t="n">
-        <v>59.05</v>
+        <v>334.82</v>
       </c>
       <c r="K40" t="n">
-        <v>106.33</v>
+        <v>368.09</v>
       </c>
       <c r="L40" t="n">
-        <v>121.63</v>
+        <v>497.59</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:07:17</t>
+          <t>05:58:27</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.31</v>
+        <v>2.78</v>
       </c>
       <c r="F41" t="n">
-        <v>8.57</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="G41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H41" t="n">
-        <v>21.3</v>
+        <v>15.2</v>
       </c>
       <c r="I41" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J41" t="n">
-        <v>156.6</v>
+        <v>-194.74</v>
       </c>
       <c r="K41" t="n">
-        <v>-622.05</v>
+        <v>40.52</v>
       </c>
       <c r="L41" t="n">
-        <v>641.46</v>
+        <v>198.91</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:08:05</t>
+          <t>05:59:17</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.25</v>
+        <v>2.79</v>
       </c>
       <c r="F42" t="n">
-        <v>8.59</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="G42" t="n">
-        <v>0.7</v>
+        <v>12.8</v>
       </c>
       <c r="H42" t="n">
-        <v>26.6</v>
+        <v>22.5</v>
       </c>
       <c r="I42" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J42" t="n">
-        <v>446.72</v>
+        <v>217.59</v>
       </c>
       <c r="K42" t="n">
-        <v>160.3</v>
+        <v>249.09</v>
       </c>
       <c r="L42" t="n">
-        <v>474.61</v>
+        <v>330.75</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:09:37</t>
+          <t>06:00:50</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.95</v>
+        <v>2.6</v>
       </c>
       <c r="F43" t="n">
-        <v>8.66</v>
+        <v>8.44</v>
       </c>
       <c r="G43" t="n">
-        <v>17.1</v>
+        <v>11.8</v>
       </c>
       <c r="H43" t="n">
-        <v>23.9</v>
+        <v>17.9</v>
       </c>
       <c r="I43" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J43" t="n">
-        <v>-276.24</v>
+        <v>-283.15</v>
       </c>
       <c r="K43" t="n">
-        <v>-319.31</v>
+        <v>402.61</v>
       </c>
       <c r="L43" t="n">
-        <v>422.22</v>
+        <v>492.21</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:20:07</t>
+          <t>06:09:16</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.97</v>
+        <v>2.85</v>
       </c>
       <c r="F44" t="n">
-        <v>7.88</v>
+        <v>7.6</v>
       </c>
       <c r="G44" t="n">
-        <v>13.8</v>
+        <v>1.9</v>
       </c>
       <c r="H44" t="n">
-        <v>21.3</v>
+        <v>17.5</v>
       </c>
       <c r="I44" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J44" t="n">
-        <v>-50.39</v>
+        <v>190.28</v>
       </c>
       <c r="K44" t="n">
-        <v>93.87</v>
+        <v>-153.31</v>
       </c>
       <c r="L44" t="n">
-        <v>106.54</v>
+        <v>244.36</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:22:47</t>
+          <t>06:11:09</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.47</v>
+        <v>2.6</v>
       </c>
       <c r="F45" t="n">
-        <v>8.65</v>
+        <v>8.07</v>
       </c>
       <c r="G45" t="n">
-        <v>17.8</v>
+        <v>9.1</v>
       </c>
       <c r="H45" t="n">
-        <v>22.4</v>
+        <v>22.9</v>
       </c>
       <c r="I45" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J45" t="n">
-        <v>-4.18</v>
+        <v>-215.58</v>
       </c>
       <c r="K45" t="n">
-        <v>-52.15</v>
+        <v>-101.9</v>
       </c>
       <c r="L45" t="n">
-        <v>52.31</v>
+        <v>238.45</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:24:26</t>
+          <t>06:13:14</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.43</v>
+        <v>3.11</v>
       </c>
       <c r="F46" t="n">
-        <v>9.09</v>
+        <v>7.4</v>
       </c>
       <c r="G46" t="n">
-        <v>8.5</v>
+        <v>13.4</v>
       </c>
       <c r="H46" t="n">
-        <v>27.1</v>
+        <v>25.2</v>
       </c>
       <c r="I46" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>152.53</v>
+        <v>152.21</v>
       </c>
       <c r="K46" t="n">
-        <v>25.71</v>
+        <v>188.31</v>
       </c>
       <c r="L46" t="n">
-        <v>154.69</v>
+        <v>242.13</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:30:02</t>
+          <t>06:18:11</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>3.67</v>
+        <v>3.23</v>
       </c>
       <c r="F47" t="n">
-        <v>7.75</v>
+        <v>8.93</v>
       </c>
       <c r="G47" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="H47" t="n">
-        <v>22.6</v>
+        <v>19.4</v>
       </c>
       <c r="I47" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J47" t="n">
-        <v>-19.67</v>
+        <v>6.78</v>
       </c>
       <c r="K47" t="n">
-        <v>-44.26</v>
+        <v>32.38</v>
       </c>
       <c r="L47" t="n">
-        <v>48.44</v>
+        <v>33.08</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:32:21</t>
+          <t>06:19:08</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="F48" t="n">
-        <v>8.26</v>
+        <v>8.85</v>
       </c>
       <c r="G48" t="n">
-        <v>11.5</v>
+        <v>1.4</v>
       </c>
       <c r="H48" t="n">
-        <v>24.2</v>
+        <v>16.7</v>
       </c>
       <c r="I48" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>77.48</v>
+        <v>207.8</v>
       </c>
       <c r="K48" t="n">
-        <v>99.75</v>
+        <v>-237.64</v>
       </c>
       <c r="L48" t="n">
-        <v>126.31</v>
+        <v>315.68</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:34:18</t>
+          <t>06:19:59</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.55</v>
+        <v>2.72</v>
       </c>
       <c r="F49" t="n">
-        <v>7.99</v>
+        <v>8.33</v>
       </c>
       <c r="G49" t="n">
-        <v>11.7</v>
+        <v>13.3</v>
       </c>
       <c r="H49" t="n">
-        <v>25.1</v>
+        <v>14.3</v>
       </c>
       <c r="I49" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>57.39</v>
+        <v>-92.34999999999999</v>
       </c>
       <c r="K49" t="n">
-        <v>62.27</v>
+        <v>-0.3</v>
       </c>
       <c r="L49" t="n">
-        <v>84.69</v>
+        <v>92.34999999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:39:44</t>
+          <t>06:24:25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.64</v>
+        <v>2.73</v>
       </c>
       <c r="F50" t="n">
-        <v>8.27</v>
+        <v>8.08</v>
       </c>
       <c r="G50" t="n">
-        <v>0.5</v>
+        <v>6.9</v>
       </c>
       <c r="H50" t="n">
-        <v>22.2</v>
+        <v>18.6</v>
       </c>
       <c r="I50" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J50" t="n">
-        <v>13.88</v>
+        <v>-282.56</v>
       </c>
       <c r="K50" t="n">
-        <v>55.38</v>
+        <v>73.83</v>
       </c>
       <c r="L50" t="n">
-        <v>57.09</v>
+        <v>292.05</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:42:05</t>
+          <t>06:26:45</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.35</v>
+        <v>2.83</v>
       </c>
       <c r="F51" t="n">
-        <v>8.34</v>
+        <v>8.4</v>
       </c>
       <c r="G51" t="n">
-        <v>12.2</v>
+        <v>3</v>
       </c>
       <c r="H51" t="n">
-        <v>18.8</v>
+        <v>20.9</v>
       </c>
       <c r="I51" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J51" t="n">
-        <v>-120.76</v>
+        <v>30.7</v>
       </c>
       <c r="K51" t="n">
-        <v>-18.04</v>
+        <v>-243.85</v>
       </c>
       <c r="L51" t="n">
-        <v>122.1</v>
+        <v>245.78</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:44:25</t>
+          <t>06:28:40</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3.39</v>
+        <v>2.67</v>
       </c>
       <c r="F52" t="n">
-        <v>8.359999999999999</v>
+        <v>8.42</v>
       </c>
       <c r="G52" t="n">
-        <v>359.7</v>
+        <v>11.1</v>
       </c>
       <c r="H52" t="n">
-        <v>18.5</v>
+        <v>18.2</v>
       </c>
       <c r="I52" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J52" t="n">
-        <v>177.15</v>
+        <v>1.6</v>
       </c>
       <c r="K52" t="n">
-        <v>43.7</v>
+        <v>-194.84</v>
       </c>
       <c r="L52" t="n">
-        <v>182.46</v>
+        <v>194.85</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:48:21</t>
+          <t>06:32:17</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.16</v>
+        <v>3.21</v>
       </c>
       <c r="F53" t="n">
-        <v>7.97</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="G53" t="n">
-        <v>1.3</v>
+        <v>14.9</v>
       </c>
       <c r="H53" t="n">
-        <v>19.3</v>
+        <v>18.6</v>
       </c>
       <c r="I53" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J53" t="n">
-        <v>-365.48</v>
+        <v>148.21</v>
       </c>
       <c r="K53" t="n">
-        <v>-252.48</v>
+        <v>251.23</v>
       </c>
       <c r="L53" t="n">
-        <v>444.2</v>
+        <v>291.69</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:50:50</t>
+          <t>06:33:10</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3.15</v>
+        <v>3.29</v>
       </c>
       <c r="F54" t="n">
-        <v>8.24</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="G54" t="n">
-        <v>9</v>
+        <v>4.1</v>
       </c>
       <c r="H54" t="n">
-        <v>20.8</v>
+        <v>17.4</v>
       </c>
       <c r="I54" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>431.67</v>
+        <v>39.03</v>
       </c>
       <c r="K54" t="n">
-        <v>-44.37</v>
+        <v>97.93000000000001</v>
       </c>
       <c r="L54" t="n">
-        <v>433.94</v>
+        <v>105.42</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:52:14</t>
+          <t>06:34:11</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.85</v>
+        <v>2.92</v>
       </c>
       <c r="F55" t="n">
-        <v>7.52</v>
+        <v>8.23</v>
       </c>
       <c r="G55" t="n">
-        <v>354.7</v>
+        <v>3.8</v>
       </c>
       <c r="H55" t="n">
-        <v>22.4</v>
+        <v>24.5</v>
       </c>
       <c r="I55" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>120.16</v>
+        <v>-143.53</v>
       </c>
       <c r="K55" t="n">
-        <v>-39.61</v>
+        <v>-387.63</v>
       </c>
       <c r="L55" t="n">
-        <v>126.52</v>
+        <v>413.35</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:58:14</t>
+          <t>06:38:18</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.34</v>
+        <v>2.92</v>
       </c>
       <c r="F56" t="n">
-        <v>7.64</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="G56" t="n">
-        <v>19.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H56" t="n">
-        <v>19.9</v>
+        <v>19</v>
       </c>
       <c r="I56" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J56" t="n">
-        <v>-564.64</v>
+        <v>-134.06</v>
       </c>
       <c r="K56" t="n">
-        <v>-74.92</v>
+        <v>-349.3</v>
       </c>
       <c r="L56" t="n">
-        <v>569.58</v>
+        <v>374.14</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07:00:50</t>
+          <t>06:40:34</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="F57" t="n">
-        <v>8.57</v>
+        <v>7.35</v>
       </c>
       <c r="G57" t="n">
-        <v>9.4</v>
+        <v>19.2</v>
       </c>
       <c r="H57" t="n">
-        <v>22.6</v>
+        <v>22.2</v>
       </c>
       <c r="I57" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J57" t="n">
-        <v>-10.9</v>
+        <v>239.17</v>
       </c>
       <c r="K57" t="n">
-        <v>118.74</v>
+        <v>-48.73</v>
       </c>
       <c r="L57" t="n">
-        <v>119.24</v>
+        <v>244.09</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07:01:53</t>
+          <t>06:41:09</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.23</v>
+        <v>2.75</v>
       </c>
       <c r="F58" t="n">
-        <v>8.58</v>
+        <v>8.1</v>
       </c>
       <c r="G58" t="n">
-        <v>28.5</v>
+        <v>7.5</v>
       </c>
       <c r="H58" t="n">
-        <v>24.5</v>
+        <v>18.3</v>
       </c>
       <c r="I58" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J58" t="n">
-        <v>221.91</v>
+        <v>411.09</v>
       </c>
       <c r="K58" t="n">
-        <v>526.91</v>
+        <v>-367.46</v>
       </c>
       <c r="L58" t="n">
-        <v>571.73</v>
+        <v>551.39</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:14:11</t>
+          <t>06:50:28</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="F59" t="n">
-        <v>8.199999999999999</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="G59" t="n">
-        <v>14.6</v>
+        <v>9</v>
       </c>
       <c r="H59" t="n">
-        <v>21.9</v>
+        <v>18</v>
       </c>
       <c r="I59" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>37.14</v>
+        <v>48.37</v>
       </c>
       <c r="K59" t="n">
-        <v>32.48</v>
+        <v>-89.76000000000001</v>
       </c>
       <c r="L59" t="n">
-        <v>49.34</v>
+        <v>101.96</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:15:15</t>
+          <t>06:52:24</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>3.24</v>
+        <v>2.87</v>
       </c>
       <c r="F60" t="n">
-        <v>9.039999999999999</v>
+        <v>8.57</v>
       </c>
       <c r="G60" t="n">
-        <v>16.6</v>
+        <v>8.5</v>
       </c>
       <c r="H60" t="n">
-        <v>15.5</v>
+        <v>24.3</v>
       </c>
       <c r="I60" t="n">
         <v>29</v>
       </c>
       <c r="J60" t="n">
-        <v>2.67</v>
+        <v>60.88</v>
       </c>
       <c r="K60" t="n">
-        <v>-39.54</v>
+        <v>1.45</v>
       </c>
       <c r="L60" t="n">
-        <v>39.63</v>
+        <v>60.89</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:16:53</t>
+          <t>06:54:34</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>3.37</v>
+        <v>3.06</v>
       </c>
       <c r="F61" t="n">
-        <v>8.289999999999999</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="G61" t="n">
-        <v>23.1</v>
+        <v>4.5</v>
       </c>
       <c r="H61" t="n">
-        <v>24.3</v>
+        <v>19.2</v>
       </c>
       <c r="I61" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J61" t="n">
-        <v>11.63</v>
+        <v>-78.17</v>
       </c>
       <c r="K61" t="n">
-        <v>165.52</v>
+        <v>-27.24</v>
       </c>
       <c r="L61" t="n">
-        <v>165.93</v>
+        <v>82.78</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:20:55</t>
+          <t>06:59:30</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="F62" t="n">
-        <v>8.390000000000001</v>
+        <v>7.74</v>
       </c>
       <c r="G62" t="n">
-        <v>8.6</v>
+        <v>10.4</v>
       </c>
       <c r="H62" t="n">
-        <v>21.7</v>
+        <v>20.7</v>
       </c>
       <c r="I62" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>164.52</v>
+        <v>-50.54</v>
       </c>
       <c r="K62" t="n">
-        <v>-25.36</v>
+        <v>82.2</v>
       </c>
       <c r="L62" t="n">
-        <v>166.46</v>
+        <v>96.48999999999999</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:22:55</t>
+          <t>07:01:20</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="F63" t="n">
-        <v>8.460000000000001</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="G63" t="n">
-        <v>3.8</v>
+        <v>19.1</v>
       </c>
       <c r="H63" t="n">
-        <v>23.2</v>
+        <v>25</v>
       </c>
       <c r="I63" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J63" t="n">
-        <v>-80.59999999999999</v>
+        <v>3.24</v>
       </c>
       <c r="K63" t="n">
-        <v>-30.66</v>
+        <v>141.47</v>
       </c>
       <c r="L63" t="n">
-        <v>86.23</v>
+        <v>141.51</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:23:53</t>
+          <t>07:03:25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.41</v>
+        <v>3.05</v>
       </c>
       <c r="F64" t="n">
-        <v>7.87</v>
+        <v>7.98</v>
       </c>
       <c r="G64" t="n">
-        <v>12.7</v>
+        <v>25.3</v>
       </c>
       <c r="H64" t="n">
-        <v>22.7</v>
+        <v>14</v>
       </c>
       <c r="I64" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J64" t="n">
-        <v>-12.62</v>
+        <v>-38.05</v>
       </c>
       <c r="K64" t="n">
-        <v>-22.72</v>
+        <v>-274.05</v>
       </c>
       <c r="L64" t="n">
-        <v>25.99</v>
+        <v>276.68</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:29:21</t>
+          <t>07:07:30</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.01</v>
+        <v>2.7</v>
       </c>
       <c r="F65" t="n">
-        <v>7.92</v>
+        <v>7.94</v>
       </c>
       <c r="G65" t="n">
-        <v>16.2</v>
+        <v>10.1</v>
       </c>
       <c r="H65" t="n">
-        <v>20.5</v>
+        <v>13.9</v>
       </c>
       <c r="I65" t="n">
         <v>27</v>
       </c>
       <c r="J65" t="n">
-        <v>-54</v>
+        <v>-154.53</v>
       </c>
       <c r="K65" t="n">
-        <v>-27.54</v>
+        <v>59.17</v>
       </c>
       <c r="L65" t="n">
-        <v>60.62</v>
+        <v>165.47</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:30:21</t>
+          <t>07:09:24</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>3.28</v>
+        <v>2.69</v>
       </c>
       <c r="F66" t="n">
-        <v>8.43</v>
+        <v>8.18</v>
       </c>
       <c r="G66" t="n">
-        <v>357.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H66" t="n">
-        <v>19.2</v>
+        <v>21.6</v>
       </c>
       <c r="I66" t="n">
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-27.88</v>
+        <v>-140.36</v>
       </c>
       <c r="K66" t="n">
-        <v>-243.91</v>
+        <v>-135.14</v>
       </c>
       <c r="L66" t="n">
-        <v>245.5</v>
+        <v>194.85</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:32:57</t>
+          <t>07:11:10</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.98</v>
+        <v>3.44</v>
       </c>
       <c r="F67" t="n">
-        <v>7.66</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G67" t="n">
-        <v>4.5</v>
+        <v>17.3</v>
       </c>
       <c r="H67" t="n">
-        <v>14.1</v>
+        <v>14.9</v>
       </c>
       <c r="I67" t="n">
         <v>27</v>
       </c>
       <c r="J67" t="n">
-        <v>49.97</v>
+        <v>237.96</v>
       </c>
       <c r="K67" t="n">
-        <v>-6.13</v>
+        <v>-138.66</v>
       </c>
       <c r="L67" t="n">
-        <v>50.35</v>
+        <v>275.41</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:38:00</t>
+          <t>07:16:36</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.91</v>
+        <v>3.18</v>
       </c>
       <c r="F68" t="n">
-        <v>8.02</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G68" t="n">
-        <v>16.6</v>
+        <v>6.8</v>
       </c>
       <c r="H68" t="n">
-        <v>15.8</v>
+        <v>21.9</v>
       </c>
       <c r="I68" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>118.23</v>
+        <v>220.19</v>
       </c>
       <c r="K68" t="n">
-        <v>-587.12</v>
+        <v>-14.11</v>
       </c>
       <c r="L68" t="n">
-        <v>598.9</v>
+        <v>220.64</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:40:11</t>
+          <t>07:18:14</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>3.13</v>
+        <v>2.89</v>
       </c>
       <c r="F69" t="n">
-        <v>8.5</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="G69" t="n">
-        <v>7.1</v>
+        <v>4.7</v>
       </c>
       <c r="H69" t="n">
-        <v>19.2</v>
+        <v>18</v>
       </c>
       <c r="I69" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>-15.79</v>
+        <v>-54.11</v>
       </c>
       <c r="K69" t="n">
-        <v>-336.75</v>
+        <v>77.34999999999999</v>
       </c>
       <c r="L69" t="n">
-        <v>337.12</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:41:02</t>
+          <t>07:19:49</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.93</v>
+        <v>4.11</v>
       </c>
       <c r="F70" t="n">
-        <v>8.06</v>
+        <v>8.85</v>
       </c>
       <c r="G70" t="n">
-        <v>7.2</v>
+        <v>14.2</v>
       </c>
       <c r="H70" t="n">
-        <v>13.6</v>
+        <v>24.6</v>
       </c>
       <c r="I70" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J70" t="n">
-        <v>-199.35</v>
+        <v>267.95</v>
       </c>
       <c r="K70" t="n">
-        <v>-1.89</v>
+        <v>424.11</v>
       </c>
       <c r="L70" t="n">
-        <v>199.36</v>
+        <v>501.66</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:47:02</t>
+          <t>07:24:22</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="F71" t="n">
-        <v>8.17</v>
+        <v>8.24</v>
       </c>
       <c r="G71" t="n">
-        <v>16.7</v>
+        <v>5.6</v>
       </c>
       <c r="H71" t="n">
-        <v>20.7</v>
+        <v>27.4</v>
       </c>
       <c r="I71" t="n">
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>36.22</v>
+        <v>-125.9</v>
       </c>
       <c r="K71" t="n">
-        <v>28.92</v>
+        <v>-653.12</v>
       </c>
       <c r="L71" t="n">
-        <v>46.35</v>
+        <v>665.15</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:47:46</t>
+          <t>07:26:28</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2.95</v>
+        <v>3.39</v>
       </c>
       <c r="F72" t="n">
-        <v>8.029999999999999</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="G72" t="n">
-        <v>16.5</v>
+        <v>358.5</v>
       </c>
       <c r="H72" t="n">
-        <v>20.6</v>
+        <v>20.3</v>
       </c>
       <c r="I72" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J72" t="n">
-        <v>-590.25</v>
+        <v>-444.35</v>
       </c>
       <c r="K72" t="n">
-        <v>-314.21</v>
+        <v>140.74</v>
       </c>
       <c r="L72" t="n">
-        <v>668.67</v>
+        <v>466.11</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:50:01</t>
+          <t>07:28:02</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.72</v>
+        <v>2.85</v>
       </c>
       <c r="F73" t="n">
-        <v>8.140000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="G73" t="n">
-        <v>0.3</v>
+        <v>3.4</v>
       </c>
       <c r="H73" t="n">
-        <v>17.6</v>
+        <v>22.8</v>
       </c>
       <c r="I73" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J73" t="n">
-        <v>61.18</v>
+        <v>196.76</v>
       </c>
       <c r="K73" t="n">
-        <v>-89.31</v>
+        <v>575.9400000000001</v>
       </c>
       <c r="L73" t="n">
-        <v>108.25</v>
+        <v>608.62</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>08:00:40</t>
+          <t>07:40:20</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>2.56</v>
+        <v>2.77</v>
       </c>
       <c r="F74" t="n">
-        <v>8.550000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="G74" t="n">
-        <v>11.9</v>
+        <v>25.7</v>
       </c>
       <c r="H74" t="n">
-        <v>16.6</v>
+        <v>24.3</v>
       </c>
       <c r="I74" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>-36.63</v>
+        <v>43.8</v>
       </c>
       <c r="K74" t="n">
-        <v>67.84999999999999</v>
+        <v>-62.82</v>
       </c>
       <c r="L74" t="n">
-        <v>77.09999999999999</v>
+        <v>76.58</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>08:02:33</t>
+          <t>07:41:34</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>3.15</v>
+        <v>2.86</v>
       </c>
       <c r="F75" t="n">
-        <v>8.029999999999999</v>
+        <v>8.07</v>
       </c>
       <c r="G75" t="n">
-        <v>8.4</v>
+        <v>21.9</v>
       </c>
       <c r="H75" t="n">
-        <v>21.9</v>
+        <v>14.4</v>
       </c>
       <c r="I75" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>43.75</v>
+        <v>171.89</v>
       </c>
       <c r="K75" t="n">
-        <v>56.31</v>
+        <v>37.09</v>
       </c>
       <c r="L75" t="n">
-        <v>71.31</v>
+        <v>175.85</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>08:04:50</t>
+          <t>07:43:29</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.26</v>
+        <v>2.99</v>
       </c>
       <c r="F76" t="n">
-        <v>8.01</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="G76" t="n">
-        <v>14.3</v>
+        <v>14.1</v>
       </c>
       <c r="H76" t="n">
-        <v>21.4</v>
+        <v>18.9</v>
       </c>
       <c r="I76" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J76" t="n">
-        <v>-91.15000000000001</v>
+        <v>-139.46</v>
       </c>
       <c r="K76" t="n">
-        <v>-5.2</v>
+        <v>-99.62</v>
       </c>
       <c r="L76" t="n">
-        <v>91.3</v>
+        <v>171.39</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>08:10:04</t>
+          <t>07:50:08</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>2.97</v>
+        <v>2.71</v>
       </c>
       <c r="F77" t="n">
-        <v>8.859999999999999</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="G77" t="n">
-        <v>9.699999999999999</v>
+        <v>1</v>
       </c>
       <c r="H77" t="n">
-        <v>15.8</v>
+        <v>16.8</v>
       </c>
       <c r="I77" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J77" t="n">
-        <v>2.33</v>
+        <v>-152.42</v>
       </c>
       <c r="K77" t="n">
-        <v>12.97</v>
+        <v>33.39</v>
       </c>
       <c r="L77" t="n">
-        <v>13.18</v>
+        <v>156.03</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>08:12:04</t>
+          <t>07:51:59</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>3.4</v>
+        <v>3.53</v>
       </c>
       <c r="F78" t="n">
-        <v>8.16</v>
+        <v>8.65</v>
       </c>
       <c r="G78" t="n">
-        <v>4.8</v>
+        <v>20.2</v>
       </c>
       <c r="H78" t="n">
-        <v>17.5</v>
+        <v>19.4</v>
       </c>
       <c r="I78" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J78" t="n">
-        <v>-105.52</v>
+        <v>-82.43000000000001</v>
       </c>
       <c r="K78" t="n">
-        <v>97.98</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>143.99</v>
+        <v>109.57</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>08:13:31</t>
+          <t>07:53:42</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>3.35</v>
+        <v>2.73</v>
       </c>
       <c r="F79" t="n">
-        <v>8.26</v>
+        <v>7.53</v>
       </c>
       <c r="G79" t="n">
-        <v>11.9</v>
+        <v>13.4</v>
       </c>
       <c r="H79" t="n">
-        <v>23.1</v>
+        <v>24.8</v>
       </c>
       <c r="I79" t="n">
         <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>-109.72</v>
+        <v>-93.12</v>
       </c>
       <c r="K79" t="n">
-        <v>72.44</v>
+        <v>-19.27</v>
       </c>
       <c r="L79" t="n">
-        <v>131.48</v>
+        <v>95.09</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:18:17</t>
+          <t>07:58:28</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.37</v>
+        <v>2.77</v>
       </c>
       <c r="F80" t="n">
-        <v>8.76</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="G80" t="n">
-        <v>9</v>
+        <v>13.1</v>
       </c>
       <c r="H80" t="n">
-        <v>22.5</v>
+        <v>26.7</v>
       </c>
       <c r="I80" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>178.56</v>
+        <v>-279.06</v>
       </c>
       <c r="K80" t="n">
-        <v>-132.39</v>
+        <v>-199.7</v>
       </c>
       <c r="L80" t="n">
-        <v>222.28</v>
+        <v>343.15</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:19:10</t>
+          <t>07:59:21</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.99</v>
+        <v>2.65</v>
       </c>
       <c r="F81" t="n">
-        <v>8.640000000000001</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="G81" t="n">
-        <v>8.300000000000001</v>
+        <v>11.1</v>
       </c>
       <c r="H81" t="n">
-        <v>18.2</v>
+        <v>15.7</v>
       </c>
       <c r="I81" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>56.57</v>
+        <v>153.71</v>
       </c>
       <c r="K81" t="n">
-        <v>-114.27</v>
+        <v>-21.76</v>
       </c>
       <c r="L81" t="n">
-        <v>127.5</v>
+        <v>155.25</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:21:13</t>
+          <t>08:00:34</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="F82" t="n">
-        <v>8.65</v>
+        <v>8.08</v>
       </c>
       <c r="G82" t="n">
-        <v>1.8</v>
+        <v>21.8</v>
       </c>
       <c r="H82" t="n">
-        <v>19.4</v>
+        <v>11.6</v>
       </c>
       <c r="I82" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J82" t="n">
-        <v>177.03</v>
+        <v>-77.95999999999999</v>
       </c>
       <c r="K82" t="n">
-        <v>20.51</v>
+        <v>94.94</v>
       </c>
       <c r="L82" t="n">
-        <v>178.21</v>
+        <v>122.85</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:25:10</t>
+          <t>08:03:51</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.69</v>
+        <v>2.81</v>
       </c>
       <c r="F83" t="n">
-        <v>8.779999999999999</v>
+        <v>8.17</v>
       </c>
       <c r="G83" t="n">
-        <v>356.1</v>
+        <v>12.9</v>
       </c>
       <c r="H83" t="n">
-        <v>14.5</v>
+        <v>20.5</v>
       </c>
       <c r="I83" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J83" t="n">
-        <v>32.73</v>
+        <v>222.72</v>
       </c>
       <c r="K83" t="n">
-        <v>60.59</v>
+        <v>226.43</v>
       </c>
       <c r="L83" t="n">
-        <v>68.87</v>
+        <v>317.61</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:26:37</t>
+          <t>08:05:34</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.24</v>
+        <v>3.23</v>
       </c>
       <c r="F84" t="n">
-        <v>8.25</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="G84" t="n">
-        <v>9.1</v>
+        <v>31.3</v>
       </c>
       <c r="H84" t="n">
-        <v>16.2</v>
+        <v>23.1</v>
       </c>
       <c r="I84" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J84" t="n">
-        <v>-206.35</v>
+        <v>-216.26</v>
       </c>
       <c r="K84" t="n">
-        <v>-590.13</v>
+        <v>-40.53</v>
       </c>
       <c r="L84" t="n">
-        <v>625.16</v>
+        <v>220.03</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:28:52</t>
+          <t>08:06:53</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.95</v>
+        <v>3.03</v>
       </c>
       <c r="F85" t="n">
-        <v>9.039999999999999</v>
+        <v>7.65</v>
       </c>
       <c r="G85" t="n">
-        <v>10.6</v>
+        <v>358.8</v>
       </c>
       <c r="H85" t="n">
-        <v>20.6</v>
+        <v>24.4</v>
       </c>
       <c r="I85" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>249.17</v>
+        <v>-218.77</v>
       </c>
       <c r="K85" t="n">
-        <v>-67.25</v>
+        <v>-296.84</v>
       </c>
       <c r="L85" t="n">
-        <v>258.08</v>
+        <v>368.75</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:33:11</t>
+          <t>08:10:05</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,10 +3649,10 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="F86" t="n">
-        <v>7.9</v>
+        <v>8.08</v>
       </c>
       <c r="G86" t="n">
         <v>4.9</v>
@@ -3661,22 +3661,22 @@
         <v>19.6</v>
       </c>
       <c r="I86" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>-311.4</v>
+        <v>347.41</v>
       </c>
       <c r="K86" t="n">
-        <v>-81.48999999999999</v>
+        <v>546.66</v>
       </c>
       <c r="L86" t="n">
-        <v>321.89</v>
+        <v>647.71</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:35:01</t>
+          <t>08:10:56</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.91</v>
+        <v>3.16</v>
       </c>
       <c r="F87" t="n">
-        <v>7.78</v>
+        <v>8.83</v>
       </c>
       <c r="G87" t="n">
-        <v>4.6</v>
+        <v>13</v>
       </c>
       <c r="H87" t="n">
-        <v>21.9</v>
+        <v>21.5</v>
       </c>
       <c r="I87" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>127.5</v>
+        <v>-81.12</v>
       </c>
       <c r="K87" t="n">
-        <v>412.73</v>
+        <v>199.55</v>
       </c>
       <c r="L87" t="n">
-        <v>431.98</v>
+        <v>215.4</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:36:19</t>
+          <t>08:12:05</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.63</v>
+        <v>3.12</v>
       </c>
       <c r="F88" t="n">
-        <v>8.710000000000001</v>
+        <v>8</v>
       </c>
       <c r="G88" t="n">
-        <v>7.8</v>
+        <v>16.4</v>
       </c>
       <c r="H88" t="n">
-        <v>25.5</v>
+        <v>14.4</v>
       </c>
       <c r="I88" t="n">
         <v>28</v>
       </c>
       <c r="J88" t="n">
-        <v>-419.36</v>
+        <v>309.11</v>
       </c>
       <c r="K88" t="n">
-        <v>-580.28</v>
+        <v>208.26</v>
       </c>
       <c r="L88" t="n">
-        <v>715.95</v>
+        <v>372.72</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-10.xlsx
+++ b/output/2024-07-10.xlsx
@@ -640,13 +640,13 @@
         <v>30</v>
       </c>
       <c r="J14" t="n">
-        <v>-61.7</v>
+        <v>-56.37</v>
       </c>
       <c r="K14" t="n">
-        <v>-44.6</v>
+        <v>-40.74</v>
       </c>
       <c r="L14" t="n">
-        <v>76.13</v>
+        <v>69.55</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>30</v>
       </c>
       <c r="J15" t="n">
-        <v>163.93</v>
+        <v>100.73</v>
       </c>
       <c r="K15" t="n">
-        <v>131.99</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>210.47</v>
+        <v>129.32</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>-74.06999999999999</v>
+        <v>-63.89</v>
       </c>
       <c r="K16" t="n">
-        <v>-13.32</v>
+        <v>-11.49</v>
       </c>
       <c r="L16" t="n">
-        <v>75.26000000000001</v>
+        <v>64.91</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>-120.54</v>
+        <v>-110.25</v>
       </c>
       <c r="K17" t="n">
-        <v>-73.43000000000001</v>
+        <v>-67.17</v>
       </c>
       <c r="L17" t="n">
-        <v>141.14</v>
+        <v>129.1</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>-73.38</v>
+        <v>-72.36</v>
       </c>
       <c r="K18" t="n">
-        <v>88.95</v>
+        <v>87.70999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>115.31</v>
+        <v>113.7</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>29</v>
       </c>
       <c r="J19" t="n">
-        <v>-5.21</v>
+        <v>-5.36</v>
       </c>
       <c r="K19" t="n">
-        <v>-63.46</v>
+        <v>-65.23999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>63.68</v>
+        <v>65.45999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>-169.42</v>
+        <v>-211.61</v>
       </c>
       <c r="K20" t="n">
-        <v>-81.59999999999999</v>
+        <v>-101.91</v>
       </c>
       <c r="L20" t="n">
-        <v>188.05</v>
+        <v>234.87</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>27</v>
       </c>
       <c r="J21" t="n">
-        <v>54.56</v>
+        <v>58.86</v>
       </c>
       <c r="K21" t="n">
-        <v>-127.67</v>
+        <v>-137.74</v>
       </c>
       <c r="L21" t="n">
-        <v>138.84</v>
+        <v>149.79</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>30</v>
       </c>
       <c r="J22" t="n">
-        <v>-56.23</v>
+        <v>-61.13</v>
       </c>
       <c r="K22" t="n">
-        <v>-98.67</v>
+        <v>-107.25</v>
       </c>
       <c r="L22" t="n">
-        <v>113.57</v>
+        <v>123.45</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>30</v>
       </c>
       <c r="J23" t="n">
-        <v>189.67</v>
+        <v>200.41</v>
       </c>
       <c r="K23" t="n">
-        <v>-105.88</v>
+        <v>-111.88</v>
       </c>
       <c r="L23" t="n">
-        <v>217.22</v>
+        <v>229.53</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>28</v>
       </c>
       <c r="J24" t="n">
-        <v>213.3</v>
+        <v>211.13</v>
       </c>
       <c r="K24" t="n">
-        <v>188.6</v>
+        <v>186.69</v>
       </c>
       <c r="L24" t="n">
-        <v>284.72</v>
+        <v>281.83</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>-308.83</v>
+        <v>-300.1</v>
       </c>
       <c r="K25" t="n">
-        <v>-153.85</v>
+        <v>-149.5</v>
       </c>
       <c r="L25" t="n">
-        <v>345.03</v>
+        <v>335.28</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>30</v>
       </c>
       <c r="J26" t="n">
-        <v>275.44</v>
+        <v>264.03</v>
       </c>
       <c r="K26" t="n">
-        <v>172.67</v>
+        <v>165.52</v>
       </c>
       <c r="L26" t="n">
-        <v>325.09</v>
+        <v>311.62</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>-12.99</v>
+        <v>-23.42</v>
       </c>
       <c r="K27" t="n">
-        <v>-201.98</v>
+        <v>-364.22</v>
       </c>
       <c r="L27" t="n">
-        <v>202.4</v>
+        <v>364.97</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>29</v>
       </c>
       <c r="J28" t="n">
-        <v>-174.52</v>
+        <v>-163.12</v>
       </c>
       <c r="K28" t="n">
-        <v>365.13</v>
+        <v>341.27</v>
       </c>
       <c r="L28" t="n">
-        <v>404.69</v>
+        <v>378.25</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>-139.62</v>
+        <v>-102.08</v>
       </c>
       <c r="K29" t="n">
-        <v>4.12</v>
+        <v>3.01</v>
       </c>
       <c r="L29" t="n">
-        <v>139.68</v>
+        <v>102.13</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>29</v>
       </c>
       <c r="J30" t="n">
-        <v>-7.03</v>
+        <v>-6.36</v>
       </c>
       <c r="K30" t="n">
-        <v>-85.81999999999999</v>
+        <v>-77.63</v>
       </c>
       <c r="L30" t="n">
-        <v>86.11</v>
+        <v>77.89</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>11.91</v>
+        <v>11.86</v>
       </c>
       <c r="K31" t="n">
-        <v>-100.08</v>
+        <v>-99.69</v>
       </c>
       <c r="L31" t="n">
-        <v>100.78</v>
+        <v>100.4</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>29</v>
       </c>
       <c r="J32" t="n">
-        <v>-35.19</v>
+        <v>-41.19</v>
       </c>
       <c r="K32" t="n">
-        <v>-52.94</v>
+        <v>-61.97</v>
       </c>
       <c r="L32" t="n">
-        <v>63.57</v>
+        <v>74.42</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>29</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.5</v>
+        <v>-1.23</v>
       </c>
       <c r="K33" t="n">
-        <v>190.71</v>
+        <v>155.9</v>
       </c>
       <c r="L33" t="n">
-        <v>190.71</v>
+        <v>155.91</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>27</v>
       </c>
       <c r="J34" t="n">
-        <v>99.13</v>
+        <v>86.86</v>
       </c>
       <c r="K34" t="n">
-        <v>45.95</v>
+        <v>40.26</v>
       </c>
       <c r="L34" t="n">
-        <v>109.26</v>
+        <v>95.73999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>25</v>
       </c>
       <c r="J35" t="n">
-        <v>-229.54</v>
+        <v>-241.11</v>
       </c>
       <c r="K35" t="n">
-        <v>53.27</v>
+        <v>55.95</v>
       </c>
       <c r="L35" t="n">
-        <v>235.64</v>
+        <v>247.52</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>344.2</v>
+        <v>300.89</v>
       </c>
       <c r="K36" t="n">
-        <v>143.5</v>
+        <v>125.44</v>
       </c>
       <c r="L36" t="n">
-        <v>372.91</v>
+        <v>325.99</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>24</v>
       </c>
       <c r="J37" t="n">
-        <v>-498.32</v>
+        <v>-449.41</v>
       </c>
       <c r="K37" t="n">
-        <v>263.39</v>
+        <v>237.53</v>
       </c>
       <c r="L37" t="n">
-        <v>563.65</v>
+        <v>508.32</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>28</v>
       </c>
       <c r="J38" t="n">
-        <v>101.97</v>
+        <v>98.76000000000001</v>
       </c>
       <c r="K38" t="n">
-        <v>-309.23</v>
+        <v>-299.49</v>
       </c>
       <c r="L38" t="n">
-        <v>325.61</v>
+        <v>315.36</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>28</v>
       </c>
       <c r="J39" t="n">
-        <v>-111</v>
+        <v>-135.68</v>
       </c>
       <c r="K39" t="n">
-        <v>125.87</v>
+        <v>153.85</v>
       </c>
       <c r="L39" t="n">
-        <v>167.82</v>
+        <v>205.14</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>25</v>
       </c>
       <c r="J40" t="n">
-        <v>334.82</v>
+        <v>307.75</v>
       </c>
       <c r="K40" t="n">
-        <v>368.09</v>
+        <v>338.33</v>
       </c>
       <c r="L40" t="n">
-        <v>497.59</v>
+        <v>457.35</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>24</v>
       </c>
       <c r="J41" t="n">
-        <v>-194.74</v>
+        <v>-331.48</v>
       </c>
       <c r="K41" t="n">
-        <v>40.52</v>
+        <v>68.98</v>
       </c>
       <c r="L41" t="n">
-        <v>198.91</v>
+        <v>338.58</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>27</v>
       </c>
       <c r="J42" t="n">
-        <v>217.59</v>
+        <v>258.34</v>
       </c>
       <c r="K42" t="n">
-        <v>249.09</v>
+        <v>295.74</v>
       </c>
       <c r="L42" t="n">
-        <v>330.75</v>
+        <v>392.68</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>30</v>
       </c>
       <c r="J43" t="n">
-        <v>-283.15</v>
+        <v>-246.14</v>
       </c>
       <c r="K43" t="n">
-        <v>402.61</v>
+        <v>349.98</v>
       </c>
       <c r="L43" t="n">
-        <v>492.21</v>
+        <v>427.87</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>29</v>
       </c>
       <c r="J44" t="n">
-        <v>190.28</v>
+        <v>123.86</v>
       </c>
       <c r="K44" t="n">
-        <v>-153.31</v>
+        <v>-99.79000000000001</v>
       </c>
       <c r="L44" t="n">
-        <v>244.36</v>
+        <v>159.06</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>28</v>
       </c>
       <c r="J45" t="n">
-        <v>-215.58</v>
+        <v>-136.05</v>
       </c>
       <c r="K45" t="n">
-        <v>-101.9</v>
+        <v>-64.31</v>
       </c>
       <c r="L45" t="n">
-        <v>238.45</v>
+        <v>150.49</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>152.21</v>
+        <v>119.97</v>
       </c>
       <c r="K46" t="n">
-        <v>188.31</v>
+        <v>148.42</v>
       </c>
       <c r="L46" t="n">
-        <v>242.13</v>
+        <v>190.84</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>29</v>
       </c>
       <c r="J47" t="n">
-        <v>6.78</v>
+        <v>14.07</v>
       </c>
       <c r="K47" t="n">
-        <v>32.38</v>
+        <v>67.22</v>
       </c>
       <c r="L47" t="n">
-        <v>33.08</v>
+        <v>68.68000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>207.8</v>
+        <v>160.63</v>
       </c>
       <c r="K48" t="n">
-        <v>-237.64</v>
+        <v>-183.7</v>
       </c>
       <c r="L48" t="n">
-        <v>315.68</v>
+        <v>244.02</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>-92.34999999999999</v>
+        <v>-111.25</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.3</v>
+        <v>-0.37</v>
       </c>
       <c r="L49" t="n">
-        <v>92.34999999999999</v>
+        <v>111.25</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>28</v>
       </c>
       <c r="J50" t="n">
-        <v>-282.56</v>
+        <v>-235.01</v>
       </c>
       <c r="K50" t="n">
-        <v>73.83</v>
+        <v>61.4</v>
       </c>
       <c r="L50" t="n">
-        <v>292.05</v>
+        <v>242.9</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>29</v>
       </c>
       <c r="J51" t="n">
-        <v>30.7</v>
+        <v>26.42</v>
       </c>
       <c r="K51" t="n">
-        <v>-243.85</v>
+        <v>-209.86</v>
       </c>
       <c r="L51" t="n">
-        <v>245.78</v>
+        <v>211.51</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>28</v>
       </c>
       <c r="J52" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="K52" t="n">
-        <v>-194.84</v>
+        <v>-182.71</v>
       </c>
       <c r="L52" t="n">
-        <v>194.85</v>
+        <v>182.71</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>30</v>
       </c>
       <c r="J53" t="n">
-        <v>148.21</v>
+        <v>146.57</v>
       </c>
       <c r="K53" t="n">
-        <v>251.23</v>
+        <v>248.45</v>
       </c>
       <c r="L53" t="n">
-        <v>291.69</v>
+        <v>288.46</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>39.03</v>
+        <v>80.18000000000001</v>
       </c>
       <c r="K54" t="n">
-        <v>97.93000000000001</v>
+        <v>201.18</v>
       </c>
       <c r="L54" t="n">
-        <v>105.42</v>
+        <v>216.57</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>-143.53</v>
+        <v>-146.92</v>
       </c>
       <c r="K55" t="n">
-        <v>-387.63</v>
+        <v>-396.79</v>
       </c>
       <c r="L55" t="n">
-        <v>413.35</v>
+        <v>423.12</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>29</v>
       </c>
       <c r="J56" t="n">
-        <v>-134.06</v>
+        <v>-143.5</v>
       </c>
       <c r="K56" t="n">
-        <v>-349.3</v>
+        <v>-373.89</v>
       </c>
       <c r="L56" t="n">
-        <v>374.14</v>
+        <v>400.48</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>29</v>
       </c>
       <c r="J57" t="n">
-        <v>239.17</v>
+        <v>306.3</v>
       </c>
       <c r="K57" t="n">
-        <v>-48.73</v>
+        <v>-62.41</v>
       </c>
       <c r="L57" t="n">
-        <v>244.09</v>
+        <v>312.59</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>26</v>
       </c>
       <c r="J58" t="n">
-        <v>411.09</v>
+        <v>424.82</v>
       </c>
       <c r="K58" t="n">
-        <v>-367.46</v>
+        <v>-379.73</v>
       </c>
       <c r="L58" t="n">
-        <v>551.39</v>
+        <v>569.8</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>48.37</v>
+        <v>41.69</v>
       </c>
       <c r="K59" t="n">
-        <v>-89.76000000000001</v>
+        <v>-77.36</v>
       </c>
       <c r="L59" t="n">
-        <v>101.96</v>
+        <v>87.87</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>29</v>
       </c>
       <c r="J60" t="n">
-        <v>60.88</v>
+        <v>65</v>
       </c>
       <c r="K60" t="n">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="L60" t="n">
-        <v>60.89</v>
+        <v>65.02</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>29</v>
       </c>
       <c r="J61" t="n">
-        <v>-78.17</v>
+        <v>-76.8</v>
       </c>
       <c r="K61" t="n">
-        <v>-27.24</v>
+        <v>-26.76</v>
       </c>
       <c r="L61" t="n">
-        <v>82.78</v>
+        <v>81.33</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>-50.54</v>
+        <v>-58.12</v>
       </c>
       <c r="K62" t="n">
-        <v>82.2</v>
+        <v>94.53</v>
       </c>
       <c r="L62" t="n">
-        <v>96.48999999999999</v>
+        <v>110.97</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>29</v>
       </c>
       <c r="J63" t="n">
-        <v>3.24</v>
+        <v>2.7</v>
       </c>
       <c r="K63" t="n">
-        <v>141.47</v>
+        <v>118.16</v>
       </c>
       <c r="L63" t="n">
-        <v>141.51</v>
+        <v>118.19</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>28</v>
       </c>
       <c r="J64" t="n">
-        <v>-38.05</v>
+        <v>-28.39</v>
       </c>
       <c r="K64" t="n">
-        <v>-274.05</v>
+        <v>-204.49</v>
       </c>
       <c r="L64" t="n">
-        <v>276.68</v>
+        <v>206.45</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>27</v>
       </c>
       <c r="J65" t="n">
-        <v>-154.53</v>
+        <v>-160.51</v>
       </c>
       <c r="K65" t="n">
-        <v>59.17</v>
+        <v>61.46</v>
       </c>
       <c r="L65" t="n">
-        <v>165.47</v>
+        <v>171.88</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-140.36</v>
+        <v>-152.89</v>
       </c>
       <c r="K66" t="n">
-        <v>-135.14</v>
+        <v>-147.2</v>
       </c>
       <c r="L66" t="n">
-        <v>194.85</v>
+        <v>212.23</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>27</v>
       </c>
       <c r="J67" t="n">
-        <v>237.96</v>
+        <v>242.11</v>
       </c>
       <c r="K67" t="n">
-        <v>-138.66</v>
+        <v>-141.08</v>
       </c>
       <c r="L67" t="n">
-        <v>275.41</v>
+        <v>280.22</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>220.19</v>
+        <v>309.64</v>
       </c>
       <c r="K68" t="n">
-        <v>-14.11</v>
+        <v>-19.85</v>
       </c>
       <c r="L68" t="n">
-        <v>220.64</v>
+        <v>310.28</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>-54.11</v>
+        <v>-107.4</v>
       </c>
       <c r="K69" t="n">
-        <v>77.34999999999999</v>
+        <v>153.54</v>
       </c>
       <c r="L69" t="n">
-        <v>94.40000000000001</v>
+        <v>187.38</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>28</v>
       </c>
       <c r="J70" t="n">
-        <v>267.95</v>
+        <v>290.23</v>
       </c>
       <c r="K70" t="n">
-        <v>424.11</v>
+        <v>459.37</v>
       </c>
       <c r="L70" t="n">
-        <v>501.66</v>
+        <v>543.37</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>-125.9</v>
+        <v>-138.64</v>
       </c>
       <c r="K71" t="n">
-        <v>-653.12</v>
+        <v>-719.17</v>
       </c>
       <c r="L71" t="n">
-        <v>665.15</v>
+        <v>732.41</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>24</v>
       </c>
       <c r="J72" t="n">
-        <v>-444.35</v>
+        <v>-573.65</v>
       </c>
       <c r="K72" t="n">
-        <v>140.74</v>
+        <v>181.69</v>
       </c>
       <c r="L72" t="n">
-        <v>466.11</v>
+        <v>601.74</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>30</v>
       </c>
       <c r="J73" t="n">
-        <v>196.76</v>
+        <v>172.07</v>
       </c>
       <c r="K73" t="n">
-        <v>575.9400000000001</v>
+        <v>503.67</v>
       </c>
       <c r="L73" t="n">
-        <v>608.62</v>
+        <v>532.25</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>43.8</v>
+        <v>46.47</v>
       </c>
       <c r="K74" t="n">
-        <v>-62.82</v>
+        <v>-66.65000000000001</v>
       </c>
       <c r="L74" t="n">
-        <v>76.58</v>
+        <v>81.25</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>171.89</v>
+        <v>147.04</v>
       </c>
       <c r="K75" t="n">
-        <v>37.09</v>
+        <v>31.72</v>
       </c>
       <c r="L75" t="n">
-        <v>175.85</v>
+        <v>150.43</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>28</v>
       </c>
       <c r="J76" t="n">
-        <v>-139.46</v>
+        <v>-107.63</v>
       </c>
       <c r="K76" t="n">
-        <v>-99.62</v>
+        <v>-76.89</v>
       </c>
       <c r="L76" t="n">
-        <v>171.39</v>
+        <v>132.27</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>26</v>
       </c>
       <c r="J77" t="n">
-        <v>-152.42</v>
+        <v>-134.59</v>
       </c>
       <c r="K77" t="n">
-        <v>33.39</v>
+        <v>29.48</v>
       </c>
       <c r="L77" t="n">
-        <v>156.03</v>
+        <v>137.78</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>29</v>
       </c>
       <c r="J78" t="n">
-        <v>-82.43000000000001</v>
+        <v>-89.45</v>
       </c>
       <c r="K78" t="n">
-        <v>72.18000000000001</v>
+        <v>78.31999999999999</v>
       </c>
       <c r="L78" t="n">
-        <v>109.57</v>
+        <v>118.89</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>-93.12</v>
+        <v>-109.03</v>
       </c>
       <c r="K79" t="n">
-        <v>-19.27</v>
+        <v>-22.56</v>
       </c>
       <c r="L79" t="n">
-        <v>95.09</v>
+        <v>111.34</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>-279.06</v>
+        <v>-241.25</v>
       </c>
       <c r="K80" t="n">
-        <v>-199.7</v>
+        <v>-172.64</v>
       </c>
       <c r="L80" t="n">
-        <v>343.15</v>
+        <v>296.66</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>153.71</v>
+        <v>182.55</v>
       </c>
       <c r="K81" t="n">
-        <v>-21.76</v>
+        <v>-25.84</v>
       </c>
       <c r="L81" t="n">
-        <v>155.25</v>
+        <v>184.37</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>26</v>
       </c>
       <c r="J82" t="n">
-        <v>-77.95999999999999</v>
+        <v>-114.46</v>
       </c>
       <c r="K82" t="n">
-        <v>94.94</v>
+        <v>139.39</v>
       </c>
       <c r="L82" t="n">
-        <v>122.85</v>
+        <v>180.37</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>30</v>
       </c>
       <c r="J83" t="n">
-        <v>222.72</v>
+        <v>193.96</v>
       </c>
       <c r="K83" t="n">
-        <v>226.43</v>
+        <v>197.19</v>
       </c>
       <c r="L83" t="n">
-        <v>317.61</v>
+        <v>276.6</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>29</v>
       </c>
       <c r="J84" t="n">
-        <v>-216.26</v>
+        <v>-249.91</v>
       </c>
       <c r="K84" t="n">
-        <v>-40.53</v>
+        <v>-46.83</v>
       </c>
       <c r="L84" t="n">
-        <v>220.03</v>
+        <v>254.26</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>-218.77</v>
+        <v>-244.29</v>
       </c>
       <c r="K85" t="n">
-        <v>-296.84</v>
+        <v>-331.46</v>
       </c>
       <c r="L85" t="n">
-        <v>368.75</v>
+        <v>411.76</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>347.41</v>
+        <v>365.76</v>
       </c>
       <c r="K86" t="n">
-        <v>546.66</v>
+        <v>575.54</v>
       </c>
       <c r="L86" t="n">
-        <v>647.71</v>
+        <v>681.9299999999999</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>-81.12</v>
+        <v>-126.37</v>
       </c>
       <c r="K87" t="n">
-        <v>199.55</v>
+        <v>310.87</v>
       </c>
       <c r="L87" t="n">
-        <v>215.4</v>
+        <v>335.58</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>28</v>
       </c>
       <c r="J88" t="n">
-        <v>309.11</v>
+        <v>356.26</v>
       </c>
       <c r="K88" t="n">
-        <v>208.26</v>
+        <v>240.03</v>
       </c>
       <c r="L88" t="n">
-        <v>372.72</v>
+        <v>429.57</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-10.xlsx
+++ b/output/2024-07-10.xlsx
@@ -640,13 +640,13 @@
         <v>30</v>
       </c>
       <c r="J14" t="n">
-        <v>-56.37</v>
+        <v>-60.84</v>
       </c>
       <c r="K14" t="n">
-        <v>-40.74</v>
+        <v>-43.98</v>
       </c>
       <c r="L14" t="n">
-        <v>69.55</v>
+        <v>75.08</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>30</v>
       </c>
       <c r="J15" t="n">
-        <v>100.73</v>
+        <v>111.13</v>
       </c>
       <c r="K15" t="n">
-        <v>81.09999999999999</v>
+        <v>89.48</v>
       </c>
       <c r="L15" t="n">
-        <v>129.32</v>
+        <v>142.68</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>-63.89</v>
+        <v>-60.18</v>
       </c>
       <c r="K16" t="n">
-        <v>-11.49</v>
+        <v>-10.82</v>
       </c>
       <c r="L16" t="n">
-        <v>64.91</v>
+        <v>61.14</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>-110.25</v>
+        <v>-90.28</v>
       </c>
       <c r="K17" t="n">
-        <v>-67.17</v>
+        <v>-55</v>
       </c>
       <c r="L17" t="n">
-        <v>129.1</v>
+        <v>105.72</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>-72.36</v>
+        <v>-62.2</v>
       </c>
       <c r="K18" t="n">
-        <v>87.70999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>113.7</v>
+        <v>97.75</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>29</v>
       </c>
       <c r="J19" t="n">
-        <v>-5.36</v>
+        <v>-5.45</v>
       </c>
       <c r="K19" t="n">
-        <v>-65.23999999999999</v>
+        <v>-66.36</v>
       </c>
       <c r="L19" t="n">
-        <v>65.45999999999999</v>
+        <v>66.59</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>-211.61</v>
+        <v>-140.66</v>
       </c>
       <c r="K20" t="n">
-        <v>-101.91</v>
+        <v>-67.73999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>234.87</v>
+        <v>156.12</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>27</v>
       </c>
       <c r="J21" t="n">
-        <v>58.86</v>
+        <v>46.38</v>
       </c>
       <c r="K21" t="n">
-        <v>-137.74</v>
+        <v>-108.53</v>
       </c>
       <c r="L21" t="n">
-        <v>149.79</v>
+        <v>118.03</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>30</v>
       </c>
       <c r="J22" t="n">
-        <v>-61.13</v>
+        <v>-54.56</v>
       </c>
       <c r="K22" t="n">
-        <v>-107.25</v>
+        <v>-95.73</v>
       </c>
       <c r="L22" t="n">
-        <v>123.45</v>
+        <v>110.19</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>30</v>
       </c>
       <c r="J23" t="n">
-        <v>200.41</v>
+        <v>154.48</v>
       </c>
       <c r="K23" t="n">
-        <v>-111.88</v>
+        <v>-86.23999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>229.53</v>
+        <v>176.92</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>28</v>
       </c>
       <c r="J24" t="n">
-        <v>211.13</v>
+        <v>150.1</v>
       </c>
       <c r="K24" t="n">
-        <v>186.69</v>
+        <v>132.72</v>
       </c>
       <c r="L24" t="n">
-        <v>281.83</v>
+        <v>200.37</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>-300.1</v>
+        <v>-203.83</v>
       </c>
       <c r="K25" t="n">
-        <v>-149.5</v>
+        <v>-101.54</v>
       </c>
       <c r="L25" t="n">
-        <v>335.28</v>
+        <v>227.72</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>30</v>
       </c>
       <c r="J26" t="n">
-        <v>264.03</v>
+        <v>193.04</v>
       </c>
       <c r="K26" t="n">
-        <v>165.52</v>
+        <v>121.01</v>
       </c>
       <c r="L26" t="n">
-        <v>311.62</v>
+        <v>227.83</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>-23.42</v>
+        <v>-12.59</v>
       </c>
       <c r="K27" t="n">
-        <v>-364.22</v>
+        <v>-195.82</v>
       </c>
       <c r="L27" t="n">
-        <v>364.97</v>
+        <v>196.23</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>29</v>
       </c>
       <c r="J28" t="n">
-        <v>-163.12</v>
+        <v>-113.14</v>
       </c>
       <c r="K28" t="n">
-        <v>341.27</v>
+        <v>236.72</v>
       </c>
       <c r="L28" t="n">
-        <v>378.25</v>
+        <v>262.37</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>-102.08</v>
+        <v>-97.73</v>
       </c>
       <c r="K29" t="n">
-        <v>3.01</v>
+        <v>2.88</v>
       </c>
       <c r="L29" t="n">
-        <v>102.13</v>
+        <v>97.78</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>29</v>
       </c>
       <c r="J30" t="n">
-        <v>-6.36</v>
+        <v>-6.54</v>
       </c>
       <c r="K30" t="n">
-        <v>-77.63</v>
+        <v>-79.79000000000001</v>
       </c>
       <c r="L30" t="n">
-        <v>77.89</v>
+        <v>80.05</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>11.86</v>
+        <v>10.29</v>
       </c>
       <c r="K31" t="n">
-        <v>-99.69</v>
+        <v>-86.45999999999999</v>
       </c>
       <c r="L31" t="n">
-        <v>100.4</v>
+        <v>87.06999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>29</v>
       </c>
       <c r="J32" t="n">
-        <v>-41.19</v>
+        <v>-40.22</v>
       </c>
       <c r="K32" t="n">
-        <v>-61.97</v>
+        <v>-60.51</v>
       </c>
       <c r="L32" t="n">
-        <v>74.42</v>
+        <v>72.66</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>29</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.23</v>
+        <v>-1.16</v>
       </c>
       <c r="K33" t="n">
-        <v>155.9</v>
+        <v>147.01</v>
       </c>
       <c r="L33" t="n">
-        <v>155.91</v>
+        <v>147.01</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>27</v>
       </c>
       <c r="J34" t="n">
-        <v>86.86</v>
+        <v>80.79000000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>40.26</v>
+        <v>37.45</v>
       </c>
       <c r="L34" t="n">
-        <v>95.73999999999999</v>
+        <v>89.05</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>25</v>
       </c>
       <c r="J35" t="n">
-        <v>-241.11</v>
+        <v>-168.99</v>
       </c>
       <c r="K35" t="n">
-        <v>55.95</v>
+        <v>39.22</v>
       </c>
       <c r="L35" t="n">
-        <v>247.52</v>
+        <v>173.48</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>300.89</v>
+        <v>209.6</v>
       </c>
       <c r="K36" t="n">
-        <v>125.44</v>
+        <v>87.39</v>
       </c>
       <c r="L36" t="n">
-        <v>325.99</v>
+        <v>227.09</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>24</v>
       </c>
       <c r="J37" t="n">
-        <v>-449.41</v>
+        <v>-297.42</v>
       </c>
       <c r="K37" t="n">
-        <v>237.53</v>
+        <v>157.2</v>
       </c>
       <c r="L37" t="n">
-        <v>508.32</v>
+        <v>336.41</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>28</v>
       </c>
       <c r="J38" t="n">
-        <v>98.76000000000001</v>
+        <v>69.68000000000001</v>
       </c>
       <c r="K38" t="n">
-        <v>-299.49</v>
+        <v>-211.29</v>
       </c>
       <c r="L38" t="n">
-        <v>315.36</v>
+        <v>222.48</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>28</v>
       </c>
       <c r="J39" t="n">
-        <v>-135.68</v>
+        <v>-96.72</v>
       </c>
       <c r="K39" t="n">
-        <v>153.85</v>
+        <v>109.67</v>
       </c>
       <c r="L39" t="n">
-        <v>205.14</v>
+        <v>146.23</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>25</v>
       </c>
       <c r="J40" t="n">
-        <v>307.75</v>
+        <v>195.02</v>
       </c>
       <c r="K40" t="n">
-        <v>338.33</v>
+        <v>214.4</v>
       </c>
       <c r="L40" t="n">
-        <v>457.35</v>
+        <v>289.83</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>24</v>
       </c>
       <c r="J41" t="n">
-        <v>-331.48</v>
+        <v>-181.72</v>
       </c>
       <c r="K41" t="n">
-        <v>68.98</v>
+        <v>37.81</v>
       </c>
       <c r="L41" t="n">
-        <v>338.58</v>
+        <v>185.61</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>27</v>
       </c>
       <c r="J42" t="n">
-        <v>258.34</v>
+        <v>159.01</v>
       </c>
       <c r="K42" t="n">
-        <v>295.74</v>
+        <v>182.03</v>
       </c>
       <c r="L42" t="n">
-        <v>392.68</v>
+        <v>241.7</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>30</v>
       </c>
       <c r="J43" t="n">
-        <v>-246.14</v>
+        <v>-177.62</v>
       </c>
       <c r="K43" t="n">
-        <v>349.98</v>
+        <v>252.56</v>
       </c>
       <c r="L43" t="n">
-        <v>427.87</v>
+        <v>308.76</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>29</v>
       </c>
       <c r="J44" t="n">
-        <v>123.86</v>
+        <v>127.3</v>
       </c>
       <c r="K44" t="n">
-        <v>-99.79000000000001</v>
+        <v>-102.57</v>
       </c>
       <c r="L44" t="n">
-        <v>159.06</v>
+        <v>163.48</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>28</v>
       </c>
       <c r="J45" t="n">
-        <v>-136.05</v>
+        <v>-137.9</v>
       </c>
       <c r="K45" t="n">
-        <v>-64.31</v>
+        <v>-65.18000000000001</v>
       </c>
       <c r="L45" t="n">
-        <v>150.49</v>
+        <v>152.52</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>119.97</v>
+        <v>104.76</v>
       </c>
       <c r="K46" t="n">
-        <v>148.42</v>
+        <v>129.61</v>
       </c>
       <c r="L46" t="n">
-        <v>190.84</v>
+        <v>166.65</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>29</v>
       </c>
       <c r="J47" t="n">
-        <v>14.07</v>
+        <v>13.27</v>
       </c>
       <c r="K47" t="n">
-        <v>67.22</v>
+        <v>63.39</v>
       </c>
       <c r="L47" t="n">
-        <v>68.68000000000001</v>
+        <v>64.76000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>160.63</v>
+        <v>134.78</v>
       </c>
       <c r="K48" t="n">
-        <v>-183.7</v>
+        <v>-154.13</v>
       </c>
       <c r="L48" t="n">
-        <v>244.02</v>
+        <v>204.75</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>-111.25</v>
+        <v>-88.56</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.37</v>
+        <v>-0.29</v>
       </c>
       <c r="L49" t="n">
-        <v>111.25</v>
+        <v>88.56999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>28</v>
       </c>
       <c r="J50" t="n">
-        <v>-235.01</v>
+        <v>-190.35</v>
       </c>
       <c r="K50" t="n">
-        <v>61.4</v>
+        <v>49.74</v>
       </c>
       <c r="L50" t="n">
-        <v>242.9</v>
+        <v>196.74</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>29</v>
       </c>
       <c r="J51" t="n">
-        <v>26.42</v>
+        <v>22.25</v>
       </c>
       <c r="K51" t="n">
-        <v>-209.86</v>
+        <v>-176.69</v>
       </c>
       <c r="L51" t="n">
-        <v>211.51</v>
+        <v>178.09</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>28</v>
       </c>
       <c r="J52" t="n">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="K52" t="n">
-        <v>-182.71</v>
+        <v>-148.91</v>
       </c>
       <c r="L52" t="n">
-        <v>182.71</v>
+        <v>148.91</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>30</v>
       </c>
       <c r="J53" t="n">
-        <v>146.57</v>
+        <v>111.71</v>
       </c>
       <c r="K53" t="n">
-        <v>248.45</v>
+        <v>189.35</v>
       </c>
       <c r="L53" t="n">
-        <v>288.46</v>
+        <v>219.84</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>80.18000000000001</v>
+        <v>50.4</v>
       </c>
       <c r="K54" t="n">
-        <v>201.18</v>
+        <v>126.45</v>
       </c>
       <c r="L54" t="n">
-        <v>216.57</v>
+        <v>136.13</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>-146.92</v>
+        <v>-91.23999999999999</v>
       </c>
       <c r="K55" t="n">
-        <v>-396.79</v>
+        <v>-246.41</v>
       </c>
       <c r="L55" t="n">
-        <v>423.12</v>
+        <v>262.76</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>29</v>
       </c>
       <c r="J56" t="n">
-        <v>-143.5</v>
+        <v>-96.16</v>
       </c>
       <c r="K56" t="n">
-        <v>-373.89</v>
+        <v>-250.56</v>
       </c>
       <c r="L56" t="n">
-        <v>400.48</v>
+        <v>268.38</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>29</v>
       </c>
       <c r="J57" t="n">
-        <v>306.3</v>
+        <v>205.51</v>
       </c>
       <c r="K57" t="n">
-        <v>-62.41</v>
+        <v>-41.87</v>
       </c>
       <c r="L57" t="n">
-        <v>312.59</v>
+        <v>209.73</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>26</v>
       </c>
       <c r="J58" t="n">
-        <v>424.82</v>
+        <v>251.51</v>
       </c>
       <c r="K58" t="n">
-        <v>-379.73</v>
+        <v>-224.81</v>
       </c>
       <c r="L58" t="n">
-        <v>569.8</v>
+        <v>337.34</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>41.69</v>
+        <v>38.04</v>
       </c>
       <c r="K59" t="n">
-        <v>-77.36</v>
+        <v>-70.59</v>
       </c>
       <c r="L59" t="n">
-        <v>87.87</v>
+        <v>80.19</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>29</v>
       </c>
       <c r="J60" t="n">
-        <v>65</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="K60" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="L60" t="n">
-        <v>65.02</v>
+        <v>66.67</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>29</v>
       </c>
       <c r="J61" t="n">
-        <v>-76.8</v>
+        <v>-77.13</v>
       </c>
       <c r="K61" t="n">
-        <v>-26.76</v>
+        <v>-26.87</v>
       </c>
       <c r="L61" t="n">
-        <v>81.33</v>
+        <v>81.67</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>-58.12</v>
+        <v>-48.69</v>
       </c>
       <c r="K62" t="n">
-        <v>94.53</v>
+        <v>79.2</v>
       </c>
       <c r="L62" t="n">
-        <v>110.97</v>
+        <v>92.97</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>29</v>
       </c>
       <c r="J63" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="K63" t="n">
-        <v>118.16</v>
+        <v>114.38</v>
       </c>
       <c r="L63" t="n">
-        <v>118.19</v>
+        <v>114.41</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>28</v>
       </c>
       <c r="J64" t="n">
-        <v>-28.39</v>
+        <v>-25.83</v>
       </c>
       <c r="K64" t="n">
-        <v>-204.49</v>
+        <v>-186.05</v>
       </c>
       <c r="L64" t="n">
-        <v>206.45</v>
+        <v>187.84</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>27</v>
       </c>
       <c r="J65" t="n">
-        <v>-160.51</v>
+        <v>-124.7</v>
       </c>
       <c r="K65" t="n">
-        <v>61.46</v>
+        <v>47.75</v>
       </c>
       <c r="L65" t="n">
-        <v>171.88</v>
+        <v>133.52</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-152.89</v>
+        <v>-105.82</v>
       </c>
       <c r="K66" t="n">
-        <v>-147.2</v>
+        <v>-101.88</v>
       </c>
       <c r="L66" t="n">
-        <v>212.23</v>
+        <v>146.9</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>27</v>
       </c>
       <c r="J67" t="n">
-        <v>242.11</v>
+        <v>177.58</v>
       </c>
       <c r="K67" t="n">
-        <v>-141.08</v>
+        <v>-103.48</v>
       </c>
       <c r="L67" t="n">
-        <v>280.22</v>
+        <v>205.53</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>309.64</v>
+        <v>181.9</v>
       </c>
       <c r="K68" t="n">
-        <v>-19.85</v>
+        <v>-11.66</v>
       </c>
       <c r="L68" t="n">
-        <v>310.28</v>
+        <v>182.28</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>-107.4</v>
+        <v>-66.86</v>
       </c>
       <c r="K69" t="n">
-        <v>153.54</v>
+        <v>95.59</v>
       </c>
       <c r="L69" t="n">
-        <v>187.38</v>
+        <v>116.65</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>28</v>
       </c>
       <c r="J70" t="n">
-        <v>290.23</v>
+        <v>190.66</v>
       </c>
       <c r="K70" t="n">
-        <v>459.37</v>
+        <v>301.77</v>
       </c>
       <c r="L70" t="n">
-        <v>543.37</v>
+        <v>356.95</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>-138.64</v>
+        <v>-76.48999999999999</v>
       </c>
       <c r="K71" t="n">
-        <v>-719.17</v>
+        <v>-396.8</v>
       </c>
       <c r="L71" t="n">
-        <v>732.41</v>
+        <v>404.11</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>24</v>
       </c>
       <c r="J72" t="n">
-        <v>-573.65</v>
+        <v>-304.07</v>
       </c>
       <c r="K72" t="n">
-        <v>181.69</v>
+        <v>96.31</v>
       </c>
       <c r="L72" t="n">
-        <v>601.74</v>
+        <v>318.96</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>30</v>
       </c>
       <c r="J73" t="n">
-        <v>172.07</v>
+        <v>122.07</v>
       </c>
       <c r="K73" t="n">
-        <v>503.67</v>
+        <v>357.33</v>
       </c>
       <c r="L73" t="n">
-        <v>532.25</v>
+        <v>377.6</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>46.47</v>
+        <v>42.16</v>
       </c>
       <c r="K74" t="n">
-        <v>-66.65000000000001</v>
+        <v>-60.47</v>
       </c>
       <c r="L74" t="n">
-        <v>81.25</v>
+        <v>73.72</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>147.04</v>
+        <v>122.39</v>
       </c>
       <c r="K75" t="n">
-        <v>31.72</v>
+        <v>26.4</v>
       </c>
       <c r="L75" t="n">
-        <v>150.43</v>
+        <v>125.2</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>28</v>
       </c>
       <c r="J76" t="n">
-        <v>-107.63</v>
+        <v>-103.72</v>
       </c>
       <c r="K76" t="n">
-        <v>-76.89</v>
+        <v>-74.09</v>
       </c>
       <c r="L76" t="n">
-        <v>132.27</v>
+        <v>127.47</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>26</v>
       </c>
       <c r="J77" t="n">
-        <v>-134.59</v>
+        <v>-115.59</v>
       </c>
       <c r="K77" t="n">
-        <v>29.48</v>
+        <v>25.32</v>
       </c>
       <c r="L77" t="n">
-        <v>137.78</v>
+        <v>118.33</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>29</v>
       </c>
       <c r="J78" t="n">
-        <v>-89.45</v>
+        <v>-82.43000000000001</v>
       </c>
       <c r="K78" t="n">
-        <v>78.31999999999999</v>
+        <v>72.17</v>
       </c>
       <c r="L78" t="n">
-        <v>118.89</v>
+        <v>109.56</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>-109.03</v>
+        <v>-86.72</v>
       </c>
       <c r="K79" t="n">
-        <v>-22.56</v>
+        <v>-17.95</v>
       </c>
       <c r="L79" t="n">
-        <v>111.34</v>
+        <v>88.55</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>-241.25</v>
+        <v>-178.53</v>
       </c>
       <c r="K80" t="n">
-        <v>-172.64</v>
+        <v>-127.75</v>
       </c>
       <c r="L80" t="n">
-        <v>296.66</v>
+        <v>219.53</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>182.55</v>
+        <v>126.89</v>
       </c>
       <c r="K81" t="n">
-        <v>-25.84</v>
+        <v>-17.96</v>
       </c>
       <c r="L81" t="n">
-        <v>184.37</v>
+        <v>128.16</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>26</v>
       </c>
       <c r="J82" t="n">
-        <v>-114.46</v>
+        <v>-81.17</v>
       </c>
       <c r="K82" t="n">
-        <v>139.39</v>
+        <v>98.84999999999999</v>
       </c>
       <c r="L82" t="n">
-        <v>180.37</v>
+        <v>127.91</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>30</v>
       </c>
       <c r="J83" t="n">
-        <v>193.96</v>
+        <v>152.43</v>
       </c>
       <c r="K83" t="n">
-        <v>197.19</v>
+        <v>154.97</v>
       </c>
       <c r="L83" t="n">
-        <v>276.6</v>
+        <v>217.37</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>29</v>
       </c>
       <c r="J84" t="n">
-        <v>-249.91</v>
+        <v>-180.45</v>
       </c>
       <c r="K84" t="n">
-        <v>-46.83</v>
+        <v>-33.82</v>
       </c>
       <c r="L84" t="n">
-        <v>254.26</v>
+        <v>183.6</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>-244.29</v>
+        <v>-145.06</v>
       </c>
       <c r="K85" t="n">
-        <v>-331.46</v>
+        <v>-196.83</v>
       </c>
       <c r="L85" t="n">
-        <v>411.76</v>
+        <v>244.51</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>365.76</v>
+        <v>205.68</v>
       </c>
       <c r="K86" t="n">
-        <v>575.54</v>
+        <v>323.65</v>
       </c>
       <c r="L86" t="n">
-        <v>681.9299999999999</v>
+        <v>383.48</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>-126.37</v>
+        <v>-76.09</v>
       </c>
       <c r="K87" t="n">
-        <v>310.87</v>
+        <v>187.17</v>
       </c>
       <c r="L87" t="n">
-        <v>335.58</v>
+        <v>202.05</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>28</v>
       </c>
       <c r="J88" t="n">
-        <v>356.26</v>
+        <v>224.81</v>
       </c>
       <c r="K88" t="n">
-        <v>240.03</v>
+        <v>151.47</v>
       </c>
       <c r="L88" t="n">
-        <v>429.57</v>
+        <v>271.08</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-10.xlsx
+++ b/output/2024-07-10.xlsx
@@ -640,13 +640,13 @@
         <v>30</v>
       </c>
       <c r="J14" t="n">
-        <v>-60.84</v>
+        <v>-55.26</v>
       </c>
       <c r="K14" t="n">
-        <v>-43.98</v>
+        <v>-39.94</v>
       </c>
       <c r="L14" t="n">
-        <v>75.08</v>
+        <v>68.18000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>30</v>
       </c>
       <c r="J15" t="n">
-        <v>111.13</v>
+        <v>102.4</v>
       </c>
       <c r="K15" t="n">
-        <v>89.48</v>
+        <v>82.45</v>
       </c>
       <c r="L15" t="n">
-        <v>142.68</v>
+        <v>131.47</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>-60.18</v>
+        <v>-56.94</v>
       </c>
       <c r="K16" t="n">
-        <v>-10.82</v>
+        <v>-10.24</v>
       </c>
       <c r="L16" t="n">
-        <v>61.14</v>
+        <v>57.86</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>-90.28</v>
+        <v>-88.56999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>-55</v>
+        <v>-53.96</v>
       </c>
       <c r="L17" t="n">
-        <v>105.72</v>
+        <v>103.71</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>-62.2</v>
+        <v>-59.89</v>
       </c>
       <c r="K18" t="n">
-        <v>75.40000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>97.75</v>
+        <v>94.12</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>29</v>
       </c>
       <c r="J19" t="n">
-        <v>-5.45</v>
+        <v>-5.19</v>
       </c>
       <c r="K19" t="n">
-        <v>-66.36</v>
+        <v>-63.22</v>
       </c>
       <c r="L19" t="n">
-        <v>66.59</v>
+        <v>63.43</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>-140.66</v>
+        <v>-142.15</v>
       </c>
       <c r="K20" t="n">
-        <v>-67.73999999999999</v>
+        <v>-68.45999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>156.12</v>
+        <v>157.78</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>27</v>
       </c>
       <c r="J21" t="n">
-        <v>46.38</v>
+        <v>46.2</v>
       </c>
       <c r="K21" t="n">
-        <v>-108.53</v>
+        <v>-108.11</v>
       </c>
       <c r="L21" t="n">
-        <v>118.03</v>
+        <v>117.56</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>30</v>
       </c>
       <c r="J22" t="n">
-        <v>-54.56</v>
+        <v>-53.87</v>
       </c>
       <c r="K22" t="n">
-        <v>-95.73</v>
+        <v>-94.52</v>
       </c>
       <c r="L22" t="n">
-        <v>110.19</v>
+        <v>108.79</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>30</v>
       </c>
       <c r="J23" t="n">
-        <v>154.48</v>
+        <v>154.79</v>
       </c>
       <c r="K23" t="n">
-        <v>-86.23999999999999</v>
+        <v>-86.41</v>
       </c>
       <c r="L23" t="n">
-        <v>176.92</v>
+        <v>177.27</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>28</v>
       </c>
       <c r="J24" t="n">
-        <v>150.1</v>
+        <v>151.6</v>
       </c>
       <c r="K24" t="n">
-        <v>132.72</v>
+        <v>134.05</v>
       </c>
       <c r="L24" t="n">
-        <v>200.37</v>
+        <v>202.37</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>-203.83</v>
+        <v>-209.01</v>
       </c>
       <c r="K25" t="n">
-        <v>-101.54</v>
+        <v>-104.12</v>
       </c>
       <c r="L25" t="n">
-        <v>227.72</v>
+        <v>233.51</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>30</v>
       </c>
       <c r="J26" t="n">
-        <v>193.04</v>
+        <v>198.95</v>
       </c>
       <c r="K26" t="n">
-        <v>121.01</v>
+        <v>124.72</v>
       </c>
       <c r="L26" t="n">
-        <v>227.83</v>
+        <v>234.81</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>-12.59</v>
+        <v>-13.21</v>
       </c>
       <c r="K27" t="n">
-        <v>-195.82</v>
+        <v>-205.38</v>
       </c>
       <c r="L27" t="n">
-        <v>196.23</v>
+        <v>205.8</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>29</v>
       </c>
       <c r="J28" t="n">
-        <v>-113.14</v>
+        <v>-116.35</v>
       </c>
       <c r="K28" t="n">
-        <v>236.72</v>
+        <v>243.42</v>
       </c>
       <c r="L28" t="n">
-        <v>262.37</v>
+        <v>269.8</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>-97.73</v>
+        <v>-92.03</v>
       </c>
       <c r="K29" t="n">
-        <v>2.88</v>
+        <v>2.71</v>
       </c>
       <c r="L29" t="n">
-        <v>97.78</v>
+        <v>92.06999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>29</v>
       </c>
       <c r="J30" t="n">
-        <v>-6.54</v>
+        <v>-5.98</v>
       </c>
       <c r="K30" t="n">
-        <v>-79.79000000000001</v>
+        <v>-73</v>
       </c>
       <c r="L30" t="n">
-        <v>80.05</v>
+        <v>73.25</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>10.29</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>-86.45999999999999</v>
+        <v>-81.48</v>
       </c>
       <c r="L31" t="n">
-        <v>87.06999999999999</v>
+        <v>82.05</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>29</v>
       </c>
       <c r="J32" t="n">
-        <v>-40.22</v>
+        <v>-38.67</v>
       </c>
       <c r="K32" t="n">
-        <v>-60.51</v>
+        <v>-58.18</v>
       </c>
       <c r="L32" t="n">
-        <v>72.66</v>
+        <v>69.86</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>29</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.16</v>
+        <v>-1.12</v>
       </c>
       <c r="K33" t="n">
-        <v>147.01</v>
+        <v>141.93</v>
       </c>
       <c r="L33" t="n">
-        <v>147.01</v>
+        <v>141.93</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>27</v>
       </c>
       <c r="J34" t="n">
-        <v>80.79000000000001</v>
+        <v>77.06</v>
       </c>
       <c r="K34" t="n">
-        <v>37.45</v>
+        <v>35.72</v>
       </c>
       <c r="L34" t="n">
-        <v>89.05</v>
+        <v>84.94</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>25</v>
       </c>
       <c r="J35" t="n">
-        <v>-168.99</v>
+        <v>-170.86</v>
       </c>
       <c r="K35" t="n">
-        <v>39.22</v>
+        <v>39.65</v>
       </c>
       <c r="L35" t="n">
-        <v>173.48</v>
+        <v>175.4</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>209.6</v>
+        <v>212.57</v>
       </c>
       <c r="K36" t="n">
-        <v>87.39</v>
+        <v>88.62</v>
       </c>
       <c r="L36" t="n">
-        <v>227.09</v>
+        <v>230.31</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>24</v>
       </c>
       <c r="J37" t="n">
-        <v>-297.42</v>
+        <v>-302.03</v>
       </c>
       <c r="K37" t="n">
-        <v>157.2</v>
+        <v>159.64</v>
       </c>
       <c r="L37" t="n">
-        <v>336.41</v>
+        <v>341.62</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>28</v>
       </c>
       <c r="J38" t="n">
-        <v>69.68000000000001</v>
+        <v>71.11</v>
       </c>
       <c r="K38" t="n">
-        <v>-211.29</v>
+        <v>-215.64</v>
       </c>
       <c r="L38" t="n">
-        <v>222.48</v>
+        <v>227.07</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>28</v>
       </c>
       <c r="J39" t="n">
-        <v>-96.72</v>
+        <v>-99.22</v>
       </c>
       <c r="K39" t="n">
-        <v>109.67</v>
+        <v>112.5</v>
       </c>
       <c r="L39" t="n">
-        <v>146.23</v>
+        <v>150</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>25</v>
       </c>
       <c r="J40" t="n">
-        <v>195.02</v>
+        <v>203.16</v>
       </c>
       <c r="K40" t="n">
-        <v>214.4</v>
+        <v>223.34</v>
       </c>
       <c r="L40" t="n">
-        <v>289.83</v>
+        <v>301.92</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>24</v>
       </c>
       <c r="J41" t="n">
-        <v>-181.72</v>
+        <v>-189.97</v>
       </c>
       <c r="K41" t="n">
-        <v>37.81</v>
+        <v>39.53</v>
       </c>
       <c r="L41" t="n">
-        <v>185.61</v>
+        <v>194.04</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>27</v>
       </c>
       <c r="J42" t="n">
-        <v>159.01</v>
+        <v>165.36</v>
       </c>
       <c r="K42" t="n">
-        <v>182.03</v>
+        <v>189.29</v>
       </c>
       <c r="L42" t="n">
-        <v>241.7</v>
+        <v>251.34</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>30</v>
       </c>
       <c r="J43" t="n">
-        <v>-177.62</v>
+        <v>-180.57</v>
       </c>
       <c r="K43" t="n">
-        <v>252.56</v>
+        <v>256.75</v>
       </c>
       <c r="L43" t="n">
-        <v>308.76</v>
+        <v>313.89</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>29</v>
       </c>
       <c r="J44" t="n">
-        <v>127.3</v>
+        <v>116.51</v>
       </c>
       <c r="K44" t="n">
-        <v>-102.57</v>
+        <v>-93.87</v>
       </c>
       <c r="L44" t="n">
-        <v>163.48</v>
+        <v>149.62</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>28</v>
       </c>
       <c r="J45" t="n">
-        <v>-137.9</v>
+        <v>-127.95</v>
       </c>
       <c r="K45" t="n">
-        <v>-65.18000000000001</v>
+        <v>-60.48</v>
       </c>
       <c r="L45" t="n">
-        <v>152.52</v>
+        <v>141.52</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>104.76</v>
+        <v>98.62</v>
       </c>
       <c r="K46" t="n">
-        <v>129.61</v>
+        <v>122.01</v>
       </c>
       <c r="L46" t="n">
-        <v>166.65</v>
+        <v>156.88</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>29</v>
       </c>
       <c r="J47" t="n">
-        <v>13.27</v>
+        <v>12.73</v>
       </c>
       <c r="K47" t="n">
-        <v>63.39</v>
+        <v>60.82</v>
       </c>
       <c r="L47" t="n">
-        <v>64.76000000000001</v>
+        <v>62.14</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>134.78</v>
+        <v>130.65</v>
       </c>
       <c r="K48" t="n">
-        <v>-154.13</v>
+        <v>-149.41</v>
       </c>
       <c r="L48" t="n">
-        <v>204.75</v>
+        <v>198.47</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>-88.56</v>
+        <v>-86.13</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.29</v>
+        <v>-0.28</v>
       </c>
       <c r="L49" t="n">
-        <v>88.56999999999999</v>
+        <v>86.13</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>28</v>
       </c>
       <c r="J50" t="n">
-        <v>-190.35</v>
+        <v>-188.94</v>
       </c>
       <c r="K50" t="n">
-        <v>49.74</v>
+        <v>49.37</v>
       </c>
       <c r="L50" t="n">
-        <v>196.74</v>
+        <v>195.29</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>29</v>
       </c>
       <c r="J51" t="n">
-        <v>22.25</v>
+        <v>22.03</v>
       </c>
       <c r="K51" t="n">
-        <v>-176.69</v>
+        <v>-174.94</v>
       </c>
       <c r="L51" t="n">
-        <v>178.09</v>
+        <v>176.32</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>28</v>
       </c>
       <c r="J52" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="K52" t="n">
-        <v>-148.91</v>
+        <v>-147.72</v>
       </c>
       <c r="L52" t="n">
-        <v>148.91</v>
+        <v>147.72</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>30</v>
       </c>
       <c r="J53" t="n">
-        <v>111.71</v>
+        <v>111.7</v>
       </c>
       <c r="K53" t="n">
-        <v>189.35</v>
+        <v>189.34</v>
       </c>
       <c r="L53" t="n">
-        <v>219.84</v>
+        <v>219.83</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>50.4</v>
+        <v>51.49</v>
       </c>
       <c r="K54" t="n">
-        <v>126.45</v>
+        <v>129.2</v>
       </c>
       <c r="L54" t="n">
-        <v>136.13</v>
+        <v>139.08</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>-91.23999999999999</v>
+        <v>-94.91</v>
       </c>
       <c r="K55" t="n">
-        <v>-246.41</v>
+        <v>-256.32</v>
       </c>
       <c r="L55" t="n">
-        <v>262.76</v>
+        <v>273.32</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>29</v>
       </c>
       <c r="J56" t="n">
-        <v>-96.16</v>
+        <v>-98.23999999999999</v>
       </c>
       <c r="K56" t="n">
-        <v>-250.56</v>
+        <v>-255.97</v>
       </c>
       <c r="L56" t="n">
-        <v>268.38</v>
+        <v>274.17</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>29</v>
       </c>
       <c r="J57" t="n">
-        <v>205.51</v>
+        <v>210.96</v>
       </c>
       <c r="K57" t="n">
-        <v>-41.87</v>
+        <v>-42.98</v>
       </c>
       <c r="L57" t="n">
-        <v>209.73</v>
+        <v>215.3</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>26</v>
       </c>
       <c r="J58" t="n">
-        <v>251.51</v>
+        <v>261.47</v>
       </c>
       <c r="K58" t="n">
-        <v>-224.81</v>
+        <v>-233.71</v>
       </c>
       <c r="L58" t="n">
-        <v>337.34</v>
+        <v>350.69</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>38.04</v>
+        <v>35.63</v>
       </c>
       <c r="K59" t="n">
-        <v>-70.59</v>
+        <v>-66.11</v>
       </c>
       <c r="L59" t="n">
-        <v>80.19</v>
+        <v>75.09999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>29</v>
       </c>
       <c r="J60" t="n">
-        <v>66.65000000000001</v>
+        <v>61.6</v>
       </c>
       <c r="K60" t="n">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="L60" t="n">
-        <v>66.67</v>
+        <v>61.62</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>29</v>
       </c>
       <c r="J61" t="n">
-        <v>-77.13</v>
+        <v>-70.76000000000001</v>
       </c>
       <c r="K61" t="n">
-        <v>-26.87</v>
+        <v>-24.65</v>
       </c>
       <c r="L61" t="n">
-        <v>81.67</v>
+        <v>74.93000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>-48.69</v>
+        <v>-47.49</v>
       </c>
       <c r="K62" t="n">
-        <v>79.2</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="L62" t="n">
-        <v>92.97</v>
+        <v>90.67</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>29</v>
       </c>
       <c r="J63" t="n">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="K63" t="n">
-        <v>114.38</v>
+        <v>110.17</v>
       </c>
       <c r="L63" t="n">
-        <v>114.41</v>
+        <v>110.2</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>28</v>
       </c>
       <c r="J64" t="n">
-        <v>-25.83</v>
+        <v>-24.69</v>
       </c>
       <c r="K64" t="n">
-        <v>-186.05</v>
+        <v>-177.81</v>
       </c>
       <c r="L64" t="n">
-        <v>187.84</v>
+        <v>179.51</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>27</v>
       </c>
       <c r="J65" t="n">
-        <v>-124.7</v>
+        <v>-123.63</v>
       </c>
       <c r="K65" t="n">
-        <v>47.75</v>
+        <v>47.34</v>
       </c>
       <c r="L65" t="n">
-        <v>133.52</v>
+        <v>132.38</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-105.82</v>
+        <v>-107.79</v>
       </c>
       <c r="K66" t="n">
-        <v>-101.88</v>
+        <v>-103.78</v>
       </c>
       <c r="L66" t="n">
-        <v>146.9</v>
+        <v>149.63</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>27</v>
       </c>
       <c r="J67" t="n">
-        <v>177.58</v>
+        <v>176.32</v>
       </c>
       <c r="K67" t="n">
-        <v>-103.48</v>
+        <v>-102.74</v>
       </c>
       <c r="L67" t="n">
-        <v>205.53</v>
+        <v>204.07</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>181.9</v>
+        <v>189.04</v>
       </c>
       <c r="K68" t="n">
-        <v>-11.66</v>
+        <v>-12.12</v>
       </c>
       <c r="L68" t="n">
-        <v>182.28</v>
+        <v>189.43</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>-66.86</v>
+        <v>-68.92</v>
       </c>
       <c r="K69" t="n">
-        <v>95.59</v>
+        <v>98.53</v>
       </c>
       <c r="L69" t="n">
-        <v>116.65</v>
+        <v>120.24</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>28</v>
       </c>
       <c r="J70" t="n">
-        <v>190.66</v>
+        <v>196.09</v>
       </c>
       <c r="K70" t="n">
-        <v>301.77</v>
+        <v>310.36</v>
       </c>
       <c r="L70" t="n">
-        <v>356.95</v>
+        <v>367.12</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>-76.48999999999999</v>
+        <v>-80.77</v>
       </c>
       <c r="K71" t="n">
-        <v>-396.8</v>
+        <v>-419.01</v>
       </c>
       <c r="L71" t="n">
-        <v>404.11</v>
+        <v>426.73</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>24</v>
       </c>
       <c r="J72" t="n">
-        <v>-304.07</v>
+        <v>-320.09</v>
       </c>
       <c r="K72" t="n">
-        <v>96.31</v>
+        <v>101.38</v>
       </c>
       <c r="L72" t="n">
-        <v>318.96</v>
+        <v>335.76</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>30</v>
       </c>
       <c r="J73" t="n">
-        <v>122.07</v>
+        <v>124.71</v>
       </c>
       <c r="K73" t="n">
-        <v>357.33</v>
+        <v>365.03</v>
       </c>
       <c r="L73" t="n">
-        <v>377.6</v>
+        <v>385.75</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>42.16</v>
+        <v>39.64</v>
       </c>
       <c r="K74" t="n">
-        <v>-60.47</v>
+        <v>-56.85</v>
       </c>
       <c r="L74" t="n">
-        <v>73.72</v>
+        <v>69.31</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>122.39</v>
+        <v>114.6</v>
       </c>
       <c r="K75" t="n">
-        <v>26.4</v>
+        <v>24.73</v>
       </c>
       <c r="L75" t="n">
-        <v>125.2</v>
+        <v>117.24</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>28</v>
       </c>
       <c r="J76" t="n">
-        <v>-103.72</v>
+        <v>-95.69</v>
       </c>
       <c r="K76" t="n">
-        <v>-74.09</v>
+        <v>-68.34999999999999</v>
       </c>
       <c r="L76" t="n">
-        <v>127.47</v>
+        <v>117.59</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>26</v>
       </c>
       <c r="J77" t="n">
-        <v>-115.59</v>
+        <v>-111.64</v>
       </c>
       <c r="K77" t="n">
-        <v>25.32</v>
+        <v>24.45</v>
       </c>
       <c r="L77" t="n">
-        <v>118.33</v>
+        <v>114.29</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>29</v>
       </c>
       <c r="J78" t="n">
-        <v>-82.43000000000001</v>
+        <v>-78.87</v>
       </c>
       <c r="K78" t="n">
-        <v>72.17</v>
+        <v>69.05</v>
       </c>
       <c r="L78" t="n">
-        <v>109.56</v>
+        <v>104.83</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>-86.72</v>
+        <v>-85.64</v>
       </c>
       <c r="K79" t="n">
-        <v>-17.95</v>
+        <v>-17.72</v>
       </c>
       <c r="L79" t="n">
-        <v>88.55</v>
+        <v>87.45</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>-178.53</v>
+        <v>-181.3</v>
       </c>
       <c r="K80" t="n">
-        <v>-127.75</v>
+        <v>-129.74</v>
       </c>
       <c r="L80" t="n">
-        <v>219.53</v>
+        <v>222.94</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>126.89</v>
+        <v>128.15</v>
       </c>
       <c r="K81" t="n">
-        <v>-17.96</v>
+        <v>-18.14</v>
       </c>
       <c r="L81" t="n">
-        <v>128.16</v>
+        <v>129.43</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>26</v>
       </c>
       <c r="J82" t="n">
-        <v>-81.17</v>
+        <v>-80.64</v>
       </c>
       <c r="K82" t="n">
-        <v>98.84999999999999</v>
+        <v>98.20999999999999</v>
       </c>
       <c r="L82" t="n">
-        <v>127.91</v>
+        <v>127.08</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>30</v>
       </c>
       <c r="J83" t="n">
-        <v>152.43</v>
+        <v>153.39</v>
       </c>
       <c r="K83" t="n">
-        <v>154.97</v>
+        <v>155.94</v>
       </c>
       <c r="L83" t="n">
-        <v>217.37</v>
+        <v>218.74</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>29</v>
       </c>
       <c r="J84" t="n">
-        <v>-180.45</v>
+        <v>-182.71</v>
       </c>
       <c r="K84" t="n">
-        <v>-33.82</v>
+        <v>-34.24</v>
       </c>
       <c r="L84" t="n">
-        <v>183.6</v>
+        <v>185.89</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>-145.06</v>
+        <v>-151.49</v>
       </c>
       <c r="K85" t="n">
-        <v>-196.83</v>
+        <v>-205.55</v>
       </c>
       <c r="L85" t="n">
-        <v>244.51</v>
+        <v>255.34</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>205.68</v>
+        <v>215</v>
       </c>
       <c r="K86" t="n">
-        <v>323.65</v>
+        <v>338.31</v>
       </c>
       <c r="L86" t="n">
-        <v>383.48</v>
+        <v>400.85</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>-76.09</v>
+        <v>-78.77</v>
       </c>
       <c r="K87" t="n">
-        <v>187.17</v>
+        <v>193.78</v>
       </c>
       <c r="L87" t="n">
-        <v>202.05</v>
+        <v>209.18</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>28</v>
       </c>
       <c r="J88" t="n">
-        <v>224.81</v>
+        <v>229.13</v>
       </c>
       <c r="K88" t="n">
-        <v>151.47</v>
+        <v>154.37</v>
       </c>
       <c r="L88" t="n">
-        <v>271.08</v>
+        <v>276.28</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-10.xlsx
+++ b/output/2024-07-10.xlsx
@@ -640,13 +640,13 @@
         <v>30</v>
       </c>
       <c r="J14" t="n">
-        <v>-55.26</v>
+        <v>-31.86</v>
       </c>
       <c r="K14" t="n">
-        <v>-39.94</v>
+        <v>-23.03</v>
       </c>
       <c r="L14" t="n">
-        <v>68.18000000000001</v>
+        <v>39.31</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>30</v>
       </c>
       <c r="J15" t="n">
-        <v>102.4</v>
+        <v>60.86</v>
       </c>
       <c r="K15" t="n">
-        <v>82.45</v>
+        <v>49</v>
       </c>
       <c r="L15" t="n">
-        <v>131.47</v>
+        <v>78.13</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>-56.94</v>
+        <v>-38.37</v>
       </c>
       <c r="K16" t="n">
-        <v>-10.24</v>
+        <v>-6.9</v>
       </c>
       <c r="L16" t="n">
-        <v>57.86</v>
+        <v>38.99</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>-88.56999999999999</v>
+        <v>-56.09</v>
       </c>
       <c r="K17" t="n">
-        <v>-53.96</v>
+        <v>-34.17</v>
       </c>
       <c r="L17" t="n">
-        <v>103.71</v>
+        <v>65.68000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>-59.89</v>
+        <v>-35.86</v>
       </c>
       <c r="K18" t="n">
-        <v>72.59999999999999</v>
+        <v>43.47</v>
       </c>
       <c r="L18" t="n">
-        <v>94.12</v>
+        <v>56.35</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>29</v>
       </c>
       <c r="J19" t="n">
-        <v>-5.19</v>
+        <v>-3.34</v>
       </c>
       <c r="K19" t="n">
-        <v>-63.22</v>
+        <v>-40.63</v>
       </c>
       <c r="L19" t="n">
-        <v>63.43</v>
+        <v>40.76</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>-142.15</v>
+        <v>-74.75</v>
       </c>
       <c r="K20" t="n">
-        <v>-68.45999999999999</v>
+        <v>-36</v>
       </c>
       <c r="L20" t="n">
-        <v>157.78</v>
+        <v>82.97</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>27</v>
       </c>
       <c r="J21" t="n">
-        <v>46.2</v>
+        <v>27.71</v>
       </c>
       <c r="K21" t="n">
-        <v>-108.11</v>
+        <v>-64.84</v>
       </c>
       <c r="L21" t="n">
-        <v>117.56</v>
+        <v>70.52</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>30</v>
       </c>
       <c r="J22" t="n">
-        <v>-53.87</v>
+        <v>-30.76</v>
       </c>
       <c r="K22" t="n">
-        <v>-94.52</v>
+        <v>-53.97</v>
       </c>
       <c r="L22" t="n">
-        <v>108.79</v>
+        <v>62.13</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>30</v>
       </c>
       <c r="J23" t="n">
-        <v>154.79</v>
+        <v>92.06999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>-86.41</v>
+        <v>-51.4</v>
       </c>
       <c r="L23" t="n">
-        <v>177.27</v>
+        <v>105.45</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>28</v>
       </c>
       <c r="J24" t="n">
-        <v>151.6</v>
+        <v>93.68000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>134.05</v>
+        <v>82.83</v>
       </c>
       <c r="L24" t="n">
-        <v>202.37</v>
+        <v>125.04</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>-209.01</v>
+        <v>-128.94</v>
       </c>
       <c r="K25" t="n">
-        <v>-104.12</v>
+        <v>-64.23</v>
       </c>
       <c r="L25" t="n">
-        <v>233.51</v>
+        <v>144.06</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>30</v>
       </c>
       <c r="J26" t="n">
-        <v>198.95</v>
+        <v>131.02</v>
       </c>
       <c r="K26" t="n">
-        <v>124.72</v>
+        <v>82.13</v>
       </c>
       <c r="L26" t="n">
-        <v>234.81</v>
+        <v>154.63</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>-13.21</v>
+        <v>-7.68</v>
       </c>
       <c r="K27" t="n">
-        <v>-205.38</v>
+        <v>-119.41</v>
       </c>
       <c r="L27" t="n">
-        <v>205.8</v>
+        <v>119.65</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>29</v>
       </c>
       <c r="J28" t="n">
-        <v>-116.35</v>
+        <v>-76.62</v>
       </c>
       <c r="K28" t="n">
-        <v>243.42</v>
+        <v>160.3</v>
       </c>
       <c r="L28" t="n">
-        <v>269.8</v>
+        <v>177.67</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>-92.03</v>
+        <v>-58</v>
       </c>
       <c r="K29" t="n">
-        <v>2.71</v>
+        <v>1.71</v>
       </c>
       <c r="L29" t="n">
-        <v>92.06999999999999</v>
+        <v>58.02</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>29</v>
       </c>
       <c r="J30" t="n">
-        <v>-5.98</v>
+        <v>-3.47</v>
       </c>
       <c r="K30" t="n">
-        <v>-73</v>
+        <v>-42.31</v>
       </c>
       <c r="L30" t="n">
-        <v>73.25</v>
+        <v>42.45</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>9.699999999999999</v>
+        <v>5.65</v>
       </c>
       <c r="K31" t="n">
-        <v>-81.48</v>
+        <v>-47.47</v>
       </c>
       <c r="L31" t="n">
-        <v>82.05</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>29</v>
       </c>
       <c r="J32" t="n">
-        <v>-38.67</v>
+        <v>-22.77</v>
       </c>
       <c r="K32" t="n">
-        <v>-58.18</v>
+        <v>-34.26</v>
       </c>
       <c r="L32" t="n">
-        <v>69.86</v>
+        <v>41.14</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>29</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.12</v>
+        <v>-0.61</v>
       </c>
       <c r="K33" t="n">
-        <v>141.93</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>141.93</v>
+        <v>76.90000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>27</v>
       </c>
       <c r="J34" t="n">
-        <v>77.06</v>
+        <v>49.89</v>
       </c>
       <c r="K34" t="n">
-        <v>35.72</v>
+        <v>23.13</v>
       </c>
       <c r="L34" t="n">
-        <v>84.94</v>
+        <v>54.99</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>25</v>
       </c>
       <c r="J35" t="n">
-        <v>-170.86</v>
+        <v>-93.88</v>
       </c>
       <c r="K35" t="n">
-        <v>39.65</v>
+        <v>21.79</v>
       </c>
       <c r="L35" t="n">
-        <v>175.4</v>
+        <v>96.38</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>212.57</v>
+        <v>125.58</v>
       </c>
       <c r="K36" t="n">
-        <v>88.62</v>
+        <v>52.36</v>
       </c>
       <c r="L36" t="n">
-        <v>230.31</v>
+        <v>136.06</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>24</v>
       </c>
       <c r="J37" t="n">
-        <v>-302.03</v>
+        <v>-156.95</v>
       </c>
       <c r="K37" t="n">
-        <v>159.64</v>
+        <v>82.95</v>
       </c>
       <c r="L37" t="n">
-        <v>341.62</v>
+        <v>177.52</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>28</v>
       </c>
       <c r="J38" t="n">
-        <v>71.11</v>
+        <v>43.32</v>
       </c>
       <c r="K38" t="n">
-        <v>-215.64</v>
+        <v>-131.37</v>
       </c>
       <c r="L38" t="n">
-        <v>227.07</v>
+        <v>138.33</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>28</v>
       </c>
       <c r="J39" t="n">
-        <v>-99.22</v>
+        <v>-61.6</v>
       </c>
       <c r="K39" t="n">
-        <v>112.5</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>150</v>
+        <v>93.14</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>25</v>
       </c>
       <c r="J40" t="n">
-        <v>203.16</v>
+        <v>127.83</v>
       </c>
       <c r="K40" t="n">
-        <v>223.34</v>
+        <v>140.53</v>
       </c>
       <c r="L40" t="n">
-        <v>301.92</v>
+        <v>189.97</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>24</v>
       </c>
       <c r="J41" t="n">
-        <v>-189.97</v>
+        <v>-116.88</v>
       </c>
       <c r="K41" t="n">
-        <v>39.53</v>
+        <v>24.32</v>
       </c>
       <c r="L41" t="n">
-        <v>194.04</v>
+        <v>119.38</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>27</v>
       </c>
       <c r="J42" t="n">
-        <v>165.36</v>
+        <v>101.55</v>
       </c>
       <c r="K42" t="n">
-        <v>189.29</v>
+        <v>116.25</v>
       </c>
       <c r="L42" t="n">
-        <v>251.34</v>
+        <v>154.35</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>30</v>
       </c>
       <c r="J43" t="n">
-        <v>-180.57</v>
+        <v>-114.95</v>
       </c>
       <c r="K43" t="n">
-        <v>256.75</v>
+        <v>163.45</v>
       </c>
       <c r="L43" t="n">
-        <v>313.89</v>
+        <v>199.82</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>29</v>
       </c>
       <c r="J44" t="n">
-        <v>116.51</v>
+        <v>67.52</v>
       </c>
       <c r="K44" t="n">
-        <v>-93.87</v>
+        <v>-54.4</v>
       </c>
       <c r="L44" t="n">
-        <v>149.62</v>
+        <v>86.70999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>28</v>
       </c>
       <c r="J45" t="n">
-        <v>-127.95</v>
+        <v>-77.7</v>
       </c>
       <c r="K45" t="n">
-        <v>-60.48</v>
+        <v>-36.73</v>
       </c>
       <c r="L45" t="n">
-        <v>141.52</v>
+        <v>85.95</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>98.62</v>
+        <v>54.86</v>
       </c>
       <c r="K46" t="n">
-        <v>122.01</v>
+        <v>67.86</v>
       </c>
       <c r="L46" t="n">
-        <v>156.88</v>
+        <v>87.26000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>29</v>
       </c>
       <c r="J47" t="n">
-        <v>12.73</v>
+        <v>2.49</v>
       </c>
       <c r="K47" t="n">
-        <v>60.82</v>
+        <v>11.9</v>
       </c>
       <c r="L47" t="n">
-        <v>62.14</v>
+        <v>12.16</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>130.65</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>-149.41</v>
+        <v>-84.62</v>
       </c>
       <c r="L48" t="n">
-        <v>198.47</v>
+        <v>112.4</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>-86.13</v>
+        <v>-51.35</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.28</v>
+        <v>-0.17</v>
       </c>
       <c r="L49" t="n">
-        <v>86.13</v>
+        <v>51.35</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>28</v>
       </c>
       <c r="J50" t="n">
-        <v>-188.94</v>
+        <v>-108.92</v>
       </c>
       <c r="K50" t="n">
-        <v>49.37</v>
+        <v>28.46</v>
       </c>
       <c r="L50" t="n">
-        <v>195.29</v>
+        <v>112.58</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>29</v>
       </c>
       <c r="J51" t="n">
-        <v>22.03</v>
+        <v>12.4</v>
       </c>
       <c r="K51" t="n">
-        <v>-174.94</v>
+        <v>-98.52</v>
       </c>
       <c r="L51" t="n">
-        <v>176.32</v>
+        <v>99.3</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>28</v>
       </c>
       <c r="J52" t="n">
-        <v>1.21</v>
+        <v>0.71</v>
       </c>
       <c r="K52" t="n">
-        <v>-147.72</v>
+        <v>-86.41</v>
       </c>
       <c r="L52" t="n">
-        <v>147.72</v>
+        <v>86.41</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>30</v>
       </c>
       <c r="J53" t="n">
-        <v>111.7</v>
+        <v>64.97</v>
       </c>
       <c r="K53" t="n">
-        <v>189.34</v>
+        <v>110.13</v>
       </c>
       <c r="L53" t="n">
-        <v>219.83</v>
+        <v>127.87</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>51.49</v>
+        <v>29.51</v>
       </c>
       <c r="K54" t="n">
-        <v>129.2</v>
+        <v>74.05</v>
       </c>
       <c r="L54" t="n">
-        <v>139.08</v>
+        <v>79.72</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>-94.91</v>
+        <v>-57.55</v>
       </c>
       <c r="K55" t="n">
-        <v>-256.32</v>
+        <v>-155.43</v>
       </c>
       <c r="L55" t="n">
-        <v>273.32</v>
+        <v>165.75</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>29</v>
       </c>
       <c r="J56" t="n">
-        <v>-98.23999999999999</v>
+        <v>-58.93</v>
       </c>
       <c r="K56" t="n">
-        <v>-255.97</v>
+        <v>-153.54</v>
       </c>
       <c r="L56" t="n">
-        <v>274.17</v>
+        <v>164.46</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>29</v>
       </c>
       <c r="J57" t="n">
-        <v>210.96</v>
+        <v>126.99</v>
       </c>
       <c r="K57" t="n">
-        <v>-42.98</v>
+        <v>-25.87</v>
       </c>
       <c r="L57" t="n">
-        <v>215.3</v>
+        <v>129.6</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>26</v>
       </c>
       <c r="J58" t="n">
-        <v>261.47</v>
+        <v>161.76</v>
       </c>
       <c r="K58" t="n">
-        <v>-233.71</v>
+        <v>-144.59</v>
       </c>
       <c r="L58" t="n">
-        <v>350.69</v>
+        <v>216.97</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>35.63</v>
+        <v>22.2</v>
       </c>
       <c r="K59" t="n">
-        <v>-66.11</v>
+        <v>-41.19</v>
       </c>
       <c r="L59" t="n">
-        <v>75.09999999999999</v>
+        <v>46.79</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>29</v>
       </c>
       <c r="J60" t="n">
-        <v>61.6</v>
+        <v>35.58</v>
       </c>
       <c r="K60" t="n">
-        <v>1.47</v>
+        <v>0.85</v>
       </c>
       <c r="L60" t="n">
-        <v>61.62</v>
+        <v>35.59</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>29</v>
       </c>
       <c r="J61" t="n">
-        <v>-70.76000000000001</v>
+        <v>-39.65</v>
       </c>
       <c r="K61" t="n">
-        <v>-24.65</v>
+        <v>-13.81</v>
       </c>
       <c r="L61" t="n">
-        <v>74.93000000000001</v>
+        <v>41.99</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>-47.49</v>
+        <v>-26.79</v>
       </c>
       <c r="K62" t="n">
-        <v>77.23999999999999</v>
+        <v>43.58</v>
       </c>
       <c r="L62" t="n">
-        <v>90.67</v>
+        <v>51.16</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>29</v>
       </c>
       <c r="J63" t="n">
-        <v>2.52</v>
+        <v>1.45</v>
       </c>
       <c r="K63" t="n">
-        <v>110.17</v>
+        <v>63.59</v>
       </c>
       <c r="L63" t="n">
-        <v>110.2</v>
+        <v>63.61</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>28</v>
       </c>
       <c r="J64" t="n">
-        <v>-24.69</v>
+        <v>-13.8</v>
       </c>
       <c r="K64" t="n">
-        <v>-177.81</v>
+        <v>-99.41</v>
       </c>
       <c r="L64" t="n">
-        <v>179.51</v>
+        <v>100.36</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>27</v>
       </c>
       <c r="J65" t="n">
-        <v>-123.63</v>
+        <v>-71.79000000000001</v>
       </c>
       <c r="K65" t="n">
-        <v>47.34</v>
+        <v>27.49</v>
       </c>
       <c r="L65" t="n">
-        <v>132.38</v>
+        <v>76.87</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-107.79</v>
+        <v>-62.74</v>
       </c>
       <c r="K66" t="n">
-        <v>-103.78</v>
+        <v>-60.41</v>
       </c>
       <c r="L66" t="n">
-        <v>149.63</v>
+        <v>87.09999999999999</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>27</v>
       </c>
       <c r="J67" t="n">
-        <v>176.32</v>
+        <v>89.79000000000001</v>
       </c>
       <c r="K67" t="n">
-        <v>-102.74</v>
+        <v>-52.32</v>
       </c>
       <c r="L67" t="n">
-        <v>204.07</v>
+        <v>103.92</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>189.04</v>
+        <v>110.41</v>
       </c>
       <c r="K68" t="n">
-        <v>-12.12</v>
+        <v>-7.08</v>
       </c>
       <c r="L68" t="n">
-        <v>189.43</v>
+        <v>110.64</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>-68.92</v>
+        <v>-41.98</v>
       </c>
       <c r="K69" t="n">
-        <v>98.53</v>
+        <v>60.02</v>
       </c>
       <c r="L69" t="n">
-        <v>120.24</v>
+        <v>73.25</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>28</v>
       </c>
       <c r="J70" t="n">
-        <v>196.09</v>
+        <v>94.94</v>
       </c>
       <c r="K70" t="n">
-        <v>310.36</v>
+        <v>150.27</v>
       </c>
       <c r="L70" t="n">
-        <v>367.12</v>
+        <v>177.75</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>-80.77</v>
+        <v>-45.67</v>
       </c>
       <c r="K71" t="n">
-        <v>-419.01</v>
+        <v>-236.9</v>
       </c>
       <c r="L71" t="n">
-        <v>426.73</v>
+        <v>241.26</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>24</v>
       </c>
       <c r="J72" t="n">
-        <v>-320.09</v>
+        <v>-180.01</v>
       </c>
       <c r="K72" t="n">
-        <v>101.38</v>
+        <v>57.02</v>
       </c>
       <c r="L72" t="n">
-        <v>335.76</v>
+        <v>188.83</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>30</v>
       </c>
       <c r="J73" t="n">
-        <v>124.71</v>
+        <v>75.75</v>
       </c>
       <c r="K73" t="n">
-        <v>365.03</v>
+        <v>221.73</v>
       </c>
       <c r="L73" t="n">
-        <v>385.75</v>
+        <v>234.31</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>39.64</v>
+        <v>23.3</v>
       </c>
       <c r="K74" t="n">
-        <v>-56.85</v>
+        <v>-33.42</v>
       </c>
       <c r="L74" t="n">
-        <v>69.31</v>
+        <v>40.74</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>114.6</v>
+        <v>66.3</v>
       </c>
       <c r="K75" t="n">
-        <v>24.73</v>
+        <v>14.3</v>
       </c>
       <c r="L75" t="n">
-        <v>117.24</v>
+        <v>67.83</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>28</v>
       </c>
       <c r="J76" t="n">
-        <v>-95.69</v>
+        <v>-54.2</v>
       </c>
       <c r="K76" t="n">
-        <v>-68.34999999999999</v>
+        <v>-38.71</v>
       </c>
       <c r="L76" t="n">
-        <v>117.59</v>
+        <v>66.59999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>26</v>
       </c>
       <c r="J77" t="n">
-        <v>-111.64</v>
+        <v>-66.7</v>
       </c>
       <c r="K77" t="n">
-        <v>24.45</v>
+        <v>14.61</v>
       </c>
       <c r="L77" t="n">
-        <v>114.29</v>
+        <v>68.28</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>29</v>
       </c>
       <c r="J78" t="n">
-        <v>-78.87</v>
+        <v>-40.03</v>
       </c>
       <c r="K78" t="n">
-        <v>69.05</v>
+        <v>35.05</v>
       </c>
       <c r="L78" t="n">
-        <v>104.83</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>-85.64</v>
+        <v>-50.95</v>
       </c>
       <c r="K79" t="n">
-        <v>-17.72</v>
+        <v>-10.55</v>
       </c>
       <c r="L79" t="n">
-        <v>87.45</v>
+        <v>52.03</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>-181.3</v>
+        <v>-103.53</v>
       </c>
       <c r="K80" t="n">
-        <v>-129.74</v>
+        <v>-74.09</v>
       </c>
       <c r="L80" t="n">
-        <v>222.94</v>
+        <v>127.31</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>128.15</v>
+        <v>75.33</v>
       </c>
       <c r="K81" t="n">
-        <v>-18.14</v>
+        <v>-10.66</v>
       </c>
       <c r="L81" t="n">
-        <v>129.43</v>
+        <v>76.08</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>26</v>
       </c>
       <c r="J82" t="n">
-        <v>-80.64</v>
+        <v>-41.44</v>
       </c>
       <c r="K82" t="n">
-        <v>98.20999999999999</v>
+        <v>50.47</v>
       </c>
       <c r="L82" t="n">
-        <v>127.08</v>
+        <v>65.3</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>30</v>
       </c>
       <c r="J83" t="n">
-        <v>153.39</v>
+        <v>94.63</v>
       </c>
       <c r="K83" t="n">
-        <v>155.94</v>
+        <v>96.2</v>
       </c>
       <c r="L83" t="n">
-        <v>218.74</v>
+        <v>134.94</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>29</v>
       </c>
       <c r="J84" t="n">
-        <v>-182.71</v>
+        <v>-105.99</v>
       </c>
       <c r="K84" t="n">
-        <v>-34.24</v>
+        <v>-19.86</v>
       </c>
       <c r="L84" t="n">
-        <v>185.89</v>
+        <v>107.84</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>-151.49</v>
+        <v>-90.37</v>
       </c>
       <c r="K85" t="n">
-        <v>-205.55</v>
+        <v>-122.62</v>
       </c>
       <c r="L85" t="n">
-        <v>255.34</v>
+        <v>152.32</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>215</v>
+        <v>128.28</v>
       </c>
       <c r="K86" t="n">
-        <v>338.31</v>
+        <v>201.85</v>
       </c>
       <c r="L86" t="n">
-        <v>400.85</v>
+        <v>239.17</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>-78.77</v>
+        <v>-45.34</v>
       </c>
       <c r="K87" t="n">
-        <v>193.78</v>
+        <v>111.53</v>
       </c>
       <c r="L87" t="n">
-        <v>209.18</v>
+        <v>120.39</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>28</v>
       </c>
       <c r="J88" t="n">
-        <v>229.13</v>
+        <v>132.76</v>
       </c>
       <c r="K88" t="n">
-        <v>154.37</v>
+        <v>89.45</v>
       </c>
       <c r="L88" t="n">
-        <v>276.28</v>
+        <v>160.08</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-10.xlsx
+++ b/output/2024-07-10.xlsx
@@ -640,13 +640,13 @@
         <v>30</v>
       </c>
       <c r="J14" t="n">
-        <v>-31.86</v>
+        <v>-33.03</v>
       </c>
       <c r="K14" t="n">
-        <v>-23.03</v>
+        <v>-23.88</v>
       </c>
       <c r="L14" t="n">
-        <v>39.31</v>
+        <v>40.76</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>30</v>
       </c>
       <c r="J15" t="n">
-        <v>60.86</v>
+        <v>58.14</v>
       </c>
       <c r="K15" t="n">
-        <v>49</v>
+        <v>46.81</v>
       </c>
       <c r="L15" t="n">
-        <v>78.13</v>
+        <v>74.64</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>-38.37</v>
+        <v>-39.51</v>
       </c>
       <c r="K16" t="n">
-        <v>-6.9</v>
+        <v>-7.11</v>
       </c>
       <c r="L16" t="n">
-        <v>38.99</v>
+        <v>40.14</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>-56.09</v>
+        <v>-56.26</v>
       </c>
       <c r="K17" t="n">
-        <v>-34.17</v>
+        <v>-34.27</v>
       </c>
       <c r="L17" t="n">
-        <v>65.68000000000001</v>
+        <v>65.87</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>-35.86</v>
+        <v>-36.6</v>
       </c>
       <c r="K18" t="n">
-        <v>43.47</v>
+        <v>44.37</v>
       </c>
       <c r="L18" t="n">
-        <v>56.35</v>
+        <v>57.52</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>29</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.34</v>
+        <v>-3.53</v>
       </c>
       <c r="K19" t="n">
-        <v>-40.63</v>
+        <v>-42.98</v>
       </c>
       <c r="L19" t="n">
-        <v>40.76</v>
+        <v>43.12</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>-74.75</v>
+        <v>-76.75</v>
       </c>
       <c r="K20" t="n">
-        <v>-36</v>
+        <v>-36.96</v>
       </c>
       <c r="L20" t="n">
-        <v>82.97</v>
+        <v>85.19</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>27</v>
       </c>
       <c r="J21" t="n">
-        <v>27.71</v>
+        <v>28.63</v>
       </c>
       <c r="K21" t="n">
-        <v>-64.84</v>
+        <v>-67.01000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>70.52</v>
+        <v>72.87</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>30</v>
       </c>
       <c r="J22" t="n">
-        <v>-30.76</v>
+        <v>-32.24</v>
       </c>
       <c r="K22" t="n">
-        <v>-53.97</v>
+        <v>-56.57</v>
       </c>
       <c r="L22" t="n">
-        <v>62.13</v>
+        <v>65.11</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>30</v>
       </c>
       <c r="J23" t="n">
-        <v>92.06999999999999</v>
+        <v>93.98999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>-51.4</v>
+        <v>-52.47</v>
       </c>
       <c r="L23" t="n">
-        <v>105.45</v>
+        <v>107.64</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>28</v>
       </c>
       <c r="J24" t="n">
-        <v>93.68000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="K24" t="n">
-        <v>82.83</v>
+        <v>82.67</v>
       </c>
       <c r="L24" t="n">
-        <v>125.04</v>
+        <v>124.8</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>-128.94</v>
+        <v>-127.09</v>
       </c>
       <c r="K25" t="n">
-        <v>-64.23</v>
+        <v>-63.31</v>
       </c>
       <c r="L25" t="n">
-        <v>144.06</v>
+        <v>141.99</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>30</v>
       </c>
       <c r="J26" t="n">
-        <v>131.02</v>
+        <v>131.6</v>
       </c>
       <c r="K26" t="n">
-        <v>82.13</v>
+        <v>82.5</v>
       </c>
       <c r="L26" t="n">
-        <v>154.63</v>
+        <v>155.32</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>-7.68</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>-119.41</v>
+        <v>-127.87</v>
       </c>
       <c r="L27" t="n">
-        <v>119.65</v>
+        <v>128.14</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>29</v>
       </c>
       <c r="J28" t="n">
-        <v>-76.62</v>
+        <v>-75.81</v>
       </c>
       <c r="K28" t="n">
-        <v>160.3</v>
+        <v>158.62</v>
       </c>
       <c r="L28" t="n">
-        <v>177.67</v>
+        <v>175.8</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>-58</v>
+        <v>-57.1</v>
       </c>
       <c r="K29" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="L29" t="n">
-        <v>58.02</v>
+        <v>57.12</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>29</v>
       </c>
       <c r="J30" t="n">
-        <v>-3.47</v>
+        <v>-3.56</v>
       </c>
       <c r="K30" t="n">
-        <v>-42.31</v>
+        <v>-43.52</v>
       </c>
       <c r="L30" t="n">
-        <v>42.45</v>
+        <v>43.67</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>5.65</v>
+        <v>5.78</v>
       </c>
       <c r="K31" t="n">
-        <v>-47.47</v>
+        <v>-48.59</v>
       </c>
       <c r="L31" t="n">
-        <v>47.8</v>
+        <v>48.93</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>29</v>
       </c>
       <c r="J32" t="n">
-        <v>-22.77</v>
+        <v>-24.32</v>
       </c>
       <c r="K32" t="n">
-        <v>-34.26</v>
+        <v>-36.58</v>
       </c>
       <c r="L32" t="n">
-        <v>41.14</v>
+        <v>43.93</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>29</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.61</v>
+        <v>-0.6</v>
       </c>
       <c r="K33" t="n">
-        <v>76.90000000000001</v>
+        <v>75.73</v>
       </c>
       <c r="L33" t="n">
-        <v>76.90000000000001</v>
+        <v>75.73</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>27</v>
       </c>
       <c r="J34" t="n">
-        <v>49.89</v>
+        <v>50.71</v>
       </c>
       <c r="K34" t="n">
-        <v>23.13</v>
+        <v>23.51</v>
       </c>
       <c r="L34" t="n">
-        <v>54.99</v>
+        <v>55.89</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>25</v>
       </c>
       <c r="J35" t="n">
-        <v>-93.88</v>
+        <v>-94.12</v>
       </c>
       <c r="K35" t="n">
-        <v>21.79</v>
+        <v>21.84</v>
       </c>
       <c r="L35" t="n">
-        <v>96.38</v>
+        <v>96.62</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>125.58</v>
+        <v>121.16</v>
       </c>
       <c r="K36" t="n">
-        <v>52.36</v>
+        <v>50.51</v>
       </c>
       <c r="L36" t="n">
-        <v>136.06</v>
+        <v>131.27</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>24</v>
       </c>
       <c r="J37" t="n">
-        <v>-156.95</v>
+        <v>-148.86</v>
       </c>
       <c r="K37" t="n">
-        <v>82.95</v>
+        <v>78.68000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>177.52</v>
+        <v>168.37</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>28</v>
       </c>
       <c r="J38" t="n">
-        <v>43.32</v>
+        <v>42.9</v>
       </c>
       <c r="K38" t="n">
-        <v>-131.37</v>
+        <v>-130.1</v>
       </c>
       <c r="L38" t="n">
-        <v>138.33</v>
+        <v>137</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>28</v>
       </c>
       <c r="J39" t="n">
-        <v>-61.6</v>
+        <v>-64.23</v>
       </c>
       <c r="K39" t="n">
-        <v>69.84999999999999</v>
+        <v>72.84</v>
       </c>
       <c r="L39" t="n">
-        <v>93.14</v>
+        <v>97.11</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>25</v>
       </c>
       <c r="J40" t="n">
-        <v>127.83</v>
+        <v>123.01</v>
       </c>
       <c r="K40" t="n">
-        <v>140.53</v>
+        <v>135.23</v>
       </c>
       <c r="L40" t="n">
-        <v>189.97</v>
+        <v>182.81</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>24</v>
       </c>
       <c r="J41" t="n">
-        <v>-116.88</v>
+        <v>-124.8</v>
       </c>
       <c r="K41" t="n">
-        <v>24.32</v>
+        <v>25.97</v>
       </c>
       <c r="L41" t="n">
-        <v>119.38</v>
+        <v>127.47</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>27</v>
       </c>
       <c r="J42" t="n">
-        <v>101.55</v>
+        <v>103.3</v>
       </c>
       <c r="K42" t="n">
-        <v>116.25</v>
+        <v>118.26</v>
       </c>
       <c r="L42" t="n">
-        <v>154.35</v>
+        <v>157.02</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>30</v>
       </c>
       <c r="J43" t="n">
-        <v>-114.95</v>
+        <v>-112.25</v>
       </c>
       <c r="K43" t="n">
-        <v>163.45</v>
+        <v>159.61</v>
       </c>
       <c r="L43" t="n">
-        <v>199.82</v>
+        <v>195.13</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>29</v>
       </c>
       <c r="J44" t="n">
-        <v>67.52</v>
+        <v>64.45</v>
       </c>
       <c r="K44" t="n">
-        <v>-54.4</v>
+        <v>-51.93</v>
       </c>
       <c r="L44" t="n">
-        <v>86.70999999999999</v>
+        <v>82.77</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>28</v>
       </c>
       <c r="J45" t="n">
-        <v>-77.7</v>
+        <v>-74.03</v>
       </c>
       <c r="K45" t="n">
-        <v>-36.73</v>
+        <v>-34.99</v>
       </c>
       <c r="L45" t="n">
-        <v>85.95</v>
+        <v>81.88</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>54.86</v>
+        <v>52.96</v>
       </c>
       <c r="K46" t="n">
-        <v>67.86</v>
+        <v>65.52</v>
       </c>
       <c r="L46" t="n">
-        <v>87.26000000000001</v>
+        <v>84.23999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>29</v>
       </c>
       <c r="J47" t="n">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="K47" t="n">
-        <v>11.9</v>
+        <v>11.68</v>
       </c>
       <c r="L47" t="n">
-        <v>12.16</v>
+        <v>11.93</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>73.98999999999999</v>
+        <v>70.72</v>
       </c>
       <c r="K48" t="n">
-        <v>-84.62</v>
+        <v>-80.88</v>
       </c>
       <c r="L48" t="n">
-        <v>112.4</v>
+        <v>107.43</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>-51.35</v>
+        <v>-53.92</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.17</v>
+        <v>-0.18</v>
       </c>
       <c r="L49" t="n">
-        <v>51.35</v>
+        <v>53.92</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>28</v>
       </c>
       <c r="J50" t="n">
-        <v>-108.92</v>
+        <v>-106.73</v>
       </c>
       <c r="K50" t="n">
-        <v>28.46</v>
+        <v>27.89</v>
       </c>
       <c r="L50" t="n">
-        <v>112.58</v>
+        <v>110.31</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>29</v>
       </c>
       <c r="J51" t="n">
-        <v>12.4</v>
+        <v>12.31</v>
       </c>
       <c r="K51" t="n">
-        <v>-98.52</v>
+        <v>-97.79000000000001</v>
       </c>
       <c r="L51" t="n">
-        <v>99.3</v>
+        <v>98.56</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>28</v>
       </c>
       <c r="J52" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="K52" t="n">
-        <v>-86.41</v>
+        <v>-87.27</v>
       </c>
       <c r="L52" t="n">
-        <v>86.41</v>
+        <v>87.27</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>30</v>
       </c>
       <c r="J53" t="n">
-        <v>64.97</v>
+        <v>65.29000000000001</v>
       </c>
       <c r="K53" t="n">
-        <v>110.13</v>
+        <v>110.67</v>
       </c>
       <c r="L53" t="n">
-        <v>127.87</v>
+        <v>128.5</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>29.51</v>
+        <v>29.29</v>
       </c>
       <c r="K54" t="n">
-        <v>74.05</v>
+        <v>73.48999999999999</v>
       </c>
       <c r="L54" t="n">
-        <v>79.72</v>
+        <v>79.11</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>-57.55</v>
+        <v>-56.57</v>
       </c>
       <c r="K55" t="n">
-        <v>-155.43</v>
+        <v>-152.78</v>
       </c>
       <c r="L55" t="n">
-        <v>165.75</v>
+        <v>162.91</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>29</v>
       </c>
       <c r="J56" t="n">
-        <v>-58.93</v>
+        <v>-59.46</v>
       </c>
       <c r="K56" t="n">
-        <v>-153.54</v>
+        <v>-154.92</v>
       </c>
       <c r="L56" t="n">
-        <v>164.46</v>
+        <v>165.94</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>29</v>
       </c>
       <c r="J57" t="n">
-        <v>126.99</v>
+        <v>132.71</v>
       </c>
       <c r="K57" t="n">
-        <v>-25.87</v>
+        <v>-27.04</v>
       </c>
       <c r="L57" t="n">
-        <v>129.6</v>
+        <v>135.44</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>26</v>
       </c>
       <c r="J58" t="n">
-        <v>161.76</v>
+        <v>158.92</v>
       </c>
       <c r="K58" t="n">
-        <v>-144.59</v>
+        <v>-142.05</v>
       </c>
       <c r="L58" t="n">
-        <v>216.97</v>
+        <v>213.15</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>22.2</v>
+        <v>22.44</v>
       </c>
       <c r="K59" t="n">
-        <v>-41.19</v>
+        <v>-41.64</v>
       </c>
       <c r="L59" t="n">
-        <v>46.79</v>
+        <v>47.31</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>29</v>
       </c>
       <c r="J60" t="n">
-        <v>35.58</v>
+        <v>37.62</v>
       </c>
       <c r="K60" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="L60" t="n">
-        <v>35.59</v>
+        <v>37.63</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>29</v>
       </c>
       <c r="J61" t="n">
-        <v>-39.65</v>
+        <v>-41.07</v>
       </c>
       <c r="K61" t="n">
-        <v>-13.81</v>
+        <v>-14.31</v>
       </c>
       <c r="L61" t="n">
-        <v>41.99</v>
+        <v>43.49</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>-26.79</v>
+        <v>-27.9</v>
       </c>
       <c r="K62" t="n">
-        <v>43.58</v>
+        <v>45.38</v>
       </c>
       <c r="L62" t="n">
-        <v>51.16</v>
+        <v>53.27</v>
       </c>
     </row>
     <row r="63">
@@ -2701,10 +2701,10 @@
         <v>1.45</v>
       </c>
       <c r="K63" t="n">
-        <v>63.59</v>
+        <v>63.58</v>
       </c>
       <c r="L63" t="n">
-        <v>63.61</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>28</v>
       </c>
       <c r="J64" t="n">
-        <v>-13.8</v>
+        <v>-13.21</v>
       </c>
       <c r="K64" t="n">
-        <v>-99.41</v>
+        <v>-95.14</v>
       </c>
       <c r="L64" t="n">
-        <v>100.36</v>
+        <v>96.05</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>27</v>
       </c>
       <c r="J65" t="n">
-        <v>-71.79000000000001</v>
+        <v>-73.25</v>
       </c>
       <c r="K65" t="n">
-        <v>27.49</v>
+        <v>28.05</v>
       </c>
       <c r="L65" t="n">
-        <v>76.87</v>
+        <v>78.44</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-62.74</v>
+        <v>-63.56</v>
       </c>
       <c r="K66" t="n">
-        <v>-60.41</v>
+        <v>-61.2</v>
       </c>
       <c r="L66" t="n">
-        <v>87.09999999999999</v>
+        <v>88.23</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>27</v>
       </c>
       <c r="J67" t="n">
-        <v>89.79000000000001</v>
+        <v>88.97</v>
       </c>
       <c r="K67" t="n">
-        <v>-52.32</v>
+        <v>-51.84</v>
       </c>
       <c r="L67" t="n">
-        <v>103.92</v>
+        <v>102.97</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>110.41</v>
+        <v>114.3</v>
       </c>
       <c r="K68" t="n">
-        <v>-7.08</v>
+        <v>-7.33</v>
       </c>
       <c r="L68" t="n">
-        <v>110.64</v>
+        <v>114.53</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>-41.98</v>
+        <v>-44.95</v>
       </c>
       <c r="K69" t="n">
-        <v>60.02</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="L69" t="n">
-        <v>73.25</v>
+        <v>78.42</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>28</v>
       </c>
       <c r="J70" t="n">
-        <v>94.94</v>
+        <v>88.69</v>
       </c>
       <c r="K70" t="n">
-        <v>150.27</v>
+        <v>140.38</v>
       </c>
       <c r="L70" t="n">
-        <v>177.75</v>
+        <v>166.04</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>-45.67</v>
+        <v>-44.59</v>
       </c>
       <c r="K71" t="n">
-        <v>-236.9</v>
+        <v>-231.29</v>
       </c>
       <c r="L71" t="n">
-        <v>241.26</v>
+        <v>235.55</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>24</v>
       </c>
       <c r="J72" t="n">
-        <v>-180.01</v>
+        <v>-182.09</v>
       </c>
       <c r="K72" t="n">
-        <v>57.02</v>
+        <v>57.68</v>
       </c>
       <c r="L72" t="n">
-        <v>188.83</v>
+        <v>191.01</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>30</v>
       </c>
       <c r="J73" t="n">
-        <v>75.75</v>
+        <v>69.25</v>
       </c>
       <c r="K73" t="n">
-        <v>221.73</v>
+        <v>202.7</v>
       </c>
       <c r="L73" t="n">
-        <v>234.31</v>
+        <v>214.21</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>23.3</v>
+        <v>24.3</v>
       </c>
       <c r="K74" t="n">
-        <v>-33.42</v>
+        <v>-34.86</v>
       </c>
       <c r="L74" t="n">
-        <v>40.74</v>
+        <v>42.49</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>66.3</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="K75" t="n">
-        <v>14.3</v>
+        <v>14.04</v>
       </c>
       <c r="L75" t="n">
-        <v>67.83</v>
+        <v>66.59999999999999</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>28</v>
       </c>
       <c r="J76" t="n">
-        <v>-54.2</v>
+        <v>-53.06</v>
       </c>
       <c r="K76" t="n">
-        <v>-38.71</v>
+        <v>-37.9</v>
       </c>
       <c r="L76" t="n">
-        <v>66.59999999999999</v>
+        <v>65.2</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>26</v>
       </c>
       <c r="J77" t="n">
-        <v>-66.7</v>
+        <v>-66.47</v>
       </c>
       <c r="K77" t="n">
-        <v>14.61</v>
+        <v>14.56</v>
       </c>
       <c r="L77" t="n">
-        <v>68.28</v>
+        <v>68.05</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>29</v>
       </c>
       <c r="J78" t="n">
-        <v>-40.03</v>
+        <v>-41.09</v>
       </c>
       <c r="K78" t="n">
-        <v>35.05</v>
+        <v>35.98</v>
       </c>
       <c r="L78" t="n">
-        <v>53.2</v>
+        <v>54.61</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>-50.95</v>
+        <v>-53.13</v>
       </c>
       <c r="K79" t="n">
-        <v>-10.55</v>
+        <v>-11</v>
       </c>
       <c r="L79" t="n">
-        <v>52.03</v>
+        <v>54.25</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>-103.53</v>
+        <v>-100.32</v>
       </c>
       <c r="K80" t="n">
-        <v>-74.09</v>
+        <v>-71.79000000000001</v>
       </c>
       <c r="L80" t="n">
-        <v>127.31</v>
+        <v>123.36</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>75.33</v>
+        <v>77.8</v>
       </c>
       <c r="K81" t="n">
-        <v>-10.66</v>
+        <v>-11.01</v>
       </c>
       <c r="L81" t="n">
-        <v>76.08</v>
+        <v>78.56999999999999</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>26</v>
       </c>
       <c r="J82" t="n">
-        <v>-41.44</v>
+        <v>-44</v>
       </c>
       <c r="K82" t="n">
-        <v>50.47</v>
+        <v>53.59</v>
       </c>
       <c r="L82" t="n">
-        <v>65.3</v>
+        <v>69.34</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>30</v>
       </c>
       <c r="J83" t="n">
-        <v>94.63</v>
+        <v>93.29000000000001</v>
       </c>
       <c r="K83" t="n">
-        <v>96.2</v>
+        <v>94.84</v>
       </c>
       <c r="L83" t="n">
-        <v>134.94</v>
+        <v>133.03</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>29</v>
       </c>
       <c r="J84" t="n">
-        <v>-105.99</v>
+        <v>-108.79</v>
       </c>
       <c r="K84" t="n">
-        <v>-19.86</v>
+        <v>-20.39</v>
       </c>
       <c r="L84" t="n">
-        <v>107.84</v>
+        <v>110.68</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>-90.37</v>
+        <v>-89.56999999999999</v>
       </c>
       <c r="K85" t="n">
-        <v>-122.62</v>
+        <v>-121.53</v>
       </c>
       <c r="L85" t="n">
-        <v>152.32</v>
+        <v>150.98</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>128.28</v>
+        <v>124.64</v>
       </c>
       <c r="K86" t="n">
-        <v>201.85</v>
+        <v>196.13</v>
       </c>
       <c r="L86" t="n">
-        <v>239.17</v>
+        <v>232.38</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>-45.34</v>
+        <v>-48.07</v>
       </c>
       <c r="K87" t="n">
-        <v>111.53</v>
+        <v>118.25</v>
       </c>
       <c r="L87" t="n">
-        <v>120.39</v>
+        <v>127.65</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>28</v>
       </c>
       <c r="J88" t="n">
-        <v>132.76</v>
+        <v>134.11</v>
       </c>
       <c r="K88" t="n">
-        <v>89.45</v>
+        <v>90.36</v>
       </c>
       <c r="L88" t="n">
-        <v>160.08</v>
+        <v>161.71</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-10.xlsx
+++ b/output/2024-07-10.xlsx
@@ -640,13 +640,13 @@
         <v>30</v>
       </c>
       <c r="J14" t="n">
-        <v>-33.03</v>
+        <v>-34.36</v>
       </c>
       <c r="K14" t="n">
-        <v>-23.88</v>
+        <v>-24.84</v>
       </c>
       <c r="L14" t="n">
-        <v>40.76</v>
+        <v>42.4</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>30</v>
       </c>
       <c r="J15" t="n">
-        <v>58.14</v>
+        <v>55.02</v>
       </c>
       <c r="K15" t="n">
-        <v>46.81</v>
+        <v>44.3</v>
       </c>
       <c r="L15" t="n">
-        <v>74.64</v>
+        <v>70.64</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>-39.51</v>
+        <v>-40.8</v>
       </c>
       <c r="K16" t="n">
-        <v>-7.11</v>
+        <v>-7.34</v>
       </c>
       <c r="L16" t="n">
-        <v>40.14</v>
+        <v>41.46</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>-56.26</v>
+        <v>-56.44</v>
       </c>
       <c r="K17" t="n">
-        <v>-34.27</v>
+        <v>-34.39</v>
       </c>
       <c r="L17" t="n">
-        <v>65.87</v>
+        <v>66.09</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>-36.6</v>
+        <v>-37.45</v>
       </c>
       <c r="K18" t="n">
-        <v>44.37</v>
+        <v>45.39</v>
       </c>
       <c r="L18" t="n">
-        <v>57.52</v>
+        <v>58.85</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>29</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.53</v>
+        <v>-3.75</v>
       </c>
       <c r="K19" t="n">
-        <v>-42.98</v>
+        <v>-45.67</v>
       </c>
       <c r="L19" t="n">
-        <v>43.12</v>
+        <v>45.82</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>-76.75</v>
+        <v>-79.03</v>
       </c>
       <c r="K20" t="n">
-        <v>-36.96</v>
+        <v>-38.06</v>
       </c>
       <c r="L20" t="n">
-        <v>85.19</v>
+        <v>87.72</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>27</v>
       </c>
       <c r="J21" t="n">
-        <v>28.63</v>
+        <v>29.69</v>
       </c>
       <c r="K21" t="n">
-        <v>-67.01000000000001</v>
+        <v>-69.48</v>
       </c>
       <c r="L21" t="n">
-        <v>72.87</v>
+        <v>75.55</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>30</v>
       </c>
       <c r="J22" t="n">
-        <v>-32.24</v>
+        <v>-33.93</v>
       </c>
       <c r="K22" t="n">
-        <v>-56.57</v>
+        <v>-59.54</v>
       </c>
       <c r="L22" t="n">
-        <v>65.11</v>
+        <v>68.53</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>30</v>
       </c>
       <c r="J23" t="n">
-        <v>93.98999999999999</v>
+        <v>96.18000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>-52.47</v>
+        <v>-53.69</v>
       </c>
       <c r="L23" t="n">
-        <v>107.64</v>
+        <v>110.16</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>28</v>
       </c>
       <c r="J24" t="n">
-        <v>93.5</v>
+        <v>93.29000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>82.67</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>124.8</v>
+        <v>124.53</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>-127.09</v>
+        <v>-124.97</v>
       </c>
       <c r="K25" t="n">
-        <v>-63.31</v>
+        <v>-62.26</v>
       </c>
       <c r="L25" t="n">
-        <v>141.99</v>
+        <v>139.62</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>30</v>
       </c>
       <c r="J26" t="n">
-        <v>131.6</v>
+        <v>132.26</v>
       </c>
       <c r="K26" t="n">
-        <v>82.5</v>
+        <v>82.91</v>
       </c>
       <c r="L26" t="n">
-        <v>155.32</v>
+        <v>156.1</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>-8.220000000000001</v>
+        <v>-8.85</v>
       </c>
       <c r="K27" t="n">
-        <v>-127.87</v>
+        <v>-137.55</v>
       </c>
       <c r="L27" t="n">
-        <v>128.14</v>
+        <v>137.84</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>29</v>
       </c>
       <c r="J28" t="n">
-        <v>-75.81</v>
+        <v>-74.89</v>
       </c>
       <c r="K28" t="n">
-        <v>158.62</v>
+        <v>156.69</v>
       </c>
       <c r="L28" t="n">
-        <v>175.8</v>
+        <v>173.67</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>-57.1</v>
+        <v>-56.07</v>
       </c>
       <c r="K29" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="L29" t="n">
-        <v>57.12</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>29</v>
       </c>
       <c r="J30" t="n">
-        <v>-3.56</v>
+        <v>-3.68</v>
       </c>
       <c r="K30" t="n">
-        <v>-43.52</v>
+        <v>-44.91</v>
       </c>
       <c r="L30" t="n">
-        <v>43.67</v>
+        <v>45.06</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>5.78</v>
+        <v>5.94</v>
       </c>
       <c r="K31" t="n">
-        <v>-48.59</v>
+        <v>-49.88</v>
       </c>
       <c r="L31" t="n">
-        <v>48.93</v>
+        <v>50.23</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>29</v>
       </c>
       <c r="J32" t="n">
-        <v>-24.32</v>
+        <v>-26.08</v>
       </c>
       <c r="K32" t="n">
-        <v>-36.58</v>
+        <v>-39.24</v>
       </c>
       <c r="L32" t="n">
-        <v>43.93</v>
+        <v>47.11</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>29</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.6</v>
+        <v>-0.59</v>
       </c>
       <c r="K33" t="n">
-        <v>75.73</v>
+        <v>74.38</v>
       </c>
       <c r="L33" t="n">
-        <v>75.73</v>
+        <v>74.39</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>27</v>
       </c>
       <c r="J34" t="n">
-        <v>50.71</v>
+        <v>51.65</v>
       </c>
       <c r="K34" t="n">
-        <v>23.51</v>
+        <v>23.94</v>
       </c>
       <c r="L34" t="n">
-        <v>55.89</v>
+        <v>56.93</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>25</v>
       </c>
       <c r="J35" t="n">
-        <v>-94.12</v>
+        <v>-94.39</v>
       </c>
       <c r="K35" t="n">
-        <v>21.84</v>
+        <v>21.91</v>
       </c>
       <c r="L35" t="n">
-        <v>96.62</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>121.16</v>
+        <v>116.11</v>
       </c>
       <c r="K36" t="n">
-        <v>50.51</v>
+        <v>48.41</v>
       </c>
       <c r="L36" t="n">
-        <v>131.27</v>
+        <v>125.79</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>24</v>
       </c>
       <c r="J37" t="n">
-        <v>-148.86</v>
+        <v>-139.62</v>
       </c>
       <c r="K37" t="n">
-        <v>78.68000000000001</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>168.37</v>
+        <v>157.92</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>28</v>
       </c>
       <c r="J38" t="n">
-        <v>42.9</v>
+        <v>42.43</v>
       </c>
       <c r="K38" t="n">
-        <v>-130.1</v>
+        <v>-128.66</v>
       </c>
       <c r="L38" t="n">
-        <v>137</v>
+        <v>135.47</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>28</v>
       </c>
       <c r="J39" t="n">
-        <v>-64.23</v>
+        <v>-67.23999999999999</v>
       </c>
       <c r="K39" t="n">
-        <v>72.84</v>
+        <v>76.23999999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>97.11</v>
+        <v>101.66</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>25</v>
       </c>
       <c r="J40" t="n">
-        <v>123.01</v>
+        <v>117.51</v>
       </c>
       <c r="K40" t="n">
-        <v>135.23</v>
+        <v>129.18</v>
       </c>
       <c r="L40" t="n">
-        <v>182.81</v>
+        <v>174.63</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>24</v>
       </c>
       <c r="J41" t="n">
-        <v>-124.8</v>
+        <v>-133.85</v>
       </c>
       <c r="K41" t="n">
-        <v>25.97</v>
+        <v>27.85</v>
       </c>
       <c r="L41" t="n">
-        <v>127.47</v>
+        <v>136.71</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>27</v>
       </c>
       <c r="J42" t="n">
-        <v>103.3</v>
+        <v>105.31</v>
       </c>
       <c r="K42" t="n">
-        <v>118.26</v>
+        <v>120.56</v>
       </c>
       <c r="L42" t="n">
-        <v>157.02</v>
+        <v>160.08</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>30</v>
       </c>
       <c r="J43" t="n">
-        <v>-112.25</v>
+        <v>-109.17</v>
       </c>
       <c r="K43" t="n">
-        <v>159.61</v>
+        <v>155.22</v>
       </c>
       <c r="L43" t="n">
-        <v>195.13</v>
+        <v>189.77</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>29</v>
       </c>
       <c r="J44" t="n">
-        <v>64.45</v>
+        <v>60.95</v>
       </c>
       <c r="K44" t="n">
-        <v>-51.93</v>
+        <v>-49.11</v>
       </c>
       <c r="L44" t="n">
-        <v>82.77</v>
+        <v>78.27</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>28</v>
       </c>
       <c r="J45" t="n">
-        <v>-74.03</v>
+        <v>-69.81999999999999</v>
       </c>
       <c r="K45" t="n">
-        <v>-34.99</v>
+        <v>-33</v>
       </c>
       <c r="L45" t="n">
-        <v>81.88</v>
+        <v>77.23</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>52.96</v>
+        <v>50.79</v>
       </c>
       <c r="K46" t="n">
-        <v>65.52</v>
+        <v>62.83</v>
       </c>
       <c r="L46" t="n">
-        <v>84.23999999999999</v>
+        <v>80.79000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>29</v>
       </c>
       <c r="J47" t="n">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="K47" t="n">
-        <v>11.68</v>
+        <v>12.54</v>
       </c>
       <c r="L47" t="n">
-        <v>11.93</v>
+        <v>12.82</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>70.72</v>
+        <v>66.98</v>
       </c>
       <c r="K48" t="n">
-        <v>-80.88</v>
+        <v>-76.59999999999999</v>
       </c>
       <c r="L48" t="n">
-        <v>107.43</v>
+        <v>101.76</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>-53.92</v>
+        <v>-56.86</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.18</v>
+        <v>-0.19</v>
       </c>
       <c r="L49" t="n">
-        <v>53.92</v>
+        <v>56.86</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>28</v>
       </c>
       <c r="J50" t="n">
-        <v>-106.73</v>
+        <v>-104.21</v>
       </c>
       <c r="K50" t="n">
-        <v>27.89</v>
+        <v>27.23</v>
       </c>
       <c r="L50" t="n">
-        <v>110.31</v>
+        <v>107.71</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>29</v>
       </c>
       <c r="J51" t="n">
-        <v>12.31</v>
+        <v>12.21</v>
       </c>
       <c r="K51" t="n">
-        <v>-97.79000000000001</v>
+        <v>-96.95</v>
       </c>
       <c r="L51" t="n">
-        <v>98.56</v>
+        <v>97.72</v>
       </c>
     </row>
     <row r="52">
@@ -2239,10 +2239,10 @@
         <v>0.72</v>
       </c>
       <c r="K52" t="n">
-        <v>-87.27</v>
+        <v>-88.26000000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>87.27</v>
+        <v>88.26000000000001</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>30</v>
       </c>
       <c r="J53" t="n">
-        <v>65.29000000000001</v>
+        <v>65.66</v>
       </c>
       <c r="K53" t="n">
-        <v>110.67</v>
+        <v>111.29</v>
       </c>
       <c r="L53" t="n">
-        <v>128.5</v>
+        <v>129.21</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>29.29</v>
+        <v>32.22</v>
       </c>
       <c r="K54" t="n">
-        <v>73.48999999999999</v>
+        <v>80.84</v>
       </c>
       <c r="L54" t="n">
-        <v>79.11</v>
+        <v>87.03</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>-56.57</v>
+        <v>-55.44</v>
       </c>
       <c r="K55" t="n">
-        <v>-152.78</v>
+        <v>-149.74</v>
       </c>
       <c r="L55" t="n">
-        <v>162.91</v>
+        <v>159.68</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>29</v>
       </c>
       <c r="J56" t="n">
-        <v>-59.46</v>
+        <v>-60.06</v>
       </c>
       <c r="K56" t="n">
-        <v>-154.92</v>
+        <v>-156.5</v>
       </c>
       <c r="L56" t="n">
-        <v>165.94</v>
+        <v>167.63</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>29</v>
       </c>
       <c r="J57" t="n">
-        <v>132.71</v>
+        <v>139.24</v>
       </c>
       <c r="K57" t="n">
-        <v>-27.04</v>
+        <v>-28.37</v>
       </c>
       <c r="L57" t="n">
-        <v>135.44</v>
+        <v>142.1</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>26</v>
       </c>
       <c r="J58" t="n">
-        <v>158.92</v>
+        <v>155.67</v>
       </c>
       <c r="K58" t="n">
-        <v>-142.05</v>
+        <v>-139.14</v>
       </c>
       <c r="L58" t="n">
-        <v>213.15</v>
+        <v>208.79</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>22.44</v>
+        <v>22.72</v>
       </c>
       <c r="K59" t="n">
-        <v>-41.64</v>
+        <v>-42.16</v>
       </c>
       <c r="L59" t="n">
-        <v>47.31</v>
+        <v>47.89</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>29</v>
       </c>
       <c r="J60" t="n">
-        <v>37.62</v>
+        <v>39.95</v>
       </c>
       <c r="K60" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L60" t="n">
-        <v>37.63</v>
+        <v>39.97</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>29</v>
       </c>
       <c r="J61" t="n">
-        <v>-41.07</v>
+        <v>-42.69</v>
       </c>
       <c r="K61" t="n">
-        <v>-14.31</v>
+        <v>-14.88</v>
       </c>
       <c r="L61" t="n">
-        <v>43.49</v>
+        <v>45.21</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>-27.9</v>
+        <v>-29.16</v>
       </c>
       <c r="K62" t="n">
-        <v>45.38</v>
+        <v>47.43</v>
       </c>
       <c r="L62" t="n">
-        <v>53.27</v>
+        <v>55.68</v>
       </c>
     </row>
     <row r="63">
@@ -2701,10 +2701,10 @@
         <v>1.45</v>
       </c>
       <c r="K63" t="n">
-        <v>63.58</v>
+        <v>63.57</v>
       </c>
       <c r="L63" t="n">
-        <v>63.6</v>
+        <v>63.59</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>28</v>
       </c>
       <c r="J64" t="n">
-        <v>-13.21</v>
+        <v>-12.53</v>
       </c>
       <c r="K64" t="n">
-        <v>-95.14</v>
+        <v>-90.26000000000001</v>
       </c>
       <c r="L64" t="n">
-        <v>96.05</v>
+        <v>91.12</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>27</v>
       </c>
       <c r="J65" t="n">
-        <v>-73.25</v>
+        <v>-74.92</v>
       </c>
       <c r="K65" t="n">
-        <v>28.05</v>
+        <v>28.69</v>
       </c>
       <c r="L65" t="n">
-        <v>78.44</v>
+        <v>80.23</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-63.56</v>
+        <v>-64.5</v>
       </c>
       <c r="K66" t="n">
-        <v>-61.2</v>
+        <v>-62.1</v>
       </c>
       <c r="L66" t="n">
-        <v>88.23</v>
+        <v>89.53</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>27</v>
       </c>
       <c r="J67" t="n">
-        <v>88.97</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="K67" t="n">
-        <v>-51.84</v>
+        <v>-51.42</v>
       </c>
       <c r="L67" t="n">
-        <v>102.97</v>
+        <v>102.13</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>114.3</v>
+        <v>118.74</v>
       </c>
       <c r="K68" t="n">
-        <v>-7.33</v>
+        <v>-7.61</v>
       </c>
       <c r="L68" t="n">
-        <v>114.53</v>
+        <v>118.98</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>-44.95</v>
+        <v>-49.52</v>
       </c>
       <c r="K69" t="n">
-        <v>64.26000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="L69" t="n">
-        <v>78.42</v>
+        <v>86.40000000000001</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>28</v>
       </c>
       <c r="J70" t="n">
-        <v>88.69</v>
+        <v>88.16</v>
       </c>
       <c r="K70" t="n">
-        <v>140.38</v>
+        <v>139.53</v>
       </c>
       <c r="L70" t="n">
-        <v>166.04</v>
+        <v>165.05</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>-44.59</v>
+        <v>-43.21</v>
       </c>
       <c r="K71" t="n">
-        <v>-231.29</v>
+        <v>-224.14</v>
       </c>
       <c r="L71" t="n">
-        <v>235.55</v>
+        <v>228.26</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>24</v>
       </c>
       <c r="J72" t="n">
-        <v>-182.09</v>
+        <v>-182.92</v>
       </c>
       <c r="K72" t="n">
-        <v>57.68</v>
+        <v>57.94</v>
       </c>
       <c r="L72" t="n">
-        <v>191.01</v>
+        <v>191.88</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>30</v>
       </c>
       <c r="J73" t="n">
-        <v>69.25</v>
+        <v>67.59</v>
       </c>
       <c r="K73" t="n">
-        <v>202.7</v>
+        <v>197.86</v>
       </c>
       <c r="L73" t="n">
-        <v>214.21</v>
+        <v>209.08</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>24.3</v>
+        <v>25.45</v>
       </c>
       <c r="K74" t="n">
-        <v>-34.86</v>
+        <v>-36.5</v>
       </c>
       <c r="L74" t="n">
-        <v>42.49</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>65.09999999999999</v>
+        <v>63.72</v>
       </c>
       <c r="K75" t="n">
-        <v>14.04</v>
+        <v>13.75</v>
       </c>
       <c r="L75" t="n">
-        <v>66.59999999999999</v>
+        <v>65.19</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>28</v>
       </c>
       <c r="J76" t="n">
-        <v>-53.06</v>
+        <v>-51.76</v>
       </c>
       <c r="K76" t="n">
-        <v>-37.9</v>
+        <v>-36.97</v>
       </c>
       <c r="L76" t="n">
-        <v>65.2</v>
+        <v>63.61</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>26</v>
       </c>
       <c r="J77" t="n">
-        <v>-66.47</v>
+        <v>-66.20999999999999</v>
       </c>
       <c r="K77" t="n">
-        <v>14.56</v>
+        <v>14.5</v>
       </c>
       <c r="L77" t="n">
-        <v>68.05</v>
+        <v>67.78</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>29</v>
       </c>
       <c r="J78" t="n">
-        <v>-41.09</v>
+        <v>-42.69</v>
       </c>
       <c r="K78" t="n">
-        <v>35.98</v>
+        <v>37.37</v>
       </c>
       <c r="L78" t="n">
-        <v>54.61</v>
+        <v>56.73</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>-53.13</v>
+        <v>-55.62</v>
       </c>
       <c r="K79" t="n">
-        <v>-11</v>
+        <v>-11.51</v>
       </c>
       <c r="L79" t="n">
-        <v>54.25</v>
+        <v>56.79</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>-100.32</v>
+        <v>-96.65000000000001</v>
       </c>
       <c r="K80" t="n">
-        <v>-71.79000000000001</v>
+        <v>-69.16</v>
       </c>
       <c r="L80" t="n">
-        <v>123.36</v>
+        <v>118.85</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>77.8</v>
+        <v>80.61</v>
       </c>
       <c r="K81" t="n">
-        <v>-11.01</v>
+        <v>-11.41</v>
       </c>
       <c r="L81" t="n">
-        <v>78.56999999999999</v>
+        <v>81.42</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>26</v>
       </c>
       <c r="J82" t="n">
-        <v>-44</v>
+        <v>-46.96</v>
       </c>
       <c r="K82" t="n">
-        <v>53.59</v>
+        <v>57.19</v>
       </c>
       <c r="L82" t="n">
-        <v>69.34</v>
+        <v>74</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>30</v>
       </c>
       <c r="J83" t="n">
+        <v>91.76000000000001</v>
+      </c>
+      <c r="K83" t="n">
         <v>93.29000000000001</v>
       </c>
-      <c r="K83" t="n">
-        <v>94.84</v>
-      </c>
       <c r="L83" t="n">
-        <v>133.03</v>
+        <v>130.85</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>29</v>
       </c>
       <c r="J84" t="n">
-        <v>-108.79</v>
+        <v>-111.98</v>
       </c>
       <c r="K84" t="n">
-        <v>-20.39</v>
+        <v>-20.99</v>
       </c>
       <c r="L84" t="n">
-        <v>110.68</v>
+        <v>113.93</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>-89.56999999999999</v>
+        <v>-88.66</v>
       </c>
       <c r="K85" t="n">
-        <v>-121.53</v>
+        <v>-120.29</v>
       </c>
       <c r="L85" t="n">
-        <v>150.98</v>
+        <v>149.44</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>124.64</v>
+        <v>120.48</v>
       </c>
       <c r="K86" t="n">
-        <v>196.13</v>
+        <v>189.58</v>
       </c>
       <c r="L86" t="n">
-        <v>232.38</v>
+        <v>224.63</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>-48.07</v>
+        <v>-51.19</v>
       </c>
       <c r="K87" t="n">
-        <v>118.25</v>
+        <v>125.93</v>
       </c>
       <c r="L87" t="n">
-        <v>127.65</v>
+        <v>135.93</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>28</v>
       </c>
       <c r="J88" t="n">
-        <v>134.11</v>
+        <v>135.65</v>
       </c>
       <c r="K88" t="n">
-        <v>90.36</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="L88" t="n">
-        <v>161.71</v>
+        <v>163.57</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-10.xlsx
+++ b/output/2024-07-10.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.88</v>
+        <v>2.54</v>
       </c>
       <c r="F14" t="n">
-        <v>8.699999999999999</v>
+        <v>7.69</v>
       </c>
       <c r="G14" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="H14" t="n">
         <v>17.6</v>
       </c>
-      <c r="H14" t="n">
-        <v>16.4</v>
-      </c>
       <c r="I14" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="J14" t="n">
-        <v>-34.36</v>
+        <v>-61.92</v>
       </c>
       <c r="K14" t="n">
-        <v>-24.84</v>
+        <v>-10.23</v>
       </c>
       <c r="L14" t="n">
-        <v>42.4</v>
+        <v>62.76</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:46:29</t>
+          <t>04:45:52</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.71</v>
+        <v>2.43</v>
       </c>
       <c r="F15" t="n">
-        <v>8.44</v>
+        <v>5.93</v>
       </c>
       <c r="G15" t="n">
-        <v>8</v>
+        <v>349</v>
       </c>
       <c r="H15" t="n">
-        <v>26.4</v>
+        <v>16</v>
       </c>
       <c r="I15" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="J15" t="n">
-        <v>55.02</v>
+        <v>-56.99</v>
       </c>
       <c r="K15" t="n">
-        <v>44.3</v>
+        <v>-34.44</v>
       </c>
       <c r="L15" t="n">
-        <v>70.64</v>
+        <v>66.59</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:48:24</t>
+          <t>04:47:36</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.17</v>
+        <v>2.68</v>
       </c>
       <c r="F16" t="n">
-        <v>9.01</v>
+        <v>4.92</v>
       </c>
       <c r="G16" t="n">
-        <v>5.9</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>21.6</v>
+        <v>15.9</v>
       </c>
       <c r="I16" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J16" t="n">
-        <v>-40.8</v>
+        <v>-37.91</v>
       </c>
       <c r="K16" t="n">
-        <v>-7.34</v>
+        <v>45.97</v>
       </c>
       <c r="L16" t="n">
-        <v>41.46</v>
+        <v>59.59</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:52:38</t>
+          <t>04:53:02</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="F17" t="n">
-        <v>7.25</v>
+        <v>5.31</v>
       </c>
       <c r="G17" t="n">
-        <v>2.8</v>
+        <v>18.3</v>
       </c>
       <c r="H17" t="n">
-        <v>23.4</v>
+        <v>19</v>
       </c>
       <c r="I17" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J17" t="n">
-        <v>-56.44</v>
+        <v>-3.92</v>
       </c>
       <c r="K17" t="n">
-        <v>-34.39</v>
+        <v>-66.41</v>
       </c>
       <c r="L17" t="n">
-        <v>66.09</v>
+        <v>66.52</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:54:32</t>
+          <t>04:54:24</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.7</v>
+        <v>3.13</v>
       </c>
       <c r="F18" t="n">
-        <v>7.85</v>
+        <v>6.73</v>
       </c>
       <c r="G18" t="n">
-        <v>2.5</v>
+        <v>359.4</v>
       </c>
       <c r="H18" t="n">
-        <v>14.8</v>
+        <v>19.1</v>
       </c>
       <c r="I18" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>-37.45</v>
+        <v>-71.72</v>
       </c>
       <c r="K18" t="n">
-        <v>45.39</v>
+        <v>-33.83</v>
       </c>
       <c r="L18" t="n">
-        <v>58.85</v>
+        <v>79.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:56:23</t>
+          <t>04:55:35</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.39</v>
+        <v>2.55</v>
       </c>
       <c r="F19" t="n">
-        <v>8.720000000000001</v>
+        <v>3.89</v>
       </c>
       <c r="G19" t="n">
-        <v>8.699999999999999</v>
+        <v>359</v>
       </c>
       <c r="H19" t="n">
-        <v>22.8</v>
+        <v>21.6</v>
       </c>
       <c r="I19" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.75</v>
+        <v>26.76</v>
       </c>
       <c r="K19" t="n">
-        <v>-45.67</v>
+        <v>-65.90000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>45.82</v>
+        <v>71.13</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:00:22</t>
+          <t>05:00:24</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.15</v>
+        <v>2.76</v>
       </c>
       <c r="F20" t="n">
-        <v>7.78</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>8.9</v>
+        <v>10.3</v>
       </c>
       <c r="H20" t="n">
-        <v>16.2</v>
+        <v>21.1</v>
       </c>
       <c r="I20" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J20" t="n">
-        <v>-79.03</v>
+        <v>-59.49</v>
       </c>
       <c r="K20" t="n">
-        <v>-38.06</v>
+        <v>-89.68000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>87.72</v>
+        <v>107.62</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:02:30</t>
+          <t>05:01:12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.57</v>
+        <v>3.03</v>
       </c>
       <c r="F21" t="n">
-        <v>7.76</v>
+        <v>6.77</v>
       </c>
       <c r="G21" t="n">
-        <v>13.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>17.1</v>
+        <v>23.8</v>
       </c>
       <c r="I21" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>29.69</v>
+        <v>106.71</v>
       </c>
       <c r="K21" t="n">
-        <v>-69.48</v>
+        <v>-49.8</v>
       </c>
       <c r="L21" t="n">
-        <v>75.55</v>
+        <v>117.76</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:04:20</t>
+          <t>05:03:03</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="F22" t="n">
-        <v>8.32</v>
+        <v>5.27</v>
       </c>
       <c r="G22" t="n">
-        <v>12.8</v>
+        <v>4.7</v>
       </c>
       <c r="H22" t="n">
-        <v>23.2</v>
+        <v>15.6</v>
       </c>
       <c r="I22" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="J22" t="n">
-        <v>-33.93</v>
+        <v>83.81999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>-59.54</v>
+        <v>79.14</v>
       </c>
       <c r="L22" t="n">
-        <v>68.53</v>
+        <v>115.28</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:08:31</t>
+          <t>05:07:25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="F23" t="n">
-        <v>8.27</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>18.3</v>
+        <v>13.2</v>
       </c>
       <c r="H23" t="n">
-        <v>19.1</v>
+        <v>20.7</v>
       </c>
       <c r="I23" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J23" t="n">
-        <v>96.18000000000001</v>
+        <v>-179.02</v>
       </c>
       <c r="K23" t="n">
-        <v>-53.69</v>
+        <v>-67.72</v>
       </c>
       <c r="L23" t="n">
-        <v>110.16</v>
+        <v>191.41</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:09:40</t>
+          <t>05:09:13</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.8</v>
+        <v>2.42</v>
       </c>
       <c r="F24" t="n">
-        <v>8.039999999999999</v>
+        <v>9.16</v>
       </c>
       <c r="G24" t="n">
-        <v>2</v>
+        <v>22.4</v>
       </c>
       <c r="H24" t="n">
-        <v>14.7</v>
+        <v>10.9</v>
       </c>
       <c r="I24" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>93.29000000000001</v>
+        <v>158.81</v>
       </c>
       <c r="K24" t="n">
-        <v>82.48999999999999</v>
+        <v>105.94</v>
       </c>
       <c r="L24" t="n">
-        <v>124.53</v>
+        <v>190.9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:10:59</t>
+          <t>05:10:00</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.81</v>
+        <v>3.08</v>
       </c>
       <c r="F25" t="n">
-        <v>8.460000000000001</v>
+        <v>5.82</v>
       </c>
       <c r="G25" t="n">
-        <v>12.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>21.3</v>
+        <v>21.7</v>
       </c>
       <c r="I25" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="J25" t="n">
-        <v>-124.97</v>
+        <v>-8.93</v>
       </c>
       <c r="K25" t="n">
-        <v>-62.26</v>
+        <v>-124.64</v>
       </c>
       <c r="L25" t="n">
-        <v>139.62</v>
+        <v>124.96</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:15:16</t>
+          <t>05:15:04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="F26" t="n">
-        <v>8.93</v>
+        <v>6.74</v>
       </c>
       <c r="G26" t="n">
-        <v>352.5</v>
+        <v>3.7</v>
       </c>
       <c r="H26" t="n">
-        <v>26.2</v>
+        <v>11.8</v>
       </c>
       <c r="I26" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J26" t="n">
-        <v>132.26</v>
+        <v>-97.45</v>
       </c>
       <c r="K26" t="n">
-        <v>82.91</v>
+        <v>256.72</v>
       </c>
       <c r="L26" t="n">
-        <v>156.1</v>
+        <v>274.6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:17:36</t>
+          <t>05:17:13</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="F27" t="n">
-        <v>8.210000000000001</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>14</v>
+        <v>16.8</v>
       </c>
       <c r="H27" t="n">
-        <v>19.2</v>
+        <v>20.1</v>
       </c>
       <c r="I27" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J27" t="n">
-        <v>-8.85</v>
+        <v>-275.18</v>
       </c>
       <c r="K27" t="n">
-        <v>-137.55</v>
+        <v>70.62</v>
       </c>
       <c r="L27" t="n">
-        <v>137.84</v>
+        <v>284.1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:19:33</t>
+          <t>05:18:57</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.43</v>
+        <v>2.82</v>
       </c>
       <c r="F28" t="n">
-        <v>7.99</v>
+        <v>6.52</v>
       </c>
       <c r="G28" t="n">
-        <v>354.2</v>
+        <v>11.2</v>
       </c>
       <c r="H28" t="n">
         <v>20.4</v>
       </c>
       <c r="I28" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-74.89</v>
+        <v>2.11</v>
       </c>
       <c r="K28" t="n">
-        <v>156.69</v>
+        <v>-186.85</v>
       </c>
       <c r="L28" t="n">
-        <v>173.67</v>
+        <v>186.87</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:28:19</t>
+          <t>05:31:40</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.43</v>
+        <v>2.82</v>
       </c>
       <c r="F29" t="n">
-        <v>8.640000000000001</v>
+        <v>6.79</v>
       </c>
       <c r="G29" t="n">
-        <v>11</v>
+        <v>15.3</v>
       </c>
       <c r="H29" t="n">
-        <v>25.4</v>
+        <v>23.7</v>
       </c>
       <c r="I29" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>-56.07</v>
+        <v>7.83</v>
       </c>
       <c r="K29" t="n">
-        <v>1.65</v>
+        <v>-62.84</v>
       </c>
       <c r="L29" t="n">
-        <v>56.1</v>
+        <v>63.32</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:29:15</t>
+          <t>05:33:56</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.85</v>
+        <v>2.78</v>
       </c>
       <c r="F30" t="n">
-        <v>8.359999999999999</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G30" t="n">
-        <v>11.4</v>
+        <v>19.1</v>
       </c>
       <c r="H30" t="n">
-        <v>17.3</v>
+        <v>22.7</v>
       </c>
       <c r="I30" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="J30" t="n">
-        <v>-3.68</v>
+        <v>-33.81</v>
       </c>
       <c r="K30" t="n">
-        <v>-44.91</v>
+        <v>-51.16</v>
       </c>
       <c r="L30" t="n">
-        <v>45.06</v>
+        <v>61.33</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:30:48</t>
+          <t>05:36:48</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.82</v>
+        <v>3.23</v>
       </c>
       <c r="F31" t="n">
-        <v>8.57</v>
+        <v>6.38</v>
       </c>
       <c r="G31" t="n">
-        <v>18.1</v>
+        <v>21.9</v>
       </c>
       <c r="H31" t="n">
-        <v>22.3</v>
+        <v>20.2</v>
       </c>
       <c r="I31" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J31" t="n">
-        <v>5.94</v>
+        <v>-0.25</v>
       </c>
       <c r="K31" t="n">
-        <v>-49.88</v>
+        <v>87.84</v>
       </c>
       <c r="L31" t="n">
-        <v>50.23</v>
+        <v>87.84</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:34:32</t>
+          <t>05:41:11</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.78</v>
+        <v>2.37</v>
       </c>
       <c r="F32" t="n">
-        <v>8.76</v>
+        <v>4.88</v>
       </c>
       <c r="G32" t="n">
-        <v>16.2</v>
+        <v>16.9</v>
       </c>
       <c r="H32" t="n">
-        <v>24.7</v>
+        <v>10.8</v>
       </c>
       <c r="I32" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>-26.08</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>-39.24</v>
+        <v>31.56</v>
       </c>
       <c r="L32" t="n">
-        <v>47.11</v>
+        <v>72.54000000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:36:43</t>
+          <t>05:42:19</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3.23</v>
+        <v>2.94</v>
       </c>
       <c r="F33" t="n">
-        <v>8.9</v>
+        <v>6.62</v>
       </c>
       <c r="G33" t="n">
-        <v>11.1</v>
+        <v>9.5</v>
       </c>
       <c r="H33" t="n">
-        <v>23.6</v>
+        <v>23.3</v>
       </c>
       <c r="I33" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.59</v>
+        <v>-86.81999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>74.38</v>
+        <v>20.24</v>
       </c>
       <c r="L33" t="n">
-        <v>74.39</v>
+        <v>89.15000000000001</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:38:45</t>
+          <t>05:44:06</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.36</v>
+        <v>2.64</v>
       </c>
       <c r="F34" t="n">
-        <v>8.65</v>
+        <v>6.7</v>
       </c>
       <c r="G34" t="n">
-        <v>352.3</v>
+        <v>12.3</v>
       </c>
       <c r="H34" t="n">
-        <v>16.1</v>
+        <v>17.8</v>
       </c>
       <c r="I34" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>51.65</v>
+        <v>99.25</v>
       </c>
       <c r="K34" t="n">
-        <v>23.94</v>
+        <v>41.24</v>
       </c>
       <c r="L34" t="n">
-        <v>56.93</v>
+        <v>107.48</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:42:16</t>
+          <t>05:47:55</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.94</v>
+        <v>3.22</v>
       </c>
       <c r="F35" t="n">
-        <v>8.279999999999999</v>
+        <v>5.99</v>
       </c>
       <c r="G35" t="n">
-        <v>17.3</v>
+        <v>15.5</v>
       </c>
       <c r="H35" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I35" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>-94.39</v>
+        <v>-153.4</v>
       </c>
       <c r="K35" t="n">
-        <v>21.91</v>
+        <v>89.19</v>
       </c>
       <c r="L35" t="n">
-        <v>96.90000000000001</v>
+        <v>177.44</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:43:34</t>
+          <t>05:49:15</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="F36" t="n">
-        <v>8.42</v>
+        <v>8.99</v>
       </c>
       <c r="G36" t="n">
-        <v>6.3</v>
+        <v>12.9</v>
       </c>
       <c r="H36" t="n">
-        <v>18.6</v>
+        <v>20.3</v>
       </c>
       <c r="I36" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>116.11</v>
+        <v>50.07</v>
       </c>
       <c r="K36" t="n">
-        <v>48.41</v>
+        <v>-138.55</v>
       </c>
       <c r="L36" t="n">
-        <v>125.79</v>
+        <v>147.32</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:45:41</t>
+          <t>05:50:15</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.21</v>
+        <v>2.76</v>
       </c>
       <c r="F37" t="n">
-        <v>8.58</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="G37" t="n">
-        <v>16.8</v>
+        <v>4.5</v>
       </c>
       <c r="H37" t="n">
-        <v>19.5</v>
+        <v>14.6</v>
       </c>
       <c r="I37" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J37" t="n">
-        <v>-139.62</v>
+        <v>-64.70999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>73.79000000000001</v>
+        <v>85.45</v>
       </c>
       <c r="L37" t="n">
-        <v>157.92</v>
+        <v>107.19</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:50:30</t>
+          <t>05:54:37</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.89</v>
+        <v>2.69</v>
       </c>
       <c r="F38" t="n">
-        <v>8.449999999999999</v>
+        <v>9.08</v>
       </c>
       <c r="G38" t="n">
-        <v>11.3</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>22.5</v>
+        <v>24</v>
       </c>
       <c r="I38" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J38" t="n">
-        <v>42.43</v>
+        <v>153.42</v>
       </c>
       <c r="K38" t="n">
-        <v>-128.66</v>
+        <v>191.18</v>
       </c>
       <c r="L38" t="n">
-        <v>135.47</v>
+        <v>245.13</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:52:21</t>
+          <t>05:56:08</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1678,31 +1678,31 @@
         <v>2.77</v>
       </c>
       <c r="F39" t="n">
-        <v>8.029999999999999</v>
+        <v>5.85</v>
       </c>
       <c r="G39" t="n">
-        <v>360</v>
+        <v>16.7</v>
       </c>
       <c r="H39" t="n">
-        <v>25.2</v>
+        <v>19.6</v>
       </c>
       <c r="I39" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="J39" t="n">
-        <v>-67.23999999999999</v>
+        <v>-114.15</v>
       </c>
       <c r="K39" t="n">
-        <v>76.23999999999999</v>
+        <v>67.45999999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>101.66</v>
+        <v>132.6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:54:28</t>
+          <t>05:57:41</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.69</v>
+        <v>2.79</v>
       </c>
       <c r="F40" t="n">
-        <v>7.85</v>
+        <v>8.81</v>
       </c>
       <c r="G40" t="n">
-        <v>18.7</v>
+        <v>11</v>
       </c>
       <c r="H40" t="n">
-        <v>23.9</v>
+        <v>21.1</v>
       </c>
       <c r="I40" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>117.51</v>
+        <v>111.97</v>
       </c>
       <c r="K40" t="n">
-        <v>129.18</v>
+        <v>148.68</v>
       </c>
       <c r="L40" t="n">
-        <v>174.63</v>
+        <v>186.13</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>05:58:27</t>
+          <t>06:02:07</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.78</v>
+        <v>2.61</v>
       </c>
       <c r="F41" t="n">
-        <v>8.640000000000001</v>
+        <v>7.53</v>
       </c>
       <c r="G41" t="n">
-        <v>10</v>
+        <v>12.7</v>
       </c>
       <c r="H41" t="n">
-        <v>15.2</v>
+        <v>20.5</v>
       </c>
       <c r="I41" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J41" t="n">
-        <v>-133.85</v>
+        <v>-146.69</v>
       </c>
       <c r="K41" t="n">
-        <v>27.85</v>
+        <v>261.63</v>
       </c>
       <c r="L41" t="n">
-        <v>136.71</v>
+        <v>299.95</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>05:59:17</t>
+          <t>06:03:10</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.79</v>
+        <v>2.84</v>
       </c>
       <c r="F42" t="n">
-        <v>8.359999999999999</v>
+        <v>6.83</v>
       </c>
       <c r="G42" t="n">
-        <v>12.8</v>
+        <v>356</v>
       </c>
       <c r="H42" t="n">
-        <v>22.5</v>
+        <v>15.6</v>
       </c>
       <c r="I42" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>105.31</v>
+        <v>275.85</v>
       </c>
       <c r="K42" t="n">
-        <v>120.56</v>
+        <v>-172.12</v>
       </c>
       <c r="L42" t="n">
-        <v>160.08</v>
+        <v>325.14</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:00:50</t>
+          <t>06:04:19</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="F43" t="n">
-        <v>8.44</v>
+        <v>6.95</v>
       </c>
       <c r="G43" t="n">
-        <v>11.8</v>
+        <v>5.3</v>
       </c>
       <c r="H43" t="n">
-        <v>17.9</v>
+        <v>19.2</v>
       </c>
       <c r="I43" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>-109.17</v>
+        <v>-319.58</v>
       </c>
       <c r="K43" t="n">
-        <v>155.22</v>
+        <v>-102.74</v>
       </c>
       <c r="L43" t="n">
-        <v>189.77</v>
+        <v>335.69</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:09:16</t>
+          <t>06:16:28</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.85</v>
+        <v>3.12</v>
       </c>
       <c r="F44" t="n">
-        <v>7.6</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G44" t="n">
-        <v>1.9</v>
+        <v>351.9</v>
       </c>
       <c r="H44" t="n">
-        <v>17.5</v>
+        <v>21.4</v>
       </c>
       <c r="I44" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>60.95</v>
+        <v>66.27</v>
       </c>
       <c r="K44" t="n">
-        <v>-49.11</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="L44" t="n">
-        <v>78.27</v>
+        <v>106.63</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:11:09</t>
+          <t>06:17:36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.6</v>
+        <v>3.23</v>
       </c>
       <c r="F45" t="n">
-        <v>8.07</v>
+        <v>6.67</v>
       </c>
       <c r="G45" t="n">
-        <v>9.1</v>
+        <v>22.4</v>
       </c>
       <c r="H45" t="n">
-        <v>22.9</v>
+        <v>19.7</v>
       </c>
       <c r="I45" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="J45" t="n">
-        <v>-69.81999999999999</v>
+        <v>4.47</v>
       </c>
       <c r="K45" t="n">
-        <v>-33</v>
+        <v>15.4</v>
       </c>
       <c r="L45" t="n">
-        <v>77.23</v>
+        <v>16.04</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:13:14</t>
+          <t>06:19:53</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>3.11</v>
+        <v>2.98</v>
       </c>
       <c r="F46" t="n">
-        <v>7.4</v>
+        <v>6.97</v>
       </c>
       <c r="G46" t="n">
-        <v>13.4</v>
+        <v>20.9</v>
       </c>
       <c r="H46" t="n">
-        <v>25.2</v>
+        <v>15.4</v>
       </c>
       <c r="I46" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>50.79</v>
+        <v>72.78</v>
       </c>
       <c r="K46" t="n">
-        <v>62.83</v>
+        <v>-82.63</v>
       </c>
       <c r="L46" t="n">
-        <v>80.79000000000001</v>
+        <v>110.11</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:18:11</t>
+          <t>06:23:13</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>3.23</v>
+        <v>2.73</v>
       </c>
       <c r="F47" t="n">
-        <v>8.93</v>
+        <v>7.52</v>
       </c>
       <c r="G47" t="n">
-        <v>10</v>
+        <v>10.4</v>
       </c>
       <c r="H47" t="n">
-        <v>19.4</v>
+        <v>21.3</v>
       </c>
       <c r="I47" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>2.63</v>
+        <v>-75.18000000000001</v>
       </c>
       <c r="K47" t="n">
-        <v>12.54</v>
+        <v>4</v>
       </c>
       <c r="L47" t="n">
-        <v>12.82</v>
+        <v>75.29000000000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:19:08</t>
+          <t>06:24:35</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.98</v>
+        <v>2.73</v>
       </c>
       <c r="F48" t="n">
-        <v>8.85</v>
+        <v>7.12</v>
       </c>
       <c r="G48" t="n">
-        <v>1.4</v>
+        <v>5.6</v>
       </c>
       <c r="H48" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="I48" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>66.98</v>
+        <v>-104.99</v>
       </c>
       <c r="K48" t="n">
-        <v>-76.59999999999999</v>
+        <v>27.48</v>
       </c>
       <c r="L48" t="n">
-        <v>101.76</v>
+        <v>108.53</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:19:59</t>
+          <t>06:26:37</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.72</v>
+        <v>2.83</v>
       </c>
       <c r="F49" t="n">
-        <v>8.33</v>
+        <v>6.43</v>
       </c>
       <c r="G49" t="n">
-        <v>13.3</v>
+        <v>12</v>
       </c>
       <c r="H49" t="n">
-        <v>14.3</v>
+        <v>16.1</v>
       </c>
       <c r="I49" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>-56.86</v>
+        <v>11.9</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.19</v>
+        <v>-88.93000000000001</v>
       </c>
       <c r="L49" t="n">
-        <v>56.86</v>
+        <v>89.72</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:24:25</t>
+          <t>06:30:54</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.73</v>
+        <v>2.68</v>
       </c>
       <c r="F50" t="n">
-        <v>8.08</v>
+        <v>6.82</v>
       </c>
       <c r="G50" t="n">
-        <v>6.9</v>
+        <v>12.4</v>
       </c>
       <c r="H50" t="n">
-        <v>18.6</v>
+        <v>20.2</v>
       </c>
       <c r="I50" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>-104.21</v>
+        <v>3.95</v>
       </c>
       <c r="K50" t="n">
-        <v>27.23</v>
+        <v>-123.57</v>
       </c>
       <c r="L50" t="n">
-        <v>107.71</v>
+        <v>123.64</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:26:45</t>
+          <t>06:32:42</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.83</v>
+        <v>3.21</v>
       </c>
       <c r="F51" t="n">
-        <v>8.4</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="G51" t="n">
-        <v>3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H51" t="n">
-        <v>20.9</v>
+        <v>22.1</v>
       </c>
       <c r="I51" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="J51" t="n">
-        <v>12.21</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>-96.95</v>
+        <v>125.61</v>
       </c>
       <c r="L51" t="n">
-        <v>97.72</v>
+        <v>142.99</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:28:40</t>
+          <t>06:34:25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.67</v>
+        <v>3.29</v>
       </c>
       <c r="F52" t="n">
-        <v>8.42</v>
+        <v>8.19</v>
       </c>
       <c r="G52" t="n">
-        <v>11.1</v>
+        <v>11.7</v>
       </c>
       <c r="H52" t="n">
-        <v>18.2</v>
+        <v>16.7</v>
       </c>
       <c r="I52" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>0.72</v>
+        <v>35.3</v>
       </c>
       <c r="K52" t="n">
-        <v>-88.26000000000001</v>
+        <v>87.41</v>
       </c>
       <c r="L52" t="n">
-        <v>88.26000000000001</v>
+        <v>94.27</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:32:17</t>
+          <t>06:39:00</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.21</v>
+        <v>2.93</v>
       </c>
       <c r="F53" t="n">
-        <v>8.220000000000001</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="G53" t="n">
-        <v>14.9</v>
+        <v>8.5</v>
       </c>
       <c r="H53" t="n">
-        <v>18.6</v>
+        <v>16.6</v>
       </c>
       <c r="I53" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>65.66</v>
+        <v>-77.43000000000001</v>
       </c>
       <c r="K53" t="n">
-        <v>111.29</v>
+        <v>-195.46</v>
       </c>
       <c r="L53" t="n">
-        <v>129.21</v>
+        <v>210.24</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:33:10</t>
+          <t>06:41:00</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3.29</v>
+        <v>2.93</v>
       </c>
       <c r="F54" t="n">
-        <v>8.390000000000001</v>
+        <v>7.89</v>
       </c>
       <c r="G54" t="n">
-        <v>4.1</v>
+        <v>13.2</v>
       </c>
       <c r="H54" t="n">
-        <v>17.4</v>
+        <v>19.6</v>
       </c>
       <c r="I54" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>32.22</v>
+        <v>-65.06999999999999</v>
       </c>
       <c r="K54" t="n">
-        <v>80.84</v>
+        <v>-162.54</v>
       </c>
       <c r="L54" t="n">
-        <v>87.03</v>
+        <v>175.08</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:34:11</t>
+          <t>06:42:19</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="F55" t="n">
-        <v>8.23</v>
+        <v>6.12</v>
       </c>
       <c r="G55" t="n">
-        <v>3.8</v>
+        <v>351</v>
       </c>
       <c r="H55" t="n">
-        <v>24.5</v>
+        <v>24.2</v>
       </c>
       <c r="I55" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J55" t="n">
-        <v>-55.44</v>
+        <v>132.73</v>
       </c>
       <c r="K55" t="n">
-        <v>-149.74</v>
+        <v>7.46</v>
       </c>
       <c r="L55" t="n">
-        <v>159.68</v>
+        <v>132.94</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:38:18</t>
+          <t>06:46:49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.92</v>
+        <v>2.77</v>
       </c>
       <c r="F56" t="n">
-        <v>8.470000000000001</v>
+        <v>7.18</v>
       </c>
       <c r="G56" t="n">
-        <v>9.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="H56" t="n">
-        <v>19</v>
+        <v>18.4</v>
       </c>
       <c r="I56" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>-60.06</v>
+        <v>227.53</v>
       </c>
       <c r="K56" t="n">
-        <v>-156.5</v>
+        <v>-150.74</v>
       </c>
       <c r="L56" t="n">
-        <v>167.63</v>
+        <v>272.93</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:40:34</t>
+          <t>06:48:36</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.9</v>
+        <v>2.48</v>
       </c>
       <c r="F57" t="n">
-        <v>7.35</v>
+        <v>6.6</v>
       </c>
       <c r="G57" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="H57" t="n">
         <v>19.2</v>
       </c>
-      <c r="H57" t="n">
-        <v>22.2</v>
-      </c>
       <c r="I57" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J57" t="n">
-        <v>139.24</v>
+        <v>144.04</v>
       </c>
       <c r="K57" t="n">
-        <v>-28.37</v>
+        <v>-147.18</v>
       </c>
       <c r="L57" t="n">
-        <v>142.1</v>
+        <v>205.94</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:41:09</t>
+          <t>06:50:16</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="F58" t="n">
-        <v>8.1</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G58" t="n">
-        <v>7.5</v>
+        <v>15.3</v>
       </c>
       <c r="H58" t="n">
-        <v>18.3</v>
+        <v>18.9</v>
       </c>
       <c r="I58" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>155.67</v>
+        <v>203.2</v>
       </c>
       <c r="K58" t="n">
-        <v>-139.14</v>
+        <v>117.21</v>
       </c>
       <c r="L58" t="n">
-        <v>208.79</v>
+        <v>234.58</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06:50:28</t>
+          <t>06:59:56</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.48</v>
+        <v>3.07</v>
       </c>
       <c r="F59" t="n">
-        <v>8.380000000000001</v>
+        <v>6.66</v>
       </c>
       <c r="G59" t="n">
-        <v>9</v>
+        <v>21.3</v>
       </c>
       <c r="H59" t="n">
-        <v>18</v>
+        <v>16.9</v>
       </c>
       <c r="I59" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>22.72</v>
+        <v>-59.23</v>
       </c>
       <c r="K59" t="n">
-        <v>-42.16</v>
+        <v>-19.8</v>
       </c>
       <c r="L59" t="n">
-        <v>47.89</v>
+        <v>62.45</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06:52:24</t>
+          <t>07:02:05</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.87</v>
+        <v>3.01</v>
       </c>
       <c r="F60" t="n">
-        <v>8.57</v>
+        <v>8.92</v>
       </c>
       <c r="G60" t="n">
-        <v>8.5</v>
+        <v>358.8</v>
       </c>
       <c r="H60" t="n">
-        <v>24.3</v>
+        <v>19.9</v>
       </c>
       <c r="I60" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>39.95</v>
+        <v>-38.08</v>
       </c>
       <c r="K60" t="n">
-        <v>0.95</v>
+        <v>60.95</v>
       </c>
       <c r="L60" t="n">
-        <v>39.97</v>
+        <v>71.87</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06:54:34</t>
+          <t>07:03:41</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>3.06</v>
+        <v>2.88</v>
       </c>
       <c r="F61" t="n">
-        <v>8.869999999999999</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="G61" t="n">
-        <v>4.5</v>
+        <v>18.3</v>
       </c>
       <c r="H61" t="n">
-        <v>19.2</v>
+        <v>24.2</v>
       </c>
       <c r="I61" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-42.69</v>
+        <v>1.72</v>
       </c>
       <c r="K61" t="n">
-        <v>-14.88</v>
+        <v>75.31</v>
       </c>
       <c r="L61" t="n">
-        <v>45.21</v>
+        <v>75.33</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>06:59:30</t>
+          <t>07:07:47</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="F62" t="n">
-        <v>7.74</v>
+        <v>6.3</v>
       </c>
       <c r="G62" t="n">
-        <v>10.4</v>
+        <v>3.6</v>
       </c>
       <c r="H62" t="n">
-        <v>20.7</v>
+        <v>27.3</v>
       </c>
       <c r="I62" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>-29.16</v>
+        <v>-18.53</v>
       </c>
       <c r="K62" t="n">
-        <v>47.43</v>
+        <v>-126.85</v>
       </c>
       <c r="L62" t="n">
-        <v>55.68</v>
+        <v>128.2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:01:20</t>
+          <t>07:08:51</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="F63" t="n">
-        <v>8.720000000000001</v>
+        <v>6.98</v>
       </c>
       <c r="G63" t="n">
-        <v>19.1</v>
+        <v>2.7</v>
       </c>
       <c r="H63" t="n">
-        <v>25</v>
+        <v>19.7</v>
       </c>
       <c r="I63" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>1.45</v>
+        <v>-80.92</v>
       </c>
       <c r="K63" t="n">
-        <v>63.57</v>
+        <v>30.87</v>
       </c>
       <c r="L63" t="n">
-        <v>63.59</v>
+        <v>86.61</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:03:25</t>
+          <t>07:10:49</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.05</v>
+        <v>2.69</v>
       </c>
       <c r="F64" t="n">
-        <v>7.98</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="G64" t="n">
-        <v>25.3</v>
+        <v>7.6</v>
       </c>
       <c r="H64" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I64" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>-12.53</v>
+        <v>-61.64</v>
       </c>
       <c r="K64" t="n">
-        <v>-90.26000000000001</v>
+        <v>-59.16</v>
       </c>
       <c r="L64" t="n">
-        <v>91.12</v>
+        <v>85.44</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:07:30</t>
+          <t>07:14:41</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.7</v>
+        <v>3.45</v>
       </c>
       <c r="F65" t="n">
-        <v>7.94</v>
+        <v>6.19</v>
       </c>
       <c r="G65" t="n">
-        <v>10.1</v>
+        <v>7.9</v>
       </c>
       <c r="H65" t="n">
-        <v>13.9</v>
+        <v>23.3</v>
       </c>
       <c r="I65" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J65" t="n">
-        <v>-74.92</v>
+        <v>125.86</v>
       </c>
       <c r="K65" t="n">
-        <v>28.69</v>
+        <v>-59.51</v>
       </c>
       <c r="L65" t="n">
-        <v>80.23</v>
+        <v>139.22</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:09:24</t>
+          <t>07:17:21</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.69</v>
+        <v>3.18</v>
       </c>
       <c r="F66" t="n">
-        <v>8.18</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G66" t="n">
-        <v>8.699999999999999</v>
+        <v>8</v>
       </c>
       <c r="H66" t="n">
-        <v>21.6</v>
+        <v>18</v>
       </c>
       <c r="I66" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J66" t="n">
-        <v>-64.5</v>
+        <v>120.33</v>
       </c>
       <c r="K66" t="n">
-        <v>-62.1</v>
+        <v>4.4</v>
       </c>
       <c r="L66" t="n">
-        <v>89.53</v>
+        <v>120.41</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:11:10</t>
+          <t>07:19:15</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>3.44</v>
+        <v>2.89</v>
       </c>
       <c r="F67" t="n">
-        <v>8.199999999999999</v>
+        <v>9.19</v>
       </c>
       <c r="G67" t="n">
-        <v>17.3</v>
+        <v>18.1</v>
       </c>
       <c r="H67" t="n">
-        <v>14.9</v>
+        <v>17</v>
       </c>
       <c r="I67" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>88.23999999999999</v>
+        <v>-34.15</v>
       </c>
       <c r="K67" t="n">
-        <v>-51.42</v>
+        <v>89.56999999999999</v>
       </c>
       <c r="L67" t="n">
-        <v>102.13</v>
+        <v>95.86</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:16:36</t>
+          <t>07:23:48</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>3.18</v>
+        <v>4.12</v>
       </c>
       <c r="F68" t="n">
-        <v>8.199999999999999</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G68" t="n">
-        <v>6.8</v>
+        <v>20.9</v>
       </c>
       <c r="H68" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="I68" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>118.74</v>
+        <v>133.77</v>
       </c>
       <c r="K68" t="n">
-        <v>-7.61</v>
+        <v>221.31</v>
       </c>
       <c r="L68" t="n">
-        <v>118.98</v>
+        <v>258.6</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:18:14</t>
+          <t>07:24:52</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.89</v>
+        <v>3.3</v>
       </c>
       <c r="F69" t="n">
-        <v>8.710000000000001</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G69" t="n">
-        <v>4.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H69" t="n">
-        <v>18</v>
+        <v>17.4</v>
       </c>
       <c r="I69" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>-49.52</v>
+        <v>-43.44</v>
       </c>
       <c r="K69" t="n">
-        <v>70.8</v>
+        <v>-226.64</v>
       </c>
       <c r="L69" t="n">
-        <v>86.40000000000001</v>
+        <v>230.76</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:19:49</t>
+          <t>07:27:11</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>4.11</v>
+        <v>3.4</v>
       </c>
       <c r="F70" t="n">
-        <v>8.85</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G70" t="n">
-        <v>14.2</v>
+        <v>14.9</v>
       </c>
       <c r="H70" t="n">
-        <v>24.6</v>
+        <v>13.9</v>
       </c>
       <c r="I70" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J70" t="n">
-        <v>88.16</v>
+        <v>-162.01</v>
       </c>
       <c r="K70" t="n">
-        <v>139.53</v>
+        <v>83.25</v>
       </c>
       <c r="L70" t="n">
-        <v>165.05</v>
+        <v>182.14</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:24:22</t>
+          <t>07:31:46</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="F71" t="n">
-        <v>8.24</v>
+        <v>8.43</v>
       </c>
       <c r="G71" t="n">
-        <v>5.6</v>
+        <v>2</v>
       </c>
       <c r="H71" t="n">
-        <v>27.4</v>
+        <v>16.3</v>
       </c>
       <c r="I71" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J71" t="n">
-        <v>-43.21</v>
+        <v>94.02</v>
       </c>
       <c r="K71" t="n">
-        <v>-224.14</v>
+        <v>316.53</v>
       </c>
       <c r="L71" t="n">
-        <v>228.26</v>
+        <v>330.2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:26:28</t>
+          <t>07:32:53</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.39</v>
+        <v>2.76</v>
       </c>
       <c r="F72" t="n">
-        <v>8.550000000000001</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G72" t="n">
-        <v>358.5</v>
+        <v>2</v>
       </c>
       <c r="H72" t="n">
-        <v>20.3</v>
+        <v>27.5</v>
       </c>
       <c r="I72" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J72" t="n">
-        <v>-182.92</v>
+        <v>181.72</v>
       </c>
       <c r="K72" t="n">
-        <v>57.94</v>
+        <v>-81.87</v>
       </c>
       <c r="L72" t="n">
-        <v>191.88</v>
+        <v>199.31</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:28:02</t>
+          <t>07:34:02</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="F73" t="n">
-        <v>7.9</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G73" t="n">
-        <v>3.4</v>
+        <v>5.3</v>
       </c>
       <c r="H73" t="n">
-        <v>22.8</v>
+        <v>25.6</v>
       </c>
       <c r="I73" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J73" t="n">
-        <v>67.59</v>
+        <v>271.24</v>
       </c>
       <c r="K73" t="n">
-        <v>197.86</v>
+        <v>120.58</v>
       </c>
       <c r="L73" t="n">
-        <v>209.08</v>
+        <v>296.84</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:40:20</t>
+          <t>07:41:10</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>2.77</v>
+        <v>2.98</v>
       </c>
       <c r="F74" t="n">
-        <v>7.9</v>
+        <v>8.26</v>
       </c>
       <c r="G74" t="n">
-        <v>25.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H74" t="n">
-        <v>24.3</v>
+        <v>21.7</v>
       </c>
       <c r="I74" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J74" t="n">
-        <v>25.45</v>
+        <v>-71.73</v>
       </c>
       <c r="K74" t="n">
-        <v>-36.5</v>
+        <v>-50.39</v>
       </c>
       <c r="L74" t="n">
-        <v>44.5</v>
+        <v>87.66</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:41:34</t>
+          <t>07:42:04</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.86</v>
+        <v>2.69</v>
       </c>
       <c r="F75" t="n">
-        <v>8.07</v>
+        <v>5.14</v>
       </c>
       <c r="G75" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="H75" t="n">
-        <v>14.4</v>
+        <v>15.2</v>
       </c>
       <c r="I75" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>63.72</v>
+        <v>-62.01</v>
       </c>
       <c r="K75" t="n">
-        <v>13.75</v>
+        <v>13.65</v>
       </c>
       <c r="L75" t="n">
-        <v>65.19</v>
+        <v>63.49</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:43:29</t>
+          <t>07:43:14</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.99</v>
+        <v>3.51</v>
       </c>
       <c r="F76" t="n">
-        <v>8.220000000000001</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G76" t="n">
-        <v>14.1</v>
+        <v>16.9</v>
       </c>
       <c r="H76" t="n">
-        <v>18.9</v>
+        <v>24.8</v>
       </c>
       <c r="I76" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-51.76</v>
+        <v>-54.49</v>
       </c>
       <c r="K76" t="n">
-        <v>-36.97</v>
+        <v>47.79</v>
       </c>
       <c r="L76" t="n">
-        <v>63.61</v>
+        <v>72.48</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:50:08</t>
+          <t>07:48:35</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="F77" t="n">
-        <v>8.890000000000001</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G77" t="n">
-        <v>1</v>
+        <v>354.5</v>
       </c>
       <c r="H77" t="n">
-        <v>16.8</v>
+        <v>21.3</v>
       </c>
       <c r="I77" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J77" t="n">
-        <v>-66.20999999999999</v>
+        <v>-76.22</v>
       </c>
       <c r="K77" t="n">
-        <v>14.5</v>
+        <v>-11.56</v>
       </c>
       <c r="L77" t="n">
-        <v>67.78</v>
+        <v>77.09</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:51:59</t>
+          <t>07:49:35</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>3.53</v>
+        <v>2.75</v>
       </c>
       <c r="F78" t="n">
-        <v>8.65</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G78" t="n">
-        <v>20.2</v>
+        <v>11.7</v>
       </c>
       <c r="H78" t="n">
-        <v>19.4</v>
+        <v>21.2</v>
       </c>
       <c r="I78" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="J78" t="n">
-        <v>-42.69</v>
+        <v>-95.02</v>
       </c>
       <c r="K78" t="n">
-        <v>37.37</v>
+        <v>-67.88</v>
       </c>
       <c r="L78" t="n">
-        <v>56.73</v>
+        <v>116.77</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:53:42</t>
+          <t>07:51:04</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.73</v>
+        <v>2.64</v>
       </c>
       <c r="F79" t="n">
-        <v>7.53</v>
+        <v>8.25</v>
       </c>
       <c r="G79" t="n">
-        <v>13.4</v>
+        <v>21.7</v>
       </c>
       <c r="H79" t="n">
-        <v>24.8</v>
+        <v>20.2</v>
       </c>
       <c r="I79" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J79" t="n">
-        <v>-55.62</v>
+        <v>73.08</v>
       </c>
       <c r="K79" t="n">
-        <v>-11.51</v>
+        <v>-10.44</v>
       </c>
       <c r="L79" t="n">
-        <v>56.79</v>
+        <v>73.81999999999999</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07:58:28</t>
+          <t>07:54:15</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>2.77</v>
+        <v>3.28</v>
       </c>
       <c r="F80" t="n">
-        <v>8.390000000000001</v>
+        <v>6.09</v>
       </c>
       <c r="G80" t="n">
-        <v>13.1</v>
+        <v>5.5</v>
       </c>
       <c r="H80" t="n">
-        <v>26.7</v>
+        <v>25.5</v>
       </c>
       <c r="I80" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J80" t="n">
-        <v>-96.65000000000001</v>
+        <v>-50.58</v>
       </c>
       <c r="K80" t="n">
-        <v>-69.16</v>
+        <v>78.53</v>
       </c>
       <c r="L80" t="n">
-        <v>118.85</v>
+        <v>93.41</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07:59:21</t>
+          <t>07:56:13</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="F81" t="n">
-        <v>8.890000000000001</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G81" t="n">
-        <v>11.1</v>
+        <v>7.3</v>
       </c>
       <c r="H81" t="n">
-        <v>15.7</v>
+        <v>21.1</v>
       </c>
       <c r="I81" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>80.61</v>
+        <v>100.18</v>
       </c>
       <c r="K81" t="n">
-        <v>-11.41</v>
+        <v>108.46</v>
       </c>
       <c r="L81" t="n">
-        <v>81.42</v>
+        <v>147.65</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:00:34</t>
+          <t>07:58:27</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.3</v>
+        <v>3.21</v>
       </c>
       <c r="F82" t="n">
-        <v>8.08</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G82" t="n">
-        <v>21.8</v>
+        <v>19.6</v>
       </c>
       <c r="H82" t="n">
-        <v>11.6</v>
+        <v>30.3</v>
       </c>
       <c r="I82" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>-46.96</v>
+        <v>-121.92</v>
       </c>
       <c r="K82" t="n">
-        <v>57.19</v>
+        <v>-10.82</v>
       </c>
       <c r="L82" t="n">
-        <v>74</v>
+        <v>122.4</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:03:51</t>
+          <t>08:03:13</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.81</v>
+        <v>3.02</v>
       </c>
       <c r="F83" t="n">
-        <v>8.17</v>
+        <v>7.57</v>
       </c>
       <c r="G83" t="n">
-        <v>12.9</v>
+        <v>356.8</v>
       </c>
       <c r="H83" t="n">
-        <v>20.5</v>
+        <v>14</v>
       </c>
       <c r="I83" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="J83" t="n">
-        <v>91.76000000000001</v>
+        <v>-116.6</v>
       </c>
       <c r="K83" t="n">
-        <v>93.29000000000001</v>
+        <v>-127.96</v>
       </c>
       <c r="L83" t="n">
-        <v>130.85</v>
+        <v>173.12</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:05:34</t>
+          <t>08:05:35</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>3.23</v>
+        <v>2.94</v>
       </c>
       <c r="F84" t="n">
-        <v>8.789999999999999</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="G84" t="n">
-        <v>31.3</v>
+        <v>5.6</v>
       </c>
       <c r="H84" t="n">
-        <v>23.1</v>
+        <v>17.1</v>
       </c>
       <c r="I84" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>-111.98</v>
+        <v>114.84</v>
       </c>
       <c r="K84" t="n">
-        <v>-20.99</v>
+        <v>195.31</v>
       </c>
       <c r="L84" t="n">
-        <v>113.93</v>
+        <v>226.57</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:06:53</t>
+          <t>08:07:20</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>3.03</v>
+        <v>3.15</v>
       </c>
       <c r="F85" t="n">
-        <v>7.65</v>
+        <v>8.83</v>
       </c>
       <c r="G85" t="n">
-        <v>358.8</v>
+        <v>20.5</v>
       </c>
       <c r="H85" t="n">
-        <v>24.4</v>
+        <v>21.2</v>
       </c>
       <c r="I85" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>-88.66</v>
+        <v>-28.24</v>
       </c>
       <c r="K85" t="n">
-        <v>-120.29</v>
+        <v>152.85</v>
       </c>
       <c r="L85" t="n">
-        <v>149.44</v>
+        <v>155.44</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:10:05</t>
+          <t>08:13:25</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.95</v>
+        <v>3.12</v>
       </c>
       <c r="F86" t="n">
-        <v>8.08</v>
+        <v>6.89</v>
       </c>
       <c r="G86" t="n">
-        <v>4.9</v>
+        <v>3.8</v>
       </c>
       <c r="H86" t="n">
-        <v>19.6</v>
+        <v>22.8</v>
       </c>
       <c r="I86" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>120.48</v>
+        <v>154.77</v>
       </c>
       <c r="K86" t="n">
-        <v>189.58</v>
+        <v>150.39</v>
       </c>
       <c r="L86" t="n">
-        <v>224.63</v>
+        <v>215.81</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:10:56</t>
+          <t>08:14:53</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="F87" t="n">
         <v>8.83</v>
       </c>
       <c r="G87" t="n">
-        <v>13</v>
+        <v>357.4</v>
       </c>
       <c r="H87" t="n">
-        <v>21.5</v>
+        <v>13.1</v>
       </c>
       <c r="I87" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J87" t="n">
-        <v>-51.19</v>
+        <v>-17.23</v>
       </c>
       <c r="K87" t="n">
-        <v>125.93</v>
+        <v>-37.19</v>
       </c>
       <c r="L87" t="n">
-        <v>135.93</v>
+        <v>40.99</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:12:05</t>
+          <t>08:15:54</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="F88" t="n">
-        <v>8</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G88" t="n">
-        <v>16.4</v>
+        <v>12.1</v>
       </c>
       <c r="H88" t="n">
-        <v>14.4</v>
+        <v>21.8</v>
       </c>
       <c r="I88" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J88" t="n">
-        <v>135.65</v>
+        <v>-227.63</v>
       </c>
       <c r="K88" t="n">
-        <v>91.40000000000001</v>
+        <v>-119.84</v>
       </c>
       <c r="L88" t="n">
-        <v>163.57</v>
+        <v>257.25</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-10.xlsx
+++ b/output/2024-07-10.xlsx
@@ -640,13 +640,13 @@
         <v>18</v>
       </c>
       <c r="J14" t="n">
-        <v>-61.92</v>
+        <v>-68.56</v>
       </c>
       <c r="K14" t="n">
-        <v>-10.23</v>
+        <v>-11.33</v>
       </c>
       <c r="L14" t="n">
-        <v>62.76</v>
+        <v>69.48</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>17</v>
       </c>
       <c r="J15" t="n">
-        <v>-56.99</v>
+        <v>-63.99</v>
       </c>
       <c r="K15" t="n">
-        <v>-34.44</v>
+        <v>-38.67</v>
       </c>
       <c r="L15" t="n">
-        <v>66.59</v>
+        <v>74.77</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>19</v>
       </c>
       <c r="J16" t="n">
-        <v>-37.91</v>
+        <v>-41.36</v>
       </c>
       <c r="K16" t="n">
-        <v>45.97</v>
+        <v>50.15</v>
       </c>
       <c r="L16" t="n">
-        <v>59.59</v>
+        <v>65.01000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>17</v>
       </c>
       <c r="J17" t="n">
-        <v>-3.92</v>
+        <v>-4.4</v>
       </c>
       <c r="K17" t="n">
-        <v>-66.41</v>
+        <v>-74.56</v>
       </c>
       <c r="L17" t="n">
-        <v>66.52</v>
+        <v>74.69</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>-71.72</v>
+        <v>-78.23999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>-33.83</v>
+        <v>-36.91</v>
       </c>
       <c r="L18" t="n">
-        <v>79.3</v>
+        <v>86.51000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>26.76</v>
+        <v>30.45</v>
       </c>
       <c r="K19" t="n">
-        <v>-65.90000000000001</v>
+        <v>-74.98999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>71.13</v>
+        <v>80.94</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>17</v>
       </c>
       <c r="J20" t="n">
-        <v>-59.49</v>
+        <v>-66.79000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>-89.68000000000001</v>
+        <v>-100.7</v>
       </c>
       <c r="L20" t="n">
-        <v>107.62</v>
+        <v>120.84</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>106.71</v>
+        <v>121.43</v>
       </c>
       <c r="K21" t="n">
-        <v>-49.8</v>
+        <v>-56.67</v>
       </c>
       <c r="L21" t="n">
-        <v>117.76</v>
+        <v>134</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>21</v>
       </c>
       <c r="J22" t="n">
-        <v>83.81999999999999</v>
+        <v>88.56</v>
       </c>
       <c r="K22" t="n">
-        <v>79.14</v>
+        <v>83.62</v>
       </c>
       <c r="L22" t="n">
-        <v>115.28</v>
+        <v>121.8</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>20</v>
       </c>
       <c r="J23" t="n">
-        <v>-179.02</v>
+        <v>-192.29</v>
       </c>
       <c r="K23" t="n">
-        <v>-67.72</v>
+        <v>-72.73999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>191.41</v>
+        <v>205.58</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>158.81</v>
+        <v>180.71</v>
       </c>
       <c r="K24" t="n">
-        <v>105.94</v>
+        <v>120.55</v>
       </c>
       <c r="L24" t="n">
-        <v>190.9</v>
+        <v>217.23</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>17</v>
       </c>
       <c r="J25" t="n">
-        <v>-8.93</v>
+        <v>-10.03</v>
       </c>
       <c r="K25" t="n">
-        <v>-124.64</v>
+        <v>-139.95</v>
       </c>
       <c r="L25" t="n">
-        <v>124.96</v>
+        <v>140.31</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>16</v>
       </c>
       <c r="J26" t="n">
-        <v>-97.45</v>
+        <v>-110.89</v>
       </c>
       <c r="K26" t="n">
-        <v>256.72</v>
+        <v>292.13</v>
       </c>
       <c r="L26" t="n">
-        <v>274.6</v>
+        <v>312.47</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>18</v>
       </c>
       <c r="J27" t="n">
-        <v>-275.18</v>
+        <v>-304.66</v>
       </c>
       <c r="K27" t="n">
-        <v>70.62</v>
+        <v>78.19</v>
       </c>
       <c r="L27" t="n">
-        <v>284.1</v>
+        <v>314.53</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>2.11</v>
+        <v>2.4</v>
       </c>
       <c r="K28" t="n">
-        <v>-186.85</v>
+        <v>-212.63</v>
       </c>
       <c r="L28" t="n">
-        <v>186.87</v>
+        <v>212.64</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>7.83</v>
+        <v>8.27</v>
       </c>
       <c r="K29" t="n">
-        <v>-62.84</v>
+        <v>-66.39</v>
       </c>
       <c r="L29" t="n">
-        <v>63.32</v>
+        <v>66.91</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>19</v>
       </c>
       <c r="J30" t="n">
-        <v>-33.81</v>
+        <v>-36.88</v>
       </c>
       <c r="K30" t="n">
-        <v>-51.16</v>
+        <v>-55.82</v>
       </c>
       <c r="L30" t="n">
-        <v>61.33</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>17</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.25</v>
+        <v>-0.28</v>
       </c>
       <c r="K31" t="n">
-        <v>87.84</v>
+        <v>98.63</v>
       </c>
       <c r="L31" t="n">
-        <v>87.84</v>
+        <v>98.63</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>65.31999999999999</v>
+        <v>69.02</v>
       </c>
       <c r="K32" t="n">
-        <v>31.56</v>
+        <v>33.35</v>
       </c>
       <c r="L32" t="n">
-        <v>72.54000000000001</v>
+        <v>76.65000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>19</v>
       </c>
       <c r="J33" t="n">
-        <v>-86.81999999999999</v>
+        <v>-94.70999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>20.24</v>
+        <v>22.08</v>
       </c>
       <c r="L33" t="n">
-        <v>89.15000000000001</v>
+        <v>97.25</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>99.25</v>
+        <v>104.87</v>
       </c>
       <c r="K34" t="n">
-        <v>41.24</v>
+        <v>43.57</v>
       </c>
       <c r="L34" t="n">
-        <v>107.48</v>
+        <v>113.56</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>-153.4</v>
+        <v>-162.08</v>
       </c>
       <c r="K35" t="n">
-        <v>89.19</v>
+        <v>94.23</v>
       </c>
       <c r="L35" t="n">
-        <v>177.44</v>
+        <v>187.49</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>50.07</v>
+        <v>56.98</v>
       </c>
       <c r="K36" t="n">
-        <v>-138.55</v>
+        <v>-157.66</v>
       </c>
       <c r="L36" t="n">
-        <v>147.32</v>
+        <v>167.64</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>21</v>
       </c>
       <c r="J37" t="n">
-        <v>-64.70999999999999</v>
+        <v>-68.38</v>
       </c>
       <c r="K37" t="n">
-        <v>85.45</v>
+        <v>90.29000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>107.19</v>
+        <v>113.26</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>19</v>
       </c>
       <c r="J38" t="n">
-        <v>153.42</v>
+        <v>167.37</v>
       </c>
       <c r="K38" t="n">
-        <v>191.18</v>
+        <v>208.57</v>
       </c>
       <c r="L38" t="n">
-        <v>245.13</v>
+        <v>267.42</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>17</v>
       </c>
       <c r="J39" t="n">
-        <v>-114.15</v>
+        <v>-128.17</v>
       </c>
       <c r="K39" t="n">
-        <v>67.45999999999999</v>
+        <v>75.73999999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>132.6</v>
+        <v>148.88</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>111.97</v>
+        <v>127.41</v>
       </c>
       <c r="K40" t="n">
-        <v>148.68</v>
+        <v>169.19</v>
       </c>
       <c r="L40" t="n">
-        <v>186.13</v>
+        <v>211.8</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>18</v>
       </c>
       <c r="J41" t="n">
-        <v>-146.69</v>
+        <v>-162.41</v>
       </c>
       <c r="K41" t="n">
-        <v>261.63</v>
+        <v>289.66</v>
       </c>
       <c r="L41" t="n">
-        <v>299.95</v>
+        <v>332.08</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>275.85</v>
+        <v>313.9</v>
       </c>
       <c r="K42" t="n">
-        <v>-172.12</v>
+        <v>-195.86</v>
       </c>
       <c r="L42" t="n">
-        <v>325.14</v>
+        <v>369.99</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>-319.58</v>
+        <v>-358.83</v>
       </c>
       <c r="K43" t="n">
-        <v>-102.74</v>
+        <v>-115.36</v>
       </c>
       <c r="L43" t="n">
-        <v>335.69</v>
+        <v>376.92</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>66.27</v>
+        <v>72.29000000000001</v>
       </c>
       <c r="K44" t="n">
-        <v>83.54000000000001</v>
+        <v>91.13</v>
       </c>
       <c r="L44" t="n">
-        <v>106.63</v>
+        <v>116.32</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>17</v>
       </c>
       <c r="J45" t="n">
-        <v>4.47</v>
+        <v>5.02</v>
       </c>
       <c r="K45" t="n">
-        <v>15.4</v>
+        <v>17.29</v>
       </c>
       <c r="L45" t="n">
-        <v>16.04</v>
+        <v>18.01</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>72.78</v>
+        <v>82.81999999999999</v>
       </c>
       <c r="K46" t="n">
-        <v>-82.63</v>
+        <v>-94.02</v>
       </c>
       <c r="L46" t="n">
-        <v>110.11</v>
+        <v>125.3</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>-75.18000000000001</v>
+        <v>-82.02</v>
       </c>
       <c r="K47" t="n">
-        <v>4</v>
+        <v>4.36</v>
       </c>
       <c r="L47" t="n">
-        <v>75.29000000000001</v>
+        <v>82.13</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-104.99</v>
+        <v>-119.47</v>
       </c>
       <c r="K48" t="n">
-        <v>27.48</v>
+        <v>31.28</v>
       </c>
       <c r="L48" t="n">
-        <v>108.53</v>
+        <v>123.5</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>11.9</v>
+        <v>12.58</v>
       </c>
       <c r="K49" t="n">
-        <v>-88.93000000000001</v>
+        <v>-93.95999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>89.72</v>
+        <v>94.8</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="K50" t="n">
-        <v>-123.57</v>
+        <v>-140.62</v>
       </c>
       <c r="L50" t="n">
-        <v>123.64</v>
+        <v>140.69</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>17</v>
       </c>
       <c r="J51" t="n">
-        <v>68.31999999999999</v>
+        <v>76.70999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>125.61</v>
+        <v>141.03</v>
       </c>
       <c r="L51" t="n">
-        <v>142.99</v>
+        <v>160.55</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>35.3</v>
+        <v>37.29</v>
       </c>
       <c r="K52" t="n">
-        <v>87.41</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="L52" t="n">
-        <v>94.27</v>
+        <v>99.59999999999999</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>-77.43000000000001</v>
+        <v>-88.11</v>
       </c>
       <c r="K53" t="n">
-        <v>-195.46</v>
+        <v>-222.42</v>
       </c>
       <c r="L53" t="n">
-        <v>210.24</v>
+        <v>239.24</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>-65.06999999999999</v>
+        <v>-74.05</v>
       </c>
       <c r="K54" t="n">
-        <v>-162.54</v>
+        <v>-184.96</v>
       </c>
       <c r="L54" t="n">
-        <v>175.08</v>
+        <v>199.23</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>21</v>
       </c>
       <c r="J55" t="n">
-        <v>132.73</v>
+        <v>140.24</v>
       </c>
       <c r="K55" t="n">
-        <v>7.46</v>
+        <v>7.88</v>
       </c>
       <c r="L55" t="n">
-        <v>132.94</v>
+        <v>140.47</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>227.53</v>
+        <v>258.91</v>
       </c>
       <c r="K56" t="n">
-        <v>-150.74</v>
+        <v>-171.53</v>
       </c>
       <c r="L56" t="n">
-        <v>272.93</v>
+        <v>310.58</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>20</v>
       </c>
       <c r="J57" t="n">
-        <v>144.04</v>
+        <v>154.71</v>
       </c>
       <c r="K57" t="n">
-        <v>-147.18</v>
+        <v>-158.08</v>
       </c>
       <c r="L57" t="n">
-        <v>205.94</v>
+        <v>221.19</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>203.2</v>
+        <v>231.22</v>
       </c>
       <c r="K58" t="n">
-        <v>117.21</v>
+        <v>133.38</v>
       </c>
       <c r="L58" t="n">
-        <v>234.58</v>
+        <v>266.94</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>-59.23</v>
+        <v>-62.58</v>
       </c>
       <c r="K59" t="n">
-        <v>-19.8</v>
+        <v>-20.92</v>
       </c>
       <c r="L59" t="n">
-        <v>62.45</v>
+        <v>65.98999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>-38.08</v>
+        <v>-43.34</v>
       </c>
       <c r="K60" t="n">
-        <v>60.95</v>
+        <v>69.36</v>
       </c>
       <c r="L60" t="n">
-        <v>71.87</v>
+        <v>81.78</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="K61" t="n">
-        <v>75.31</v>
+        <v>79.56999999999999</v>
       </c>
       <c r="L61" t="n">
-        <v>75.33</v>
+        <v>79.59</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>-18.53</v>
+        <v>-21.08</v>
       </c>
       <c r="K62" t="n">
-        <v>-126.85</v>
+        <v>-144.35</v>
       </c>
       <c r="L62" t="n">
-        <v>128.2</v>
+        <v>145.88</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-80.92</v>
+        <v>-92.08</v>
       </c>
       <c r="K63" t="n">
-        <v>30.87</v>
+        <v>35.13</v>
       </c>
       <c r="L63" t="n">
-        <v>86.61</v>
+        <v>98.55</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>-61.64</v>
+        <v>-65.13</v>
       </c>
       <c r="K64" t="n">
-        <v>-59.16</v>
+        <v>-62.51</v>
       </c>
       <c r="L64" t="n">
-        <v>85.44</v>
+        <v>90.28</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>16</v>
       </c>
       <c r="J65" t="n">
-        <v>125.86</v>
+        <v>143.17</v>
       </c>
       <c r="K65" t="n">
-        <v>-59.51</v>
+        <v>-67.69</v>
       </c>
       <c r="L65" t="n">
-        <v>139.22</v>
+        <v>158.37</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>18</v>
       </c>
       <c r="J66" t="n">
-        <v>120.33</v>
+        <v>133.23</v>
       </c>
       <c r="K66" t="n">
-        <v>4.4</v>
+        <v>4.87</v>
       </c>
       <c r="L66" t="n">
-        <v>120.41</v>
+        <v>133.32</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>-34.15</v>
+        <v>-36.68</v>
       </c>
       <c r="K67" t="n">
-        <v>89.56999999999999</v>
+        <v>96.2</v>
       </c>
       <c r="L67" t="n">
-        <v>95.86</v>
+        <v>102.96</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>133.77</v>
+        <v>152.38</v>
       </c>
       <c r="K68" t="n">
-        <v>221.31</v>
+        <v>252.09</v>
       </c>
       <c r="L68" t="n">
-        <v>258.6</v>
+        <v>294.57</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>-43.44</v>
+        <v>-49.44</v>
       </c>
       <c r="K69" t="n">
-        <v>-226.64</v>
+        <v>-257.91</v>
       </c>
       <c r="L69" t="n">
-        <v>230.76</v>
+        <v>262.61</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>21</v>
       </c>
       <c r="J70" t="n">
-        <v>-162.01</v>
+        <v>-171.21</v>
       </c>
       <c r="K70" t="n">
-        <v>83.25</v>
+        <v>87.97</v>
       </c>
       <c r="L70" t="n">
-        <v>182.14</v>
+        <v>192.49</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>20</v>
       </c>
       <c r="J71" t="n">
-        <v>94.02</v>
+        <v>100.98</v>
       </c>
       <c r="K71" t="n">
-        <v>316.53</v>
+        <v>339.98</v>
       </c>
       <c r="L71" t="n">
-        <v>330.2</v>
+        <v>354.66</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>19</v>
       </c>
       <c r="J72" t="n">
-        <v>181.72</v>
+        <v>198.24</v>
       </c>
       <c r="K72" t="n">
-        <v>-81.87</v>
+        <v>-89.31</v>
       </c>
       <c r="L72" t="n">
-        <v>199.31</v>
+        <v>217.43</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>20</v>
       </c>
       <c r="J73" t="n">
-        <v>271.24</v>
+        <v>291.34</v>
       </c>
       <c r="K73" t="n">
-        <v>120.58</v>
+        <v>129.51</v>
       </c>
       <c r="L73" t="n">
-        <v>296.84</v>
+        <v>318.83</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>17</v>
       </c>
       <c r="J74" t="n">
-        <v>-71.73</v>
+        <v>-80.54000000000001</v>
       </c>
       <c r="K74" t="n">
-        <v>-50.39</v>
+        <v>-56.58</v>
       </c>
       <c r="L74" t="n">
-        <v>87.66</v>
+        <v>98.43000000000001</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>-62.01</v>
+        <v>-66.59999999999999</v>
       </c>
       <c r="K75" t="n">
-        <v>13.65</v>
+        <v>14.67</v>
       </c>
       <c r="L75" t="n">
-        <v>63.49</v>
+        <v>68.19</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-54.49</v>
+        <v>-61.93</v>
       </c>
       <c r="K76" t="n">
-        <v>47.79</v>
+        <v>54.31</v>
       </c>
       <c r="L76" t="n">
-        <v>72.48</v>
+        <v>82.37</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>19</v>
       </c>
       <c r="J77" t="n">
-        <v>-76.22</v>
+        <v>-83.15000000000001</v>
       </c>
       <c r="K77" t="n">
-        <v>-11.56</v>
+        <v>-12.61</v>
       </c>
       <c r="L77" t="n">
-        <v>77.09</v>
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>17</v>
       </c>
       <c r="J78" t="n">
-        <v>-95.02</v>
+        <v>-106.69</v>
       </c>
       <c r="K78" t="n">
-        <v>-67.88</v>
+        <v>-76.20999999999999</v>
       </c>
       <c r="L78" t="n">
-        <v>116.77</v>
+        <v>131.11</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>21</v>
       </c>
       <c r="J79" t="n">
-        <v>73.08</v>
+        <v>77.20999999999999</v>
       </c>
       <c r="K79" t="n">
-        <v>-10.44</v>
+        <v>-11.03</v>
       </c>
       <c r="L79" t="n">
-        <v>73.81999999999999</v>
+        <v>78</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>21</v>
       </c>
       <c r="J80" t="n">
-        <v>-50.58</v>
+        <v>-53.44</v>
       </c>
       <c r="K80" t="n">
-        <v>78.53</v>
+        <v>82.97</v>
       </c>
       <c r="L80" t="n">
-        <v>93.41</v>
+        <v>98.69</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>100.18</v>
+        <v>114</v>
       </c>
       <c r="K81" t="n">
-        <v>108.46</v>
+        <v>123.42</v>
       </c>
       <c r="L81" t="n">
-        <v>147.65</v>
+        <v>168.01</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>-121.92</v>
+        <v>-138.74</v>
       </c>
       <c r="K82" t="n">
-        <v>-10.82</v>
+        <v>-12.32</v>
       </c>
       <c r="L82" t="n">
-        <v>122.4</v>
+        <v>139.29</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>18</v>
       </c>
       <c r="J83" t="n">
-        <v>-116.6</v>
+        <v>-129.1</v>
       </c>
       <c r="K83" t="n">
-        <v>-127.96</v>
+        <v>-141.67</v>
       </c>
       <c r="L83" t="n">
-        <v>173.12</v>
+        <v>191.67</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>114.84</v>
+        <v>130.68</v>
       </c>
       <c r="K84" t="n">
-        <v>195.31</v>
+        <v>222.25</v>
       </c>
       <c r="L84" t="n">
-        <v>226.57</v>
+        <v>257.82</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>-28.24</v>
+        <v>-32.14</v>
       </c>
       <c r="K85" t="n">
-        <v>152.85</v>
+        <v>173.93</v>
       </c>
       <c r="L85" t="n">
-        <v>155.44</v>
+        <v>176.88</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>154.77</v>
+        <v>163.53</v>
       </c>
       <c r="K86" t="n">
-        <v>150.39</v>
+        <v>158.91</v>
       </c>
       <c r="L86" t="n">
-        <v>215.81</v>
+        <v>228.02</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>18</v>
       </c>
       <c r="J87" t="n">
-        <v>-17.23</v>
+        <v>-19.07</v>
       </c>
       <c r="K87" t="n">
-        <v>-37.19</v>
+        <v>-41.18</v>
       </c>
       <c r="L87" t="n">
-        <v>40.99</v>
+        <v>45.38</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>18</v>
       </c>
       <c r="J88" t="n">
-        <v>-227.63</v>
+        <v>-252.13</v>
       </c>
       <c r="K88" t="n">
-        <v>-119.84</v>
+        <v>-132.74</v>
       </c>
       <c r="L88" t="n">
-        <v>257.25</v>
+        <v>284.94</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-10.xlsx
+++ b/output/2024-07-10.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.54</v>
+        <v>3.66</v>
       </c>
       <c r="F14" t="n">
-        <v>7.69</v>
+        <v>5.8</v>
       </c>
       <c r="G14" t="n">
-        <v>24.2</v>
+        <v>7.8</v>
       </c>
       <c r="H14" t="n">
-        <v>17.6</v>
+        <v>46.7</v>
       </c>
       <c r="I14" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>-68.56</v>
+        <v>47.39</v>
       </c>
       <c r="K14" t="n">
-        <v>-11.33</v>
+        <v>32</v>
       </c>
       <c r="L14" t="n">
-        <v>69.48</v>
+        <v>57.18</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:45:52</t>
+          <t>04:45:38</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.43</v>
+        <v>2.73</v>
       </c>
       <c r="F15" t="n">
-        <v>5.93</v>
+        <v>6.17</v>
       </c>
       <c r="G15" t="n">
-        <v>349</v>
+        <v>16.7</v>
       </c>
       <c r="H15" t="n">
-        <v>16</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-63.99</v>
+        <v>22.38</v>
       </c>
       <c r="K15" t="n">
-        <v>-38.67</v>
+        <v>42.93</v>
       </c>
       <c r="L15" t="n">
-        <v>74.77</v>
+        <v>48.41</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:47:36</t>
+          <t>04:46:58</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="F16" t="n">
-        <v>4.92</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>5.4</v>
       </c>
       <c r="H16" t="n">
-        <v>15.9</v>
+        <v>40.9</v>
       </c>
       <c r="I16" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>-41.36</v>
+        <v>-27.28</v>
       </c>
       <c r="K16" t="n">
-        <v>50.15</v>
+        <v>19.59</v>
       </c>
       <c r="L16" t="n">
-        <v>65.01000000000001</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:53:02</t>
+          <t>04:52:07</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.39</v>
+        <v>4.04</v>
       </c>
       <c r="F17" t="n">
-        <v>5.31</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>18.3</v>
+        <v>20.9</v>
       </c>
       <c r="H17" t="n">
-        <v>19</v>
+        <v>86.8</v>
       </c>
       <c r="I17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>-4.4</v>
+        <v>57.39</v>
       </c>
       <c r="K17" t="n">
-        <v>-74.56</v>
+        <v>-67.15000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>74.69</v>
+        <v>88.33</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:54:24</t>
+          <t>04:53:14</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.13</v>
+        <v>2.56</v>
       </c>
       <c r="F18" t="n">
-        <v>6.73</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>359.4</v>
+        <v>13.6</v>
       </c>
       <c r="H18" t="n">
-        <v>19.1</v>
+        <v>47.2</v>
       </c>
       <c r="I18" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>-78.23999999999999</v>
+        <v>-43.29</v>
       </c>
       <c r="K18" t="n">
-        <v>-36.91</v>
+        <v>42.54</v>
       </c>
       <c r="L18" t="n">
-        <v>86.51000000000001</v>
+        <v>60.69</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:55:35</t>
+          <t>04:55:12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.55</v>
+        <v>2.86</v>
       </c>
       <c r="F19" t="n">
-        <v>3.89</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>359</v>
+        <v>13.9</v>
       </c>
       <c r="H19" t="n">
-        <v>21.6</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>30.45</v>
+        <v>-41.05</v>
       </c>
       <c r="K19" t="n">
-        <v>-74.98999999999999</v>
+        <v>35.48</v>
       </c>
       <c r="L19" t="n">
-        <v>80.94</v>
+        <v>54.26</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:00:24</t>
+          <t>04:58:26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.76</v>
+        <v>2.45</v>
       </c>
       <c r="F20" t="n">
-        <v>8.720000000000001</v>
+        <v>8.06</v>
       </c>
       <c r="G20" t="n">
-        <v>10.3</v>
+        <v>22.9</v>
       </c>
       <c r="H20" t="n">
-        <v>21.1</v>
+        <v>66.5</v>
       </c>
       <c r="I20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>-66.79000000000001</v>
+        <v>102.69</v>
       </c>
       <c r="K20" t="n">
-        <v>-100.7</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>120.84</v>
+        <v>125.62</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:01:12</t>
+          <t>04:59:45</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.03</v>
+        <v>2.65</v>
       </c>
       <c r="F21" t="n">
-        <v>6.77</v>
+        <v>5.64</v>
       </c>
       <c r="G21" t="n">
-        <v>9.300000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="H21" t="n">
-        <v>23.8</v>
+        <v>28.1</v>
       </c>
       <c r="I21" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J21" t="n">
-        <v>121.43</v>
+        <v>-95.36</v>
       </c>
       <c r="K21" t="n">
-        <v>-56.67</v>
+        <v>1.42</v>
       </c>
       <c r="L21" t="n">
-        <v>134</v>
+        <v>95.37</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:03:03</t>
+          <t>05:00:54</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.79</v>
+        <v>3</v>
       </c>
       <c r="F22" t="n">
-        <v>5.27</v>
+        <v>5.7</v>
       </c>
       <c r="G22" t="n">
-        <v>4.7</v>
+        <v>8.5</v>
       </c>
       <c r="H22" t="n">
-        <v>15.6</v>
+        <v>40.2</v>
       </c>
       <c r="I22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>88.56</v>
+        <v>-54.42</v>
       </c>
       <c r="K22" t="n">
-        <v>83.62</v>
+        <v>93.3</v>
       </c>
       <c r="L22" t="n">
-        <v>121.8</v>
+        <v>108.01</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:07:25</t>
+          <t>05:05:54</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.8</v>
+        <v>2.11</v>
       </c>
       <c r="F23" t="n">
-        <v>9.539999999999999</v>
+        <v>6.37</v>
       </c>
       <c r="G23" t="n">
-        <v>13.2</v>
+        <v>15.1</v>
       </c>
       <c r="H23" t="n">
-        <v>20.7</v>
+        <v>48</v>
       </c>
       <c r="I23" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>-192.29</v>
+        <v>4.22</v>
       </c>
       <c r="K23" t="n">
-        <v>-72.73999999999999</v>
+        <v>-122.95</v>
       </c>
       <c r="L23" t="n">
-        <v>205.58</v>
+        <v>123.02</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:09:13</t>
+          <t>05:07:21</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="F24" t="n">
-        <v>9.16</v>
+        <v>3.92</v>
       </c>
       <c r="G24" t="n">
-        <v>22.4</v>
+        <v>10</v>
       </c>
       <c r="H24" t="n">
-        <v>10.9</v>
+        <v>58.7</v>
       </c>
       <c r="I24" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>180.71</v>
+        <v>-50.95</v>
       </c>
       <c r="K24" t="n">
-        <v>120.55</v>
+        <v>117.71</v>
       </c>
       <c r="L24" t="n">
-        <v>217.23</v>
+        <v>128.27</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:10:00</t>
+          <t>05:08:09</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.08</v>
+        <v>2.86</v>
       </c>
       <c r="F25" t="n">
-        <v>5.82</v>
+        <v>6.41</v>
       </c>
       <c r="G25" t="n">
-        <v>8.199999999999999</v>
+        <v>13.1</v>
       </c>
       <c r="H25" t="n">
-        <v>21.7</v>
+        <v>59</v>
       </c>
       <c r="I25" t="n">
         <v>17</v>
       </c>
       <c r="J25" t="n">
-        <v>-10.03</v>
+        <v>-120.33</v>
       </c>
       <c r="K25" t="n">
-        <v>-139.95</v>
+        <v>-56.96</v>
       </c>
       <c r="L25" t="n">
-        <v>140.31</v>
+        <v>133.13</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:15:04</t>
+          <t>05:12:52</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.42</v>
+        <v>3.05</v>
       </c>
       <c r="F26" t="n">
-        <v>6.74</v>
+        <v>7.33</v>
       </c>
       <c r="G26" t="n">
-        <v>3.7</v>
+        <v>12.5</v>
       </c>
       <c r="H26" t="n">
-        <v>11.8</v>
+        <v>59.1</v>
       </c>
       <c r="I26" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>-110.89</v>
+        <v>-173.88</v>
       </c>
       <c r="K26" t="n">
-        <v>292.13</v>
+        <v>47.88</v>
       </c>
       <c r="L26" t="n">
-        <v>312.47</v>
+        <v>180.35</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:17:13</t>
+          <t>05:15:17</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.4</v>
+        <v>2.64</v>
       </c>
       <c r="F27" t="n">
-        <v>9.539999999999999</v>
+        <v>5.66</v>
       </c>
       <c r="G27" t="n">
-        <v>16.8</v>
+        <v>4.2</v>
       </c>
       <c r="H27" t="n">
-        <v>20.1</v>
+        <v>41.5</v>
       </c>
       <c r="I27" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>-304.66</v>
+        <v>-21.31</v>
       </c>
       <c r="K27" t="n">
-        <v>78.19</v>
+        <v>-196.24</v>
       </c>
       <c r="L27" t="n">
-        <v>314.53</v>
+        <v>197.39</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:18:57</t>
+          <t>05:16:45</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.82</v>
+        <v>2.54</v>
       </c>
       <c r="F28" t="n">
-        <v>6.52</v>
+        <v>5.73</v>
       </c>
       <c r="G28" t="n">
-        <v>11.2</v>
+        <v>9.1</v>
       </c>
       <c r="H28" t="n">
-        <v>20.4</v>
+        <v>40.4</v>
       </c>
       <c r="I28" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>2.4</v>
+        <v>-9.48</v>
       </c>
       <c r="K28" t="n">
-        <v>-212.63</v>
+        <v>188.78</v>
       </c>
       <c r="L28" t="n">
-        <v>212.64</v>
+        <v>189.01</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:31:40</t>
+          <t>05:29:46</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.82</v>
+        <v>3.01</v>
       </c>
       <c r="F29" t="n">
-        <v>6.79</v>
+        <v>4.45</v>
       </c>
       <c r="G29" t="n">
-        <v>15.3</v>
+        <v>3</v>
       </c>
       <c r="H29" t="n">
-        <v>23.7</v>
+        <v>75.2</v>
       </c>
       <c r="I29" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J29" t="n">
-        <v>8.27</v>
+        <v>-45.26</v>
       </c>
       <c r="K29" t="n">
-        <v>-66.39</v>
+        <v>33.33</v>
       </c>
       <c r="L29" t="n">
-        <v>66.91</v>
+        <v>56.21</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:33:56</t>
+          <t>05:32:06</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.78</v>
+        <v>3.21</v>
       </c>
       <c r="F30" t="n">
-        <v>9.539999999999999</v>
+        <v>8.56</v>
       </c>
       <c r="G30" t="n">
-        <v>19.1</v>
+        <v>20.7</v>
       </c>
       <c r="H30" t="n">
-        <v>22.7</v>
+        <v>100</v>
       </c>
       <c r="I30" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>-36.88</v>
+        <v>13.52</v>
       </c>
       <c r="K30" t="n">
-        <v>-55.82</v>
+        <v>-42.83</v>
       </c>
       <c r="L30" t="n">
-        <v>66.90000000000001</v>
+        <v>44.92</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:36:48</t>
+          <t>05:34:17</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.23</v>
+        <v>2.89</v>
       </c>
       <c r="F31" t="n">
-        <v>6.38</v>
+        <v>7.5</v>
       </c>
       <c r="G31" t="n">
-        <v>21.9</v>
+        <v>2.9</v>
       </c>
       <c r="H31" t="n">
-        <v>20.2</v>
+        <v>58.4</v>
       </c>
       <c r="I31" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.28</v>
+        <v>41.75</v>
       </c>
       <c r="K31" t="n">
-        <v>98.63</v>
+        <v>15.2</v>
       </c>
       <c r="L31" t="n">
-        <v>98.63</v>
+        <v>44.43</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:41:11</t>
+          <t>05:40:06</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.37</v>
+        <v>3</v>
       </c>
       <c r="F32" t="n">
-        <v>4.88</v>
+        <v>8.74</v>
       </c>
       <c r="G32" t="n">
-        <v>16.9</v>
+        <v>16.4</v>
       </c>
       <c r="H32" t="n">
-        <v>10.8</v>
+        <v>18.7</v>
       </c>
       <c r="I32" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>69.02</v>
+        <v>-84.20999999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>33.35</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>76.65000000000001</v>
+        <v>84.64</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:42:19</t>
+          <t>05:42:05</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.94</v>
+        <v>2.85</v>
       </c>
       <c r="F33" t="n">
-        <v>6.62</v>
+        <v>6</v>
       </c>
       <c r="G33" t="n">
-        <v>9.5</v>
+        <v>359.3</v>
       </c>
       <c r="H33" t="n">
-        <v>23.3</v>
+        <v>15.2</v>
       </c>
       <c r="I33" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>-94.70999999999999</v>
+        <v>22.99</v>
       </c>
       <c r="K33" t="n">
-        <v>22.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>97.25</v>
+        <v>22.99</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:44:06</t>
+          <t>05:43:10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.64</v>
+        <v>3.02</v>
       </c>
       <c r="F34" t="n">
-        <v>6.7</v>
+        <v>9.18</v>
       </c>
       <c r="G34" t="n">
-        <v>12.3</v>
+        <v>14.7</v>
       </c>
       <c r="H34" t="n">
-        <v>17.8</v>
+        <v>46.7</v>
       </c>
       <c r="I34" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J34" t="n">
-        <v>104.87</v>
+        <v>62.37</v>
       </c>
       <c r="K34" t="n">
-        <v>43.57</v>
+        <v>-37.57</v>
       </c>
       <c r="L34" t="n">
-        <v>113.56</v>
+        <v>72.81</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:47:55</t>
+          <t>05:48:13</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.22</v>
+        <v>2.76</v>
       </c>
       <c r="F35" t="n">
-        <v>5.99</v>
+        <v>5.98</v>
       </c>
       <c r="G35" t="n">
-        <v>15.5</v>
+        <v>359.8</v>
       </c>
       <c r="H35" t="n">
-        <v>23</v>
+        <v>59.9</v>
       </c>
       <c r="I35" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-162.08</v>
+        <v>95.95</v>
       </c>
       <c r="K35" t="n">
-        <v>94.23</v>
+        <v>14.66</v>
       </c>
       <c r="L35" t="n">
-        <v>187.49</v>
+        <v>97.06</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:49:15</t>
+          <t>05:50:33</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.88</v>
+        <v>3.11</v>
       </c>
       <c r="F36" t="n">
-        <v>8.99</v>
+        <v>9.18</v>
       </c>
       <c r="G36" t="n">
-        <v>12.9</v>
+        <v>1.8</v>
       </c>
       <c r="H36" t="n">
-        <v>20.3</v>
+        <v>42.3</v>
       </c>
       <c r="I36" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>56.98</v>
+        <v>122.74</v>
       </c>
       <c r="K36" t="n">
-        <v>-157.66</v>
+        <v>-56.93</v>
       </c>
       <c r="L36" t="n">
-        <v>167.64</v>
+        <v>135.3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:50:15</t>
+          <t>05:52:43</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.76</v>
+        <v>3.08</v>
       </c>
       <c r="F37" t="n">
-        <v>8.550000000000001</v>
+        <v>6.46</v>
       </c>
       <c r="G37" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="H37" t="n">
-        <v>14.6</v>
+        <v>41.2</v>
       </c>
       <c r="I37" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J37" t="n">
-        <v>-68.38</v>
+        <v>-46.57</v>
       </c>
       <c r="K37" t="n">
-        <v>90.29000000000001</v>
+        <v>33.94</v>
       </c>
       <c r="L37" t="n">
-        <v>113.26</v>
+        <v>57.63</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:54:37</t>
+          <t>05:57:01</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.69</v>
+        <v>2.42</v>
       </c>
       <c r="F38" t="n">
-        <v>9.08</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="H38" t="n">
-        <v>24</v>
+        <v>27.6</v>
       </c>
       <c r="I38" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>167.37</v>
+        <v>-167.06</v>
       </c>
       <c r="K38" t="n">
-        <v>208.57</v>
+        <v>94.31999999999999</v>
       </c>
       <c r="L38" t="n">
-        <v>267.42</v>
+        <v>191.85</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:56:08</t>
+          <t>05:58:53</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="F39" t="n">
-        <v>5.85</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="G39" t="n">
-        <v>16.7</v>
+        <v>6.5</v>
       </c>
       <c r="H39" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="I39" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>-128.17</v>
+        <v>-153.77</v>
       </c>
       <c r="K39" t="n">
-        <v>75.73999999999999</v>
+        <v>32.36</v>
       </c>
       <c r="L39" t="n">
-        <v>148.88</v>
+        <v>157.14</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:57:41</t>
+          <t>05:59:51</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.79</v>
+        <v>3.07</v>
       </c>
       <c r="F40" t="n">
-        <v>8.81</v>
+        <v>7.84</v>
       </c>
       <c r="G40" t="n">
-        <v>11</v>
+        <v>7.4</v>
       </c>
       <c r="H40" t="n">
-        <v>21.1</v>
+        <v>85.7</v>
       </c>
       <c r="I40" t="n">
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>127.41</v>
+        <v>114.16</v>
       </c>
       <c r="K40" t="n">
-        <v>169.19</v>
+        <v>48.41</v>
       </c>
       <c r="L40" t="n">
-        <v>211.8</v>
+        <v>124</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:02:07</t>
+          <t>06:05:12</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.61</v>
+        <v>1.94</v>
       </c>
       <c r="F41" t="n">
-        <v>7.53</v>
+        <v>3.15</v>
       </c>
       <c r="G41" t="n">
-        <v>12.7</v>
+        <v>13</v>
       </c>
       <c r="H41" t="n">
-        <v>20.5</v>
+        <v>63.5</v>
       </c>
       <c r="I41" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J41" t="n">
-        <v>-162.41</v>
+        <v>-48.35</v>
       </c>
       <c r="K41" t="n">
-        <v>289.66</v>
+        <v>161.05</v>
       </c>
       <c r="L41" t="n">
-        <v>332.08</v>
+        <v>168.15</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:03:10</t>
+          <t>06:06:50</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.84</v>
+        <v>2.72</v>
       </c>
       <c r="F42" t="n">
-        <v>6.83</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="G42" t="n">
-        <v>356</v>
+        <v>11.3</v>
       </c>
       <c r="H42" t="n">
-        <v>15.6</v>
+        <v>71.3</v>
       </c>
       <c r="I42" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>313.9</v>
+        <v>212.16</v>
       </c>
       <c r="K42" t="n">
-        <v>-195.86</v>
+        <v>-123.09</v>
       </c>
       <c r="L42" t="n">
-        <v>369.99</v>
+        <v>245.28</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:04:19</t>
+          <t>06:08:29</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.58</v>
+        <v>3.06</v>
       </c>
       <c r="F43" t="n">
-        <v>6.95</v>
+        <v>8.42</v>
       </c>
       <c r="G43" t="n">
-        <v>5.3</v>
+        <v>12.9</v>
       </c>
       <c r="H43" t="n">
-        <v>19.2</v>
+        <v>14</v>
       </c>
       <c r="I43" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>-358.83</v>
+        <v>-78.51000000000001</v>
       </c>
       <c r="K43" t="n">
-        <v>-115.36</v>
+        <v>-229.23</v>
       </c>
       <c r="L43" t="n">
-        <v>376.92</v>
+        <v>242.3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:16:28</t>
+          <t>06:17:53</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3.12</v>
+        <v>2.93</v>
       </c>
       <c r="F44" t="n">
         <v>9.539999999999999</v>
       </c>
       <c r="G44" t="n">
-        <v>351.9</v>
+        <v>347.7</v>
       </c>
       <c r="H44" t="n">
-        <v>21.4</v>
+        <v>66.7</v>
       </c>
       <c r="I44" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>72.29000000000001</v>
+        <v>-26.87</v>
       </c>
       <c r="K44" t="n">
-        <v>91.13</v>
+        <v>29.62</v>
       </c>
       <c r="L44" t="n">
-        <v>116.32</v>
+        <v>39.99</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:17:36</t>
+          <t>06:19:00</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.23</v>
+        <v>2.68</v>
       </c>
       <c r="F45" t="n">
-        <v>6.67</v>
+        <v>6.48</v>
       </c>
       <c r="G45" t="n">
-        <v>22.4</v>
+        <v>12.6</v>
       </c>
       <c r="H45" t="n">
-        <v>19.7</v>
+        <v>43.2</v>
       </c>
       <c r="I45" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>5.02</v>
+        <v>-42.29</v>
       </c>
       <c r="K45" t="n">
-        <v>17.29</v>
+        <v>0.66</v>
       </c>
       <c r="L45" t="n">
-        <v>18.01</v>
+        <v>42.29</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:19:53</t>
+          <t>06:20:06</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.98</v>
+        <v>3.17</v>
       </c>
       <c r="F46" t="n">
-        <v>6.97</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G46" t="n">
-        <v>20.9</v>
+        <v>25.8</v>
       </c>
       <c r="H46" t="n">
-        <v>15.4</v>
+        <v>44.3</v>
       </c>
       <c r="I46" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>82.81999999999999</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="K46" t="n">
-        <v>-94.02</v>
+        <v>-57.38</v>
       </c>
       <c r="L46" t="n">
-        <v>125.3</v>
+        <v>57.99</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:23:13</t>
+          <t>06:24:24</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.73</v>
+        <v>3.03</v>
       </c>
       <c r="F47" t="n">
-        <v>7.52</v>
+        <v>5.8</v>
       </c>
       <c r="G47" t="n">
-        <v>10.4</v>
+        <v>357.8</v>
       </c>
       <c r="H47" t="n">
-        <v>21.3</v>
+        <v>29.7</v>
       </c>
       <c r="I47" t="n">
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>-82.02</v>
+        <v>-87.14</v>
       </c>
       <c r="K47" t="n">
-        <v>4.36</v>
+        <v>-1.3</v>
       </c>
       <c r="L47" t="n">
-        <v>82.13</v>
+        <v>87.15000000000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:24:35</t>
+          <t>06:25:32</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.73</v>
+        <v>2.91</v>
       </c>
       <c r="F48" t="n">
-        <v>7.12</v>
+        <v>6.5</v>
       </c>
       <c r="G48" t="n">
-        <v>5.6</v>
+        <v>21.1</v>
       </c>
       <c r="H48" t="n">
-        <v>18.1</v>
+        <v>30.3</v>
       </c>
       <c r="I48" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>-119.47</v>
+        <v>70.66</v>
       </c>
       <c r="K48" t="n">
-        <v>31.28</v>
+        <v>12.88</v>
       </c>
       <c r="L48" t="n">
-        <v>123.5</v>
+        <v>71.83</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:26:37</t>
+          <t>06:27:56</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.83</v>
+        <v>3.27</v>
       </c>
       <c r="F49" t="n">
-        <v>6.43</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="G49" t="n">
-        <v>12</v>
+        <v>10.8</v>
       </c>
       <c r="H49" t="n">
-        <v>16.1</v>
+        <v>21.8</v>
       </c>
       <c r="I49" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J49" t="n">
-        <v>12.58</v>
+        <v>-65.22</v>
       </c>
       <c r="K49" t="n">
-        <v>-93.95999999999999</v>
+        <v>0.09</v>
       </c>
       <c r="L49" t="n">
-        <v>94.8</v>
+        <v>65.22</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:30:54</t>
+          <t>06:33:58</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.68</v>
+        <v>3</v>
       </c>
       <c r="F50" t="n">
-        <v>6.82</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G50" t="n">
-        <v>12.4</v>
+        <v>359</v>
       </c>
       <c r="H50" t="n">
-        <v>20.2</v>
+        <v>56</v>
       </c>
       <c r="I50" t="n">
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>4.5</v>
+        <v>-100.26</v>
       </c>
       <c r="K50" t="n">
-        <v>-140.62</v>
+        <v>4.29</v>
       </c>
       <c r="L50" t="n">
-        <v>140.69</v>
+        <v>100.36</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:32:42</t>
+          <t>06:35:53</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.21</v>
+        <v>2.95</v>
       </c>
       <c r="F51" t="n">
-        <v>9.279999999999999</v>
+        <v>8.81</v>
       </c>
       <c r="G51" t="n">
-        <v>8.199999999999999</v>
+        <v>19.4</v>
       </c>
       <c r="H51" t="n">
-        <v>22.1</v>
+        <v>51.9</v>
       </c>
       <c r="I51" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>76.70999999999999</v>
+        <v>75.29000000000001</v>
       </c>
       <c r="K51" t="n">
-        <v>141.03</v>
+        <v>66.45</v>
       </c>
       <c r="L51" t="n">
-        <v>160.55</v>
+        <v>100.42</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:34:25</t>
+          <t>06:37:20</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3.29</v>
+        <v>4.05</v>
       </c>
       <c r="F52" t="n">
-        <v>8.19</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G52" t="n">
-        <v>11.7</v>
+        <v>12.7</v>
       </c>
       <c r="H52" t="n">
-        <v>16.7</v>
+        <v>19.9</v>
       </c>
       <c r="I52" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>37.29</v>
+        <v>-118.15</v>
       </c>
       <c r="K52" t="n">
-        <v>92.34999999999999</v>
+        <v>35.33</v>
       </c>
       <c r="L52" t="n">
-        <v>99.59999999999999</v>
+        <v>123.32</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:39:00</t>
+          <t>06:43:29</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.93</v>
+        <v>3.08</v>
       </c>
       <c r="F53" t="n">
-        <v>9.390000000000001</v>
+        <v>7.62</v>
       </c>
       <c r="G53" t="n">
-        <v>8.5</v>
+        <v>357.5</v>
       </c>
       <c r="H53" t="n">
-        <v>16.6</v>
+        <v>16.4</v>
       </c>
       <c r="I53" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>-88.11</v>
+        <v>-106.56</v>
       </c>
       <c r="K53" t="n">
-        <v>-222.42</v>
+        <v>145.07</v>
       </c>
       <c r="L53" t="n">
-        <v>239.24</v>
+        <v>180</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:41:00</t>
+          <t>06:44:36</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.93</v>
+        <v>3.06</v>
       </c>
       <c r="F54" t="n">
-        <v>7.89</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="G54" t="n">
-        <v>13.2</v>
+        <v>11.5</v>
       </c>
       <c r="H54" t="n">
-        <v>19.6</v>
+        <v>28.8</v>
       </c>
       <c r="I54" t="n">
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>-74.05</v>
+        <v>178.63</v>
       </c>
       <c r="K54" t="n">
-        <v>-184.96</v>
+        <v>10.23</v>
       </c>
       <c r="L54" t="n">
-        <v>199.23</v>
+        <v>178.92</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:42:19</t>
+          <t>06:46:33</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.9</v>
+        <v>3.23</v>
       </c>
       <c r="F55" t="n">
-        <v>6.12</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G55" t="n">
-        <v>351</v>
+        <v>17.7</v>
       </c>
       <c r="H55" t="n">
-        <v>24.2</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>140.24</v>
+        <v>-68.92</v>
       </c>
       <c r="K55" t="n">
-        <v>7.88</v>
+        <v>184.63</v>
       </c>
       <c r="L55" t="n">
-        <v>140.47</v>
+        <v>197.07</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:46:49</t>
+          <t>06:51:40</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="F56" t="n">
-        <v>7.18</v>
+        <v>7.96</v>
       </c>
       <c r="G56" t="n">
-        <v>6</v>
+        <v>0.7</v>
       </c>
       <c r="H56" t="n">
-        <v>18.4</v>
+        <v>51.4</v>
       </c>
       <c r="I56" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>258.91</v>
+        <v>-111.58</v>
       </c>
       <c r="K56" t="n">
-        <v>-171.53</v>
+        <v>-129.16</v>
       </c>
       <c r="L56" t="n">
-        <v>310.58</v>
+        <v>170.68</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:48:36</t>
+          <t>06:53:35</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.48</v>
+        <v>2.98</v>
       </c>
       <c r="F57" t="n">
-        <v>6.6</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G57" t="n">
-        <v>11.6</v>
+        <v>18</v>
       </c>
       <c r="H57" t="n">
-        <v>19.2</v>
+        <v>50.3</v>
       </c>
       <c r="I57" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>154.71</v>
+        <v>-2.62</v>
       </c>
       <c r="K57" t="n">
-        <v>-158.08</v>
+        <v>-212.45</v>
       </c>
       <c r="L57" t="n">
-        <v>221.19</v>
+        <v>212.46</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:50:16</t>
+          <t>06:55:32</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.87</v>
+        <v>3.02</v>
       </c>
       <c r="F58" t="n">
-        <v>9.539999999999999</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="G58" t="n">
-        <v>15.3</v>
+        <v>18.7</v>
       </c>
       <c r="H58" t="n">
-        <v>18.9</v>
+        <v>21.1</v>
       </c>
       <c r="I58" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>231.22</v>
+        <v>196.35</v>
       </c>
       <c r="K58" t="n">
-        <v>133.38</v>
+        <v>-112.08</v>
       </c>
       <c r="L58" t="n">
-        <v>266.94</v>
+        <v>226.08</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06:59:56</t>
+          <t>07:08:32</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3.07</v>
+        <v>2.93</v>
       </c>
       <c r="F59" t="n">
-        <v>6.66</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G59" t="n">
-        <v>21.3</v>
+        <v>33</v>
       </c>
       <c r="H59" t="n">
-        <v>16.9</v>
+        <v>47.2</v>
       </c>
       <c r="I59" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>-62.58</v>
+        <v>7.24</v>
       </c>
       <c r="K59" t="n">
-        <v>-20.92</v>
+        <v>44.29</v>
       </c>
       <c r="L59" t="n">
-        <v>65.98999999999999</v>
+        <v>44.88</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:02:05</t>
+          <t>07:09:53</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>3.01</v>
+        <v>3.08</v>
       </c>
       <c r="F60" t="n">
-        <v>8.92</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G60" t="n">
-        <v>358.8</v>
+        <v>14.8</v>
       </c>
       <c r="H60" t="n">
-        <v>19.9</v>
+        <v>25.8</v>
       </c>
       <c r="I60" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J60" t="n">
-        <v>-43.34</v>
+        <v>-16.81</v>
       </c>
       <c r="K60" t="n">
-        <v>69.36</v>
+        <v>-44.58</v>
       </c>
       <c r="L60" t="n">
-        <v>81.78</v>
+        <v>47.65</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:03:41</t>
+          <t>07:11:19</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.88</v>
+        <v>3.54</v>
       </c>
       <c r="F61" t="n">
-        <v>8.029999999999999</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G61" t="n">
-        <v>18.3</v>
+        <v>1.9</v>
       </c>
       <c r="H61" t="n">
-        <v>24.2</v>
+        <v>30</v>
       </c>
       <c r="I61" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>1.82</v>
+        <v>-70.68000000000001</v>
       </c>
       <c r="K61" t="n">
-        <v>79.56999999999999</v>
+        <v>36.81</v>
       </c>
       <c r="L61" t="n">
-        <v>79.59</v>
+        <v>79.69</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:07:47</t>
+          <t>07:17:36</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.06</v>
+        <v>2.8</v>
       </c>
       <c r="F62" t="n">
-        <v>6.3</v>
+        <v>7.09</v>
       </c>
       <c r="G62" t="n">
-        <v>3.6</v>
+        <v>26</v>
       </c>
       <c r="H62" t="n">
-        <v>27.3</v>
+        <v>17</v>
       </c>
       <c r="I62" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>-21.08</v>
+        <v>66.69</v>
       </c>
       <c r="K62" t="n">
-        <v>-144.35</v>
+        <v>-69.06999999999999</v>
       </c>
       <c r="L62" t="n">
-        <v>145.88</v>
+        <v>96.01000000000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:08:51</t>
+          <t>07:19:52</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.7</v>
+        <v>2.98</v>
       </c>
       <c r="F63" t="n">
-        <v>6.98</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G63" t="n">
-        <v>2.7</v>
+        <v>9.9</v>
       </c>
       <c r="H63" t="n">
-        <v>19.7</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="I63" t="n">
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-92.08</v>
+        <v>67.13</v>
       </c>
       <c r="K63" t="n">
-        <v>35.13</v>
+        <v>13.97</v>
       </c>
       <c r="L63" t="n">
-        <v>98.55</v>
+        <v>68.56999999999999</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:10:49</t>
+          <t>07:20:57</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.69</v>
+        <v>3.17</v>
       </c>
       <c r="F64" t="n">
-        <v>8.449999999999999</v>
+        <v>5.37</v>
       </c>
       <c r="G64" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
       <c r="H64" t="n">
-        <v>19</v>
+        <v>18.1</v>
       </c>
       <c r="I64" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>-65.13</v>
+        <v>-59.59</v>
       </c>
       <c r="K64" t="n">
-        <v>-62.51</v>
+        <v>-28.86</v>
       </c>
       <c r="L64" t="n">
-        <v>90.28</v>
+        <v>66.20999999999999</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:14:41</t>
+          <t>07:25:42</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.45</v>
+        <v>3.56</v>
       </c>
       <c r="F65" t="n">
-        <v>6.19</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G65" t="n">
-        <v>7.9</v>
+        <v>3.2</v>
       </c>
       <c r="H65" t="n">
-        <v>23.3</v>
+        <v>37.4</v>
       </c>
       <c r="I65" t="n">
         <v>16</v>
       </c>
       <c r="J65" t="n">
-        <v>143.17</v>
+        <v>153.49</v>
       </c>
       <c r="K65" t="n">
-        <v>-67.69</v>
+        <v>158.27</v>
       </c>
       <c r="L65" t="n">
-        <v>158.37</v>
+        <v>220.48</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:17:21</t>
+          <t>07:27:22</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>3.18</v>
+        <v>2.71</v>
       </c>
       <c r="F66" t="n">
-        <v>9.539999999999999</v>
+        <v>8.52</v>
       </c>
       <c r="G66" t="n">
-        <v>8</v>
+        <v>11.4</v>
       </c>
       <c r="H66" t="n">
-        <v>18</v>
+        <v>29.9</v>
       </c>
       <c r="I66" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>133.23</v>
+        <v>110.82</v>
       </c>
       <c r="K66" t="n">
-        <v>4.87</v>
+        <v>28.55</v>
       </c>
       <c r="L66" t="n">
-        <v>133.32</v>
+        <v>114.44</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:19:15</t>
+          <t>07:29:08</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.89</v>
+        <v>3.19</v>
       </c>
       <c r="F67" t="n">
-        <v>9.19</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G67" t="n">
-        <v>18.1</v>
+        <v>9</v>
       </c>
       <c r="H67" t="n">
-        <v>17</v>
+        <v>65.8</v>
       </c>
       <c r="I67" t="n">
         <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>-36.68</v>
+        <v>-23.82</v>
       </c>
       <c r="K67" t="n">
-        <v>96.2</v>
+        <v>-117.72</v>
       </c>
       <c r="L67" t="n">
-        <v>102.96</v>
+        <v>120.11</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:23:48</t>
+          <t>07:33:35</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>4.12</v>
+        <v>3.53</v>
       </c>
       <c r="F68" t="n">
-        <v>9.539999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="G68" t="n">
-        <v>20.9</v>
+        <v>348.5</v>
       </c>
       <c r="H68" t="n">
-        <v>21.7</v>
+        <v>25</v>
       </c>
       <c r="I68" t="n">
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>152.38</v>
+        <v>-47.3</v>
       </c>
       <c r="K68" t="n">
-        <v>252.09</v>
+        <v>169.76</v>
       </c>
       <c r="L68" t="n">
-        <v>294.57</v>
+        <v>176.23</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:24:52</t>
+          <t>07:35:26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>3.3</v>
+        <v>3.39</v>
       </c>
       <c r="F69" t="n">
-        <v>9.539999999999999</v>
+        <v>7.43</v>
       </c>
       <c r="G69" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="H69" t="n">
-        <v>17.4</v>
+        <v>57.1</v>
       </c>
       <c r="I69" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>-49.44</v>
+        <v>215.42</v>
       </c>
       <c r="K69" t="n">
-        <v>-257.91</v>
+        <v>-22.89</v>
       </c>
       <c r="L69" t="n">
-        <v>262.61</v>
+        <v>216.63</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:27:11</t>
+          <t>07:37:26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>3.4</v>
+        <v>2.98</v>
       </c>
       <c r="F70" t="n">
-        <v>9.539999999999999</v>
+        <v>8.42</v>
       </c>
       <c r="G70" t="n">
-        <v>14.9</v>
+        <v>19.7</v>
       </c>
       <c r="H70" t="n">
-        <v>13.9</v>
+        <v>67.5</v>
       </c>
       <c r="I70" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>-171.21</v>
+        <v>-140.37</v>
       </c>
       <c r="K70" t="n">
-        <v>87.97</v>
+        <v>18.8</v>
       </c>
       <c r="L70" t="n">
-        <v>192.49</v>
+        <v>141.62</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:31:46</t>
+          <t>07:42:03</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.85</v>
+        <v>2.91</v>
       </c>
       <c r="F71" t="n">
-        <v>8.43</v>
+        <v>6.94</v>
       </c>
       <c r="G71" t="n">
-        <v>2</v>
+        <v>10.8</v>
       </c>
       <c r="H71" t="n">
-        <v>16.3</v>
+        <v>63.2</v>
       </c>
       <c r="I71" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>100.98</v>
+        <v>-30.71</v>
       </c>
       <c r="K71" t="n">
-        <v>339.98</v>
+        <v>-196.64</v>
       </c>
       <c r="L71" t="n">
-        <v>354.66</v>
+        <v>199.02</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:32:53</t>
+          <t>07:44:05</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="F72" t="n">
-        <v>9.539999999999999</v>
+        <v>9.23</v>
       </c>
       <c r="G72" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="H72" t="n">
-        <v>27.5</v>
+        <v>58.5</v>
       </c>
       <c r="I72" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>198.24</v>
+        <v>130.96</v>
       </c>
       <c r="K72" t="n">
-        <v>-89.31</v>
+        <v>213.95</v>
       </c>
       <c r="L72" t="n">
-        <v>217.43</v>
+        <v>250.85</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:34:02</t>
+          <t>07:46:18</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.84</v>
+        <v>3.06</v>
       </c>
       <c r="F73" t="n">
-        <v>9.539999999999999</v>
+        <v>6.68</v>
       </c>
       <c r="G73" t="n">
-        <v>5.3</v>
+        <v>11.8</v>
       </c>
       <c r="H73" t="n">
-        <v>25.6</v>
+        <v>13.8</v>
       </c>
       <c r="I73" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>291.34</v>
+        <v>216.75</v>
       </c>
       <c r="K73" t="n">
-        <v>129.51</v>
+        <v>-116.06</v>
       </c>
       <c r="L73" t="n">
-        <v>318.83</v>
+        <v>245.86</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:41:10</t>
+          <t>07:55:10</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>2.98</v>
+        <v>3.34</v>
       </c>
       <c r="F74" t="n">
-        <v>8.26</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G74" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="H74" t="n">
-        <v>21.7</v>
+        <v>26.8</v>
       </c>
       <c r="I74" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>-80.54000000000001</v>
+        <v>-60.24</v>
       </c>
       <c r="K74" t="n">
-        <v>-56.58</v>
+        <v>6.39</v>
       </c>
       <c r="L74" t="n">
-        <v>98.43000000000001</v>
+        <v>60.58</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:42:04</t>
+          <t>07:57:14</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.69</v>
+        <v>3.24</v>
       </c>
       <c r="F75" t="n">
-        <v>5.14</v>
+        <v>8.15</v>
       </c>
       <c r="G75" t="n">
-        <v>21.7</v>
+        <v>6.5</v>
       </c>
       <c r="H75" t="n">
-        <v>15.2</v>
+        <v>16.1</v>
       </c>
       <c r="I75" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-66.59999999999999</v>
+        <v>20.88</v>
       </c>
       <c r="K75" t="n">
-        <v>14.67</v>
+        <v>49.09</v>
       </c>
       <c r="L75" t="n">
-        <v>68.19</v>
+        <v>53.34</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:43:14</t>
+          <t>07:58:06</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.51</v>
+        <v>3.22</v>
       </c>
       <c r="F76" t="n">
         <v>9.539999999999999</v>
       </c>
       <c r="G76" t="n">
-        <v>16.9</v>
+        <v>10.9</v>
       </c>
       <c r="H76" t="n">
-        <v>24.8</v>
+        <v>46.6</v>
       </c>
       <c r="I76" t="n">
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-61.93</v>
+        <v>-45.19</v>
       </c>
       <c r="K76" t="n">
-        <v>54.31</v>
+        <v>44.54</v>
       </c>
       <c r="L76" t="n">
-        <v>82.37</v>
+        <v>63.46</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:48:35</t>
+          <t>08:02:29</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>2.72</v>
+        <v>3.57</v>
       </c>
       <c r="F77" t="n">
-        <v>9.539999999999999</v>
+        <v>8.25</v>
       </c>
       <c r="G77" t="n">
-        <v>354.5</v>
+        <v>15.7</v>
       </c>
       <c r="H77" t="n">
-        <v>21.3</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="I77" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J77" t="n">
-        <v>-83.15000000000001</v>
+        <v>24.01</v>
       </c>
       <c r="K77" t="n">
-        <v>-12.61</v>
+        <v>98.33</v>
       </c>
       <c r="L77" t="n">
-        <v>84.09999999999999</v>
+        <v>101.22</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:49:35</t>
+          <t>08:03:28</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="F78" t="n">
-        <v>9.539999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="G78" t="n">
-        <v>11.7</v>
+        <v>16.3</v>
       </c>
       <c r="H78" t="n">
-        <v>21.2</v>
+        <v>35.1</v>
       </c>
       <c r="I78" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J78" t="n">
-        <v>-106.69</v>
+        <v>-70.22</v>
       </c>
       <c r="K78" t="n">
-        <v>-76.20999999999999</v>
+        <v>-6.2</v>
       </c>
       <c r="L78" t="n">
-        <v>131.11</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:51:04</t>
+          <t>08:05:05</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.64</v>
+        <v>2.89</v>
       </c>
       <c r="F79" t="n">
-        <v>8.25</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G79" t="n">
-        <v>21.7</v>
+        <v>3.6</v>
       </c>
       <c r="H79" t="n">
-        <v>20.2</v>
+        <v>16</v>
       </c>
       <c r="I79" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>77.20999999999999</v>
+        <v>-57.74</v>
       </c>
       <c r="K79" t="n">
-        <v>-11.03</v>
+        <v>-55.62</v>
       </c>
       <c r="L79" t="n">
-        <v>78</v>
+        <v>80.17</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07:54:15</t>
+          <t>08:09:55</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.28</v>
+        <v>3.13</v>
       </c>
       <c r="F80" t="n">
-        <v>6.09</v>
+        <v>8.48</v>
       </c>
       <c r="G80" t="n">
-        <v>5.5</v>
+        <v>0.7</v>
       </c>
       <c r="H80" t="n">
-        <v>25.5</v>
+        <v>29.6</v>
       </c>
       <c r="I80" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J80" t="n">
-        <v>-53.44</v>
+        <v>-24.35</v>
       </c>
       <c r="K80" t="n">
-        <v>82.97</v>
+        <v>72.75</v>
       </c>
       <c r="L80" t="n">
-        <v>98.69</v>
+        <v>76.70999999999999</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07:56:13</t>
+          <t>08:11:46</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.8</v>
+        <v>3.23</v>
       </c>
       <c r="F81" t="n">
-        <v>8.970000000000001</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G81" t="n">
-        <v>7.3</v>
+        <v>6.4</v>
       </c>
       <c r="H81" t="n">
-        <v>21.1</v>
+        <v>43.2</v>
       </c>
       <c r="I81" t="n">
         <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>114</v>
+        <v>-89.12</v>
       </c>
       <c r="K81" t="n">
-        <v>123.42</v>
+        <v>-3.29</v>
       </c>
       <c r="L81" t="n">
-        <v>168.01</v>
+        <v>89.18000000000001</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>07:58:27</t>
+          <t>08:12:52</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.21</v>
+        <v>2.57</v>
       </c>
       <c r="F82" t="n">
         <v>9.539999999999999</v>
       </c>
       <c r="G82" t="n">
-        <v>19.6</v>
+        <v>12.8</v>
       </c>
       <c r="H82" t="n">
-        <v>30.3</v>
+        <v>24</v>
       </c>
       <c r="I82" t="n">
         <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>-138.74</v>
+        <v>28.91</v>
       </c>
       <c r="K82" t="n">
-        <v>-12.32</v>
+        <v>88.61</v>
       </c>
       <c r="L82" t="n">
-        <v>139.29</v>
+        <v>93.20999999999999</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:03:13</t>
+          <t>08:19:19</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>3.02</v>
+        <v>3.16</v>
       </c>
       <c r="F83" t="n">
-        <v>7.57</v>
+        <v>7.02</v>
       </c>
       <c r="G83" t="n">
-        <v>356.8</v>
+        <v>15.9</v>
       </c>
       <c r="H83" t="n">
-        <v>14</v>
+        <v>56.6</v>
       </c>
       <c r="I83" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>-129.1</v>
+        <v>-192.33</v>
       </c>
       <c r="K83" t="n">
-        <v>-141.67</v>
+        <v>-34.81</v>
       </c>
       <c r="L83" t="n">
-        <v>191.67</v>
+        <v>195.45</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:05:35</t>
+          <t>08:20:55</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.94</v>
+        <v>3.12</v>
       </c>
       <c r="F84" t="n">
-        <v>8.539999999999999</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G84" t="n">
-        <v>5.6</v>
+        <v>7.3</v>
       </c>
       <c r="H84" t="n">
-        <v>17.1</v>
+        <v>22.1</v>
       </c>
       <c r="I84" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>130.68</v>
+        <v>-4.95</v>
       </c>
       <c r="K84" t="n">
-        <v>222.25</v>
+        <v>-192.59</v>
       </c>
       <c r="L84" t="n">
-        <v>257.82</v>
+        <v>192.65</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:07:20</t>
+          <t>08:21:51</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>3.15</v>
+        <v>3.33</v>
       </c>
       <c r="F85" t="n">
-        <v>8.83</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G85" t="n">
-        <v>20.5</v>
+        <v>10.5</v>
       </c>
       <c r="H85" t="n">
-        <v>21.2</v>
+        <v>38.4</v>
       </c>
       <c r="I85" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J85" t="n">
-        <v>-32.14</v>
+        <v>-91.47</v>
       </c>
       <c r="K85" t="n">
-        <v>173.93</v>
+        <v>108.25</v>
       </c>
       <c r="L85" t="n">
-        <v>176.88</v>
+        <v>141.72</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:13:25</t>
+          <t>08:26:25</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3.12</v>
+        <v>3.89</v>
       </c>
       <c r="F86" t="n">
-        <v>6.89</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G86" t="n">
-        <v>3.8</v>
+        <v>18.4</v>
       </c>
       <c r="H86" t="n">
-        <v>22.8</v>
+        <v>68.2</v>
       </c>
       <c r="I86" t="n">
         <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>163.53</v>
+        <v>-13.75</v>
       </c>
       <c r="K86" t="n">
-        <v>158.91</v>
+        <v>-276.53</v>
       </c>
       <c r="L86" t="n">
-        <v>228.02</v>
+        <v>276.87</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:14:53</t>
+          <t>08:27:11</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="F87" t="n">
-        <v>8.83</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G87" t="n">
-        <v>357.4</v>
+        <v>9</v>
       </c>
       <c r="H87" t="n">
-        <v>13.1</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="I87" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>-19.07</v>
+        <v>10.17</v>
       </c>
       <c r="K87" t="n">
-        <v>-41.18</v>
+        <v>217.3</v>
       </c>
       <c r="L87" t="n">
-        <v>45.38</v>
+        <v>217.54</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:15:54</t>
+          <t>08:28:57</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.3</v>
+        <v>3.87</v>
       </c>
       <c r="F88" t="n">
-        <v>9.539999999999999</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="G88" t="n">
-        <v>12.1</v>
+        <v>24.2</v>
       </c>
       <c r="H88" t="n">
-        <v>21.8</v>
+        <v>28.6</v>
       </c>
       <c r="I88" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-252.13</v>
+        <v>-185.33</v>
       </c>
       <c r="K88" t="n">
-        <v>-132.74</v>
+        <v>-173.99</v>
       </c>
       <c r="L88" t="n">
-        <v>284.94</v>
+        <v>254.2</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-10.xlsx
+++ b/output/2024-07-10.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.66</v>
+        <v>2.66</v>
       </c>
       <c r="F14" t="n">
-        <v>5.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>7.8</v>
+        <v>16.6</v>
       </c>
       <c r="H14" t="n">
-        <v>46.7</v>
+        <v>43.2</v>
       </c>
       <c r="I14" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J14" t="n">
-        <v>47.39</v>
+        <v>-32.19</v>
       </c>
       <c r="K14" t="n">
-        <v>32</v>
+        <v>37.39</v>
       </c>
       <c r="L14" t="n">
-        <v>57.18</v>
+        <v>49.34</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:45:38</t>
+          <t>04:45:09</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.73</v>
+        <v>2.58</v>
       </c>
       <c r="F15" t="n">
-        <v>6.17</v>
+        <v>6.2</v>
       </c>
       <c r="G15" t="n">
-        <v>16.7</v>
+        <v>355</v>
       </c>
       <c r="H15" t="n">
-        <v>69.09999999999999</v>
+        <v>34.8</v>
       </c>
       <c r="I15" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J15" t="n">
-        <v>22.38</v>
+        <v>30.76</v>
       </c>
       <c r="K15" t="n">
-        <v>42.93</v>
+        <v>37.63</v>
       </c>
       <c r="L15" t="n">
-        <v>48.41</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:46:58</t>
+          <t>04:47:18</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.62</v>
+        <v>2.94</v>
       </c>
       <c r="F16" t="n">
-        <v>8.210000000000001</v>
+        <v>6.33</v>
       </c>
       <c r="G16" t="n">
-        <v>5.4</v>
+        <v>11.3</v>
       </c>
       <c r="H16" t="n">
-        <v>40.9</v>
+        <v>54.3</v>
       </c>
       <c r="I16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>-27.28</v>
+        <v>-31.54</v>
       </c>
       <c r="K16" t="n">
-        <v>19.59</v>
+        <v>42.72</v>
       </c>
       <c r="L16" t="n">
-        <v>33.59</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:52:07</t>
+          <t>04:50:54</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>4.04</v>
+        <v>3.01</v>
       </c>
       <c r="F17" t="n">
-        <v>9.539999999999999</v>
+        <v>7.93</v>
       </c>
       <c r="G17" t="n">
-        <v>20.9</v>
+        <v>18.2</v>
       </c>
       <c r="H17" t="n">
-        <v>86.8</v>
+        <v>76.8</v>
       </c>
       <c r="I17" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>57.39</v>
+        <v>61.39</v>
       </c>
       <c r="K17" t="n">
-        <v>-67.15000000000001</v>
+        <v>-54.38</v>
       </c>
       <c r="L17" t="n">
-        <v>88.33</v>
+        <v>82.01000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:53:14</t>
+          <t>04:51:55</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="F18" t="n">
-        <v>9.539999999999999</v>
+        <v>5.42</v>
       </c>
       <c r="G18" t="n">
-        <v>13.6</v>
+        <v>11.4</v>
       </c>
       <c r="H18" t="n">
-        <v>47.2</v>
+        <v>30.9</v>
       </c>
       <c r="I18" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J18" t="n">
-        <v>-43.29</v>
+        <v>44.97</v>
       </c>
       <c r="K18" t="n">
-        <v>42.54</v>
+        <v>70.27</v>
       </c>
       <c r="L18" t="n">
-        <v>60.69</v>
+        <v>83.43000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:55:12</t>
+          <t>04:54:30</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.86</v>
+        <v>3.19</v>
       </c>
       <c r="F19" t="n">
-        <v>9.539999999999999</v>
+        <v>9.09</v>
       </c>
       <c r="G19" t="n">
-        <v>13.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>64.40000000000001</v>
+        <v>41.6</v>
       </c>
       <c r="I19" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>-41.05</v>
+        <v>39.72</v>
       </c>
       <c r="K19" t="n">
-        <v>35.48</v>
+        <v>41.78</v>
       </c>
       <c r="L19" t="n">
-        <v>54.26</v>
+        <v>57.65</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04:58:26</t>
+          <t>04:59:00</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.45</v>
+        <v>3.19</v>
       </c>
       <c r="F20" t="n">
-        <v>8.06</v>
+        <v>5.84</v>
       </c>
       <c r="G20" t="n">
-        <v>22.9</v>
+        <v>0.1</v>
       </c>
       <c r="H20" t="n">
-        <v>66.5</v>
+        <v>75.3</v>
       </c>
       <c r="I20" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J20" t="n">
-        <v>102.69</v>
+        <v>-10.61</v>
       </c>
       <c r="K20" t="n">
-        <v>72.34999999999999</v>
+        <v>-126.44</v>
       </c>
       <c r="L20" t="n">
-        <v>125.62</v>
+        <v>126.88</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>04:59:45</t>
+          <t>05:00:34</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.65</v>
+        <v>2.83</v>
       </c>
       <c r="F21" t="n">
-        <v>5.64</v>
+        <v>5.36</v>
       </c>
       <c r="G21" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="H21" t="n">
-        <v>28.1</v>
+        <v>61</v>
       </c>
       <c r="I21" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>-95.36</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>1.42</v>
+        <v>-58.16</v>
       </c>
       <c r="L21" t="n">
-        <v>95.37</v>
+        <v>100.82</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:00:54</t>
+          <t>05:01:31</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="F22" t="n">
-        <v>5.7</v>
+        <v>7.97</v>
       </c>
       <c r="G22" t="n">
-        <v>8.5</v>
+        <v>3.2</v>
       </c>
       <c r="H22" t="n">
-        <v>40.2</v>
+        <v>22.8</v>
       </c>
       <c r="I22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J22" t="n">
-        <v>-54.42</v>
+        <v>72.22</v>
       </c>
       <c r="K22" t="n">
-        <v>93.3</v>
+        <v>-123</v>
       </c>
       <c r="L22" t="n">
-        <v>108.01</v>
+        <v>142.64</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:05:54</t>
+          <t>05:05:47</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.11</v>
+        <v>2.99</v>
       </c>
       <c r="F23" t="n">
-        <v>6.37</v>
+        <v>8.01</v>
       </c>
       <c r="G23" t="n">
-        <v>15.1</v>
+        <v>359.2</v>
       </c>
       <c r="H23" t="n">
-        <v>48</v>
+        <v>3.9</v>
       </c>
       <c r="I23" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J23" t="n">
-        <v>4.22</v>
+        <v>-185.07</v>
       </c>
       <c r="K23" t="n">
-        <v>-122.95</v>
+        <v>99.61</v>
       </c>
       <c r="L23" t="n">
-        <v>123.02</v>
+        <v>210.18</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:07:21</t>
+          <t>05:08:02</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="F24" t="n">
-        <v>3.92</v>
+        <v>7.75</v>
       </c>
       <c r="G24" t="n">
-        <v>10</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>58.7</v>
+        <v>63.1</v>
       </c>
       <c r="I24" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>-50.95</v>
+        <v>68.22</v>
       </c>
       <c r="K24" t="n">
-        <v>117.71</v>
+        <v>152.34</v>
       </c>
       <c r="L24" t="n">
-        <v>128.27</v>
+        <v>166.92</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:08:09</t>
+          <t>05:10:12</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="F25" t="n">
-        <v>6.41</v>
+        <v>6.86</v>
       </c>
       <c r="G25" t="n">
-        <v>13.1</v>
+        <v>26.3</v>
       </c>
       <c r="H25" t="n">
-        <v>59</v>
+        <v>15</v>
       </c>
       <c r="I25" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-120.33</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>-56.96</v>
+        <v>149.69</v>
       </c>
       <c r="L25" t="n">
-        <v>133.13</v>
+        <v>172.44</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:12:52</t>
+          <t>05:13:50</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.05</v>
+        <v>2.61</v>
       </c>
       <c r="F26" t="n">
-        <v>7.33</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>12.5</v>
+        <v>4.5</v>
       </c>
       <c r="H26" t="n">
-        <v>59.1</v>
+        <v>43</v>
       </c>
       <c r="I26" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J26" t="n">
-        <v>-173.88</v>
+        <v>-185.68</v>
       </c>
       <c r="K26" t="n">
-        <v>47.88</v>
+        <v>58.91</v>
       </c>
       <c r="L26" t="n">
-        <v>180.35</v>
+        <v>194.8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:15:17</t>
+          <t>05:16:16</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="F27" t="n">
-        <v>5.66</v>
+        <v>3.59</v>
       </c>
       <c r="G27" t="n">
-        <v>4.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H27" t="n">
-        <v>41.5</v>
+        <v>37.1</v>
       </c>
       <c r="I27" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J27" t="n">
-        <v>-21.31</v>
+        <v>64.16</v>
       </c>
       <c r="K27" t="n">
-        <v>-196.24</v>
+        <v>-213.56</v>
       </c>
       <c r="L27" t="n">
-        <v>197.39</v>
+        <v>222.99</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:16:45</t>
+          <t>05:17:09</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.54</v>
+        <v>2.9</v>
       </c>
       <c r="F28" t="n">
-        <v>5.73</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G28" t="n">
-        <v>9.1</v>
+        <v>16.7</v>
       </c>
       <c r="H28" t="n">
-        <v>40.4</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J28" t="n">
-        <v>-9.48</v>
+        <v>132.91</v>
       </c>
       <c r="K28" t="n">
-        <v>188.78</v>
+        <v>230.22</v>
       </c>
       <c r="L28" t="n">
-        <v>189.01</v>
+        <v>265.83</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:29:46</t>
+          <t>05:27:05</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.01</v>
+        <v>2.73</v>
       </c>
       <c r="F29" t="n">
-        <v>4.45</v>
+        <v>8.68</v>
       </c>
       <c r="G29" t="n">
-        <v>3</v>
+        <v>22.6</v>
       </c>
       <c r="H29" t="n">
-        <v>75.2</v>
+        <v>31.1</v>
       </c>
       <c r="I29" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J29" t="n">
-        <v>-45.26</v>
+        <v>32.41</v>
       </c>
       <c r="K29" t="n">
-        <v>33.33</v>
+        <v>-17.11</v>
       </c>
       <c r="L29" t="n">
-        <v>56.21</v>
+        <v>36.65</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:32:06</t>
+          <t>05:29:03</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.21</v>
+        <v>2.72</v>
       </c>
       <c r="F30" t="n">
-        <v>8.56</v>
+        <v>7.24</v>
       </c>
       <c r="G30" t="n">
-        <v>20.7</v>
+        <v>27.6</v>
       </c>
       <c r="H30" t="n">
-        <v>100</v>
+        <v>18.6</v>
       </c>
       <c r="I30" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J30" t="n">
-        <v>13.52</v>
+        <v>-23.9</v>
       </c>
       <c r="K30" t="n">
-        <v>-42.83</v>
+        <v>31.59</v>
       </c>
       <c r="L30" t="n">
-        <v>44.92</v>
+        <v>39.62</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:34:17</t>
+          <t>05:30:37</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.89</v>
+        <v>2.83</v>
       </c>
       <c r="F31" t="n">
-        <v>7.5</v>
+        <v>5.11</v>
       </c>
       <c r="G31" t="n">
-        <v>2.9</v>
+        <v>13.6</v>
       </c>
       <c r="H31" t="n">
-        <v>58.4</v>
+        <v>47.2</v>
       </c>
       <c r="I31" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>41.75</v>
+        <v>-39.06</v>
       </c>
       <c r="K31" t="n">
-        <v>15.2</v>
+        <v>27.04</v>
       </c>
       <c r="L31" t="n">
-        <v>44.43</v>
+        <v>47.51</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:40:06</t>
+          <t>05:35:02</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="F32" t="n">
-        <v>8.74</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G32" t="n">
-        <v>16.4</v>
+        <v>18.7</v>
       </c>
       <c r="H32" t="n">
-        <v>18.7</v>
+        <v>50.2</v>
       </c>
       <c r="I32" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>-84.20999999999999</v>
+        <v>60.82</v>
       </c>
       <c r="K32" t="n">
-        <v>8.460000000000001</v>
+        <v>44.59</v>
       </c>
       <c r="L32" t="n">
-        <v>84.64</v>
+        <v>75.42</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:42:05</t>
+          <t>05:36:35</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.85</v>
+        <v>2.92</v>
       </c>
       <c r="F33" t="n">
-        <v>6</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G33" t="n">
-        <v>359.3</v>
+        <v>0.3</v>
       </c>
       <c r="H33" t="n">
-        <v>15.2</v>
+        <v>8.9</v>
       </c>
       <c r="I33" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J33" t="n">
-        <v>22.99</v>
+        <v>34.5</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-71.7</v>
       </c>
       <c r="L33" t="n">
-        <v>22.99</v>
+        <v>79.56999999999999</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:43:10</t>
+          <t>05:39:31</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3.02</v>
+        <v>2.57</v>
       </c>
       <c r="F34" t="n">
-        <v>9.18</v>
+        <v>5.69</v>
       </c>
       <c r="G34" t="n">
-        <v>14.7</v>
+        <v>30.4</v>
       </c>
       <c r="H34" t="n">
-        <v>46.7</v>
+        <v>30.7</v>
       </c>
       <c r="I34" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J34" t="n">
-        <v>62.37</v>
+        <v>18.49</v>
       </c>
       <c r="K34" t="n">
-        <v>-37.57</v>
+        <v>-68.28</v>
       </c>
       <c r="L34" t="n">
-        <v>72.81</v>
+        <v>70.73999999999999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:48:13</t>
+          <t>05:43:51</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="F35" t="n">
-        <v>5.98</v>
+        <v>7.62</v>
       </c>
       <c r="G35" t="n">
-        <v>359.8</v>
+        <v>14</v>
       </c>
       <c r="H35" t="n">
-        <v>59.9</v>
+        <v>38</v>
       </c>
       <c r="I35" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="J35" t="n">
-        <v>95.95</v>
+        <v>-11.53</v>
       </c>
       <c r="K35" t="n">
-        <v>14.66</v>
+        <v>111.9</v>
       </c>
       <c r="L35" t="n">
-        <v>97.06</v>
+        <v>112.5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:50:33</t>
+          <t>05:46:07</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.11</v>
+        <v>2.92</v>
       </c>
       <c r="F36" t="n">
-        <v>9.18</v>
+        <v>8.34</v>
       </c>
       <c r="G36" t="n">
-        <v>1.8</v>
+        <v>19.3</v>
       </c>
       <c r="H36" t="n">
-        <v>42.3</v>
+        <v>55.4</v>
       </c>
       <c r="I36" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J36" t="n">
-        <v>122.74</v>
+        <v>61.06</v>
       </c>
       <c r="K36" t="n">
-        <v>-56.93</v>
+        <v>-106.88</v>
       </c>
       <c r="L36" t="n">
-        <v>135.3</v>
+        <v>123.09</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:52:43</t>
+          <t>05:47:02</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1594,31 +1594,31 @@
         <v>3.08</v>
       </c>
       <c r="F37" t="n">
-        <v>6.46</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G37" t="n">
         <v>3.7</v>
       </c>
       <c r="H37" t="n">
-        <v>41.2</v>
+        <v>61.7</v>
       </c>
       <c r="I37" t="n">
         <v>18</v>
       </c>
       <c r="J37" t="n">
-        <v>-46.57</v>
+        <v>-66.8</v>
       </c>
       <c r="K37" t="n">
-        <v>33.94</v>
+        <v>93.63</v>
       </c>
       <c r="L37" t="n">
-        <v>57.63</v>
+        <v>115.01</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:57:01</t>
+          <t>05:51:19</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.42</v>
+        <v>2.97</v>
       </c>
       <c r="F38" t="n">
-        <v>8.109999999999999</v>
+        <v>6.91</v>
       </c>
       <c r="G38" t="n">
-        <v>27</v>
+        <v>16.5</v>
       </c>
       <c r="H38" t="n">
-        <v>27.6</v>
+        <v>11.1</v>
       </c>
       <c r="I38" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-167.06</v>
+        <v>108.87</v>
       </c>
       <c r="K38" t="n">
-        <v>94.31999999999999</v>
+        <v>180.56</v>
       </c>
       <c r="L38" t="n">
-        <v>191.85</v>
+        <v>210.84</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:58:53</t>
+          <t>05:53:01</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="F39" t="n">
-        <v>8.869999999999999</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G39" t="n">
-        <v>6.5</v>
+        <v>12.5</v>
       </c>
       <c r="H39" t="n">
-        <v>19.5</v>
+        <v>59.1</v>
       </c>
       <c r="I39" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J39" t="n">
-        <v>-153.77</v>
+        <v>-158.08</v>
       </c>
       <c r="K39" t="n">
-        <v>32.36</v>
+        <v>3.06</v>
       </c>
       <c r="L39" t="n">
-        <v>157.14</v>
+        <v>158.11</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:59:51</t>
+          <t>05:54:54</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.07</v>
+        <v>2.75</v>
       </c>
       <c r="F40" t="n">
-        <v>7.84</v>
+        <v>6.13</v>
       </c>
       <c r="G40" t="n">
-        <v>7.4</v>
+        <v>9.5</v>
       </c>
       <c r="H40" t="n">
-        <v>85.7</v>
+        <v>47.2</v>
       </c>
       <c r="I40" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J40" t="n">
-        <v>114.16</v>
+        <v>80.97</v>
       </c>
       <c r="K40" t="n">
-        <v>48.41</v>
+        <v>-139.51</v>
       </c>
       <c r="L40" t="n">
-        <v>124</v>
+        <v>161.31</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:05:12</t>
+          <t>05:58:24</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>1.94</v>
+        <v>2.58</v>
       </c>
       <c r="F41" t="n">
-        <v>3.15</v>
+        <v>6.83</v>
       </c>
       <c r="G41" t="n">
-        <v>13</v>
+        <v>1.7</v>
       </c>
       <c r="H41" t="n">
-        <v>63.5</v>
+        <v>38.2</v>
       </c>
       <c r="I41" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J41" t="n">
-        <v>-48.35</v>
+        <v>-135.97</v>
       </c>
       <c r="K41" t="n">
-        <v>161.05</v>
+        <v>44.17</v>
       </c>
       <c r="L41" t="n">
-        <v>168.15</v>
+        <v>142.97</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:06:50</t>
+          <t>06:00:47</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.72</v>
+        <v>2.26</v>
       </c>
       <c r="F42" t="n">
-        <v>8.449999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="G42" t="n">
-        <v>11.3</v>
+        <v>22.5</v>
       </c>
       <c r="H42" t="n">
-        <v>71.3</v>
+        <v>25.2</v>
       </c>
       <c r="I42" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J42" t="n">
-        <v>212.16</v>
+        <v>94.2</v>
       </c>
       <c r="K42" t="n">
-        <v>-123.09</v>
+        <v>138.4</v>
       </c>
       <c r="L42" t="n">
-        <v>245.28</v>
+        <v>167.42</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:08:29</t>
+          <t>06:02:44</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3.06</v>
+        <v>3.21</v>
       </c>
       <c r="F43" t="n">
-        <v>8.42</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G43" t="n">
-        <v>12.9</v>
+        <v>1.9</v>
       </c>
       <c r="H43" t="n">
-        <v>14</v>
+        <v>53.2</v>
       </c>
       <c r="I43" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J43" t="n">
-        <v>-78.51000000000001</v>
+        <v>86.66</v>
       </c>
       <c r="K43" t="n">
-        <v>-229.23</v>
+        <v>-176.36</v>
       </c>
       <c r="L43" t="n">
-        <v>242.3</v>
+        <v>196.5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:17:53</t>
+          <t>06:11:35</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.93</v>
+        <v>2.82</v>
       </c>
       <c r="F44" t="n">
-        <v>9.539999999999999</v>
+        <v>9.06</v>
       </c>
       <c r="G44" t="n">
-        <v>347.7</v>
+        <v>12.7</v>
       </c>
       <c r="H44" t="n">
-        <v>66.7</v>
+        <v>24.8</v>
       </c>
       <c r="I44" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J44" t="n">
-        <v>-26.87</v>
+        <v>3.57</v>
       </c>
       <c r="K44" t="n">
-        <v>29.62</v>
+        <v>56.82</v>
       </c>
       <c r="L44" t="n">
-        <v>39.99</v>
+        <v>56.93</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:19:00</t>
+          <t>06:12:46</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.68</v>
+        <v>2.87</v>
       </c>
       <c r="F45" t="n">
-        <v>6.48</v>
+        <v>5.86</v>
       </c>
       <c r="G45" t="n">
-        <v>12.6</v>
+        <v>359.8</v>
       </c>
       <c r="H45" t="n">
-        <v>43.2</v>
+        <v>85.8</v>
       </c>
       <c r="I45" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>-42.29</v>
+        <v>-34.6</v>
       </c>
       <c r="K45" t="n">
-        <v>0.66</v>
+        <v>56.96</v>
       </c>
       <c r="L45" t="n">
-        <v>42.29</v>
+        <v>66.64</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:20:06</t>
+          <t>06:14:40</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>3.17</v>
+        <v>2.6</v>
       </c>
       <c r="F46" t="n">
-        <v>9.539999999999999</v>
+        <v>4.83</v>
       </c>
       <c r="G46" t="n">
-        <v>25.8</v>
+        <v>10</v>
       </c>
       <c r="H46" t="n">
-        <v>44.3</v>
+        <v>15.8</v>
       </c>
       <c r="I46" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>-8.369999999999999</v>
+        <v>37.82</v>
       </c>
       <c r="K46" t="n">
-        <v>-57.38</v>
+        <v>7.05</v>
       </c>
       <c r="L46" t="n">
-        <v>57.99</v>
+        <v>38.47</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:24:24</t>
+          <t>06:20:27</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>3.03</v>
+        <v>2.93</v>
       </c>
       <c r="F47" t="n">
-        <v>5.8</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G47" t="n">
-        <v>357.8</v>
+        <v>356.4</v>
       </c>
       <c r="H47" t="n">
-        <v>29.7</v>
+        <v>29.2</v>
       </c>
       <c r="I47" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>-87.14</v>
+        <v>50.32</v>
       </c>
       <c r="K47" t="n">
-        <v>-1.3</v>
+        <v>-52.54</v>
       </c>
       <c r="L47" t="n">
-        <v>87.15000000000001</v>
+        <v>72.75</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:25:32</t>
+          <t>06:22:00</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.91</v>
+        <v>3.11</v>
       </c>
       <c r="F48" t="n">
-        <v>6.5</v>
+        <v>7.82</v>
       </c>
       <c r="G48" t="n">
-        <v>21.1</v>
+        <v>4.9</v>
       </c>
       <c r="H48" t="n">
-        <v>30.3</v>
+        <v>50.5</v>
       </c>
       <c r="I48" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J48" t="n">
-        <v>70.66</v>
+        <v>68.56</v>
       </c>
       <c r="K48" t="n">
-        <v>12.88</v>
+        <v>84.98</v>
       </c>
       <c r="L48" t="n">
-        <v>71.83</v>
+        <v>109.19</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:27:56</t>
+          <t>06:23:11</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.27</v>
+        <v>2.69</v>
       </c>
       <c r="F49" t="n">
-        <v>9.390000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="G49" t="n">
-        <v>10.8</v>
+        <v>359.8</v>
       </c>
       <c r="H49" t="n">
-        <v>21.8</v>
+        <v>36.5</v>
       </c>
       <c r="I49" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J49" t="n">
-        <v>-65.22</v>
+        <v>-64.13</v>
       </c>
       <c r="K49" t="n">
-        <v>0.09</v>
+        <v>-5.76</v>
       </c>
       <c r="L49" t="n">
-        <v>65.22</v>
+        <v>64.39</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:33:58</t>
+          <t>06:28:16</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3</v>
+        <v>3.63</v>
       </c>
       <c r="F50" t="n">
-        <v>9.539999999999999</v>
+        <v>8.73</v>
       </c>
       <c r="G50" t="n">
-        <v>359</v>
+        <v>4.3</v>
       </c>
       <c r="H50" t="n">
-        <v>56</v>
+        <v>50.1</v>
       </c>
       <c r="I50" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>-100.26</v>
+        <v>-148.26</v>
       </c>
       <c r="K50" t="n">
-        <v>4.29</v>
+        <v>-184.65</v>
       </c>
       <c r="L50" t="n">
-        <v>100.36</v>
+        <v>236.8</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:35:53</t>
+          <t>06:30:23</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.95</v>
+        <v>3.14</v>
       </c>
       <c r="F51" t="n">
-        <v>8.81</v>
+        <v>9.19</v>
       </c>
       <c r="G51" t="n">
-        <v>19.4</v>
+        <v>25.7</v>
       </c>
       <c r="H51" t="n">
-        <v>51.9</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="I51" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J51" t="n">
-        <v>75.29000000000001</v>
+        <v>6.55</v>
       </c>
       <c r="K51" t="n">
-        <v>66.45</v>
+        <v>-126.48</v>
       </c>
       <c r="L51" t="n">
-        <v>100.42</v>
+        <v>126.65</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:37:20</t>
+          <t>06:31:53</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>4.05</v>
+        <v>2.91</v>
       </c>
       <c r="F52" t="n">
-        <v>9.539999999999999</v>
+        <v>7.67</v>
       </c>
       <c r="G52" t="n">
-        <v>12.7</v>
+        <v>6.5</v>
       </c>
       <c r="H52" t="n">
-        <v>19.9</v>
+        <v>19.5</v>
       </c>
       <c r="I52" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J52" t="n">
-        <v>-118.15</v>
+        <v>-97.45</v>
       </c>
       <c r="K52" t="n">
-        <v>35.33</v>
+        <v>-2.87</v>
       </c>
       <c r="L52" t="n">
-        <v>123.32</v>
+        <v>97.48999999999999</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:43:29</t>
+          <t>06:36:00</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.08</v>
+        <v>3.16</v>
       </c>
       <c r="F53" t="n">
-        <v>7.62</v>
+        <v>8.27</v>
       </c>
       <c r="G53" t="n">
-        <v>357.5</v>
+        <v>6.4</v>
       </c>
       <c r="H53" t="n">
-        <v>16.4</v>
+        <v>36.3</v>
       </c>
       <c r="I53" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>-106.56</v>
+        <v>-109.07</v>
       </c>
       <c r="K53" t="n">
-        <v>145.07</v>
+        <v>179.8</v>
       </c>
       <c r="L53" t="n">
-        <v>180</v>
+        <v>210.3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:44:36</t>
+          <t>06:37:50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3.06</v>
+        <v>2.85</v>
       </c>
       <c r="F54" t="n">
-        <v>8.949999999999999</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G54" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="H54" t="n">
-        <v>28.8</v>
+        <v>63.5</v>
       </c>
       <c r="I54" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="J54" t="n">
-        <v>178.63</v>
+        <v>-53.16</v>
       </c>
       <c r="K54" t="n">
-        <v>10.23</v>
+        <v>145.86</v>
       </c>
       <c r="L54" t="n">
-        <v>178.92</v>
+        <v>155.25</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:46:33</t>
+          <t>06:39:01</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.23</v>
+        <v>2.8</v>
       </c>
       <c r="F55" t="n">
-        <v>9.539999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G55" t="n">
-        <v>17.7</v>
+        <v>9.5</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="I55" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-68.92</v>
+        <v>166.03</v>
       </c>
       <c r="K55" t="n">
-        <v>184.63</v>
+        <v>-76.65000000000001</v>
       </c>
       <c r="L55" t="n">
-        <v>197.07</v>
+        <v>182.87</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:51:40</t>
+          <t>06:42:58</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="F56" t="n">
-        <v>7.96</v>
+        <v>5.66</v>
       </c>
       <c r="G56" t="n">
-        <v>0.7</v>
+        <v>27.1</v>
       </c>
       <c r="H56" t="n">
-        <v>51.4</v>
+        <v>49.9</v>
       </c>
       <c r="I56" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J56" t="n">
-        <v>-111.58</v>
+        <v>274.58</v>
       </c>
       <c r="K56" t="n">
-        <v>-129.16</v>
+        <v>-58.49</v>
       </c>
       <c r="L56" t="n">
-        <v>170.68</v>
+        <v>280.75</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:53:35</t>
+          <t>06:44:39</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.98</v>
+        <v>3.06</v>
       </c>
       <c r="F57" t="n">
         <v>9.539999999999999</v>
       </c>
       <c r="G57" t="n">
-        <v>18</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H57" t="n">
-        <v>50.3</v>
+        <v>25.3</v>
       </c>
       <c r="I57" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J57" t="n">
-        <v>-2.62</v>
+        <v>52.38</v>
       </c>
       <c r="K57" t="n">
-        <v>-212.45</v>
+        <v>199.87</v>
       </c>
       <c r="L57" t="n">
-        <v>212.46</v>
+        <v>206.62</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:55:32</t>
+          <t>06:46:03</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.02</v>
+        <v>2.8</v>
       </c>
       <c r="F58" t="n">
-        <v>9.449999999999999</v>
+        <v>7.88</v>
       </c>
       <c r="G58" t="n">
-        <v>18.7</v>
+        <v>6.2</v>
       </c>
       <c r="H58" t="n">
-        <v>21.1</v>
+        <v>49.3</v>
       </c>
       <c r="I58" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>196.35</v>
+        <v>-193.15</v>
       </c>
       <c r="K58" t="n">
-        <v>-112.08</v>
+        <v>-58.32</v>
       </c>
       <c r="L58" t="n">
-        <v>226.08</v>
+        <v>201.76</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:08:32</t>
+          <t>06:57:07</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.93</v>
+        <v>3.26</v>
       </c>
       <c r="F59" t="n">
         <v>9.539999999999999</v>
       </c>
       <c r="G59" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="H59" t="n">
-        <v>47.2</v>
+        <v>82.3</v>
       </c>
       <c r="I59" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J59" t="n">
-        <v>7.24</v>
+        <v>-33.95</v>
       </c>
       <c r="K59" t="n">
-        <v>44.29</v>
+        <v>52.38</v>
       </c>
       <c r="L59" t="n">
-        <v>44.88</v>
+        <v>62.42</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:09:53</t>
+          <t>06:58:25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>3.08</v>
+        <v>2.98</v>
       </c>
       <c r="F60" t="n">
-        <v>9.539999999999999</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="G60" t="n">
-        <v>14.8</v>
+        <v>357.8</v>
       </c>
       <c r="H60" t="n">
-        <v>25.8</v>
+        <v>29.7</v>
       </c>
       <c r="I60" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J60" t="n">
-        <v>-16.81</v>
+        <v>-56.65</v>
       </c>
       <c r="K60" t="n">
-        <v>-44.58</v>
+        <v>-14.47</v>
       </c>
       <c r="L60" t="n">
-        <v>47.65</v>
+        <v>58.47</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:11:19</t>
+          <t>07:00:12</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>3.54</v>
+        <v>3</v>
       </c>
       <c r="F61" t="n">
-        <v>9.539999999999999</v>
+        <v>6.91</v>
       </c>
       <c r="G61" t="n">
-        <v>1.9</v>
+        <v>18.5</v>
       </c>
       <c r="H61" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="I61" t="n">
         <v>30</v>
       </c>
-      <c r="I61" t="n">
-        <v>25</v>
-      </c>
       <c r="J61" t="n">
-        <v>-70.68000000000001</v>
+        <v>39.17</v>
       </c>
       <c r="K61" t="n">
-        <v>36.81</v>
+        <v>-26.34</v>
       </c>
       <c r="L61" t="n">
-        <v>79.69</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:17:36</t>
+          <t>07:05:24</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="F62" t="n">
-        <v>7.09</v>
+        <v>8.77</v>
       </c>
       <c r="G62" t="n">
-        <v>26</v>
+        <v>10.8</v>
       </c>
       <c r="H62" t="n">
-        <v>17</v>
+        <v>21.8</v>
       </c>
       <c r="I62" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J62" t="n">
-        <v>66.69</v>
+        <v>-60.01</v>
       </c>
       <c r="K62" t="n">
-        <v>-69.06999999999999</v>
+        <v>-15.22</v>
       </c>
       <c r="L62" t="n">
-        <v>96.01000000000001</v>
+        <v>61.91</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:19:52</t>
+          <t>07:08:02</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.98</v>
+        <v>3.08</v>
       </c>
       <c r="F63" t="n">
         <v>9.539999999999999</v>
       </c>
       <c r="G63" t="n">
-        <v>9.9</v>
+        <v>5.3</v>
       </c>
       <c r="H63" t="n">
-        <v>69.09999999999999</v>
+        <v>15.2</v>
       </c>
       <c r="I63" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J63" t="n">
-        <v>67.13</v>
+        <v>-132.45</v>
       </c>
       <c r="K63" t="n">
-        <v>13.97</v>
+        <v>93.86</v>
       </c>
       <c r="L63" t="n">
-        <v>68.56999999999999</v>
+        <v>162.33</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:20:57</t>
+          <t>07:10:08</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.17</v>
+        <v>3.41</v>
       </c>
       <c r="F64" t="n">
-        <v>5.37</v>
+        <v>7.09</v>
       </c>
       <c r="G64" t="n">
-        <v>7.1</v>
+        <v>24.8</v>
       </c>
       <c r="H64" t="n">
-        <v>18.1</v>
+        <v>49.9</v>
       </c>
       <c r="I64" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J64" t="n">
-        <v>-59.59</v>
+        <v>-30.6</v>
       </c>
       <c r="K64" t="n">
-        <v>-28.86</v>
+        <v>71.56</v>
       </c>
       <c r="L64" t="n">
-        <v>66.20999999999999</v>
+        <v>77.83</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:25:42</t>
+          <t>07:14:08</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="F65" t="n">
         <v>9.539999999999999</v>
       </c>
       <c r="G65" t="n">
-        <v>3.2</v>
+        <v>21.3</v>
       </c>
       <c r="H65" t="n">
-        <v>37.4</v>
+        <v>11.5</v>
       </c>
       <c r="I65" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="J65" t="n">
-        <v>153.49</v>
+        <v>111.22</v>
       </c>
       <c r="K65" t="n">
-        <v>158.27</v>
+        <v>-72.3</v>
       </c>
       <c r="L65" t="n">
-        <v>220.48</v>
+        <v>132.65</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:27:22</t>
+          <t>07:14:55</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="F66" t="n">
-        <v>8.52</v>
+        <v>8.75</v>
       </c>
       <c r="G66" t="n">
-        <v>11.4</v>
+        <v>5.4</v>
       </c>
       <c r="H66" t="n">
-        <v>29.9</v>
+        <v>42</v>
       </c>
       <c r="I66" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J66" t="n">
-        <v>110.82</v>
+        <v>-77.01000000000001</v>
       </c>
       <c r="K66" t="n">
-        <v>28.55</v>
+        <v>-13.88</v>
       </c>
       <c r="L66" t="n">
-        <v>114.44</v>
+        <v>78.25</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:29:08</t>
+          <t>07:16:38</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="F67" t="n">
         <v>9.539999999999999</v>
       </c>
       <c r="G67" t="n">
-        <v>9</v>
+        <v>11.9</v>
       </c>
       <c r="H67" t="n">
-        <v>65.8</v>
+        <v>84.5</v>
       </c>
       <c r="I67" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J67" t="n">
-        <v>-23.82</v>
+        <v>51.39</v>
       </c>
       <c r="K67" t="n">
-        <v>-117.72</v>
+        <v>42.69</v>
       </c>
       <c r="L67" t="n">
-        <v>120.11</v>
+        <v>66.81</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:33:35</t>
+          <t>07:21:28</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>3.53</v>
+        <v>3.1</v>
       </c>
       <c r="F68" t="n">
-        <v>9.5</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G68" t="n">
-        <v>348.5</v>
+        <v>13.5</v>
       </c>
       <c r="H68" t="n">
-        <v>25</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="I68" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J68" t="n">
-        <v>-47.3</v>
+        <v>-174.27</v>
       </c>
       <c r="K68" t="n">
-        <v>169.76</v>
+        <v>-98.51000000000001</v>
       </c>
       <c r="L68" t="n">
-        <v>176.23</v>
+        <v>200.19</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:35:26</t>
+          <t>07:22:45</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>3.39</v>
+        <v>3.28</v>
       </c>
       <c r="F69" t="n">
-        <v>7.43</v>
+        <v>9.27</v>
       </c>
       <c r="G69" t="n">
-        <v>7.8</v>
+        <v>0.7</v>
       </c>
       <c r="H69" t="n">
-        <v>57.1</v>
+        <v>51.4</v>
       </c>
       <c r="I69" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J69" t="n">
-        <v>215.42</v>
+        <v>-93.51000000000001</v>
       </c>
       <c r="K69" t="n">
-        <v>-22.89</v>
+        <v>-139.09</v>
       </c>
       <c r="L69" t="n">
-        <v>216.63</v>
+        <v>167.6</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:37:26</t>
+          <t>07:24:20</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="F70" t="n">
-        <v>8.42</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G70" t="n">
-        <v>19.7</v>
+        <v>13.1</v>
       </c>
       <c r="H70" t="n">
-        <v>67.5</v>
+        <v>48.6</v>
       </c>
       <c r="I70" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J70" t="n">
-        <v>-140.37</v>
+        <v>-179.04</v>
       </c>
       <c r="K70" t="n">
-        <v>18.8</v>
+        <v>-16.81</v>
       </c>
       <c r="L70" t="n">
-        <v>141.62</v>
+        <v>179.82</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:42:03</t>
+          <t>07:29:43</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.91</v>
+        <v>2.62</v>
       </c>
       <c r="F71" t="n">
-        <v>6.94</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G71" t="n">
-        <v>10.8</v>
+        <v>18.7</v>
       </c>
       <c r="H71" t="n">
-        <v>63.2</v>
+        <v>21.1</v>
       </c>
       <c r="I71" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J71" t="n">
-        <v>-30.71</v>
+        <v>164.09</v>
       </c>
       <c r="K71" t="n">
-        <v>-196.64</v>
+        <v>-156.61</v>
       </c>
       <c r="L71" t="n">
-        <v>199.02</v>
+        <v>226.83</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:44:05</t>
+          <t>07:30:44</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2.84</v>
+        <v>2.98</v>
       </c>
       <c r="F72" t="n">
-        <v>9.23</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G72" t="n">
-        <v>3.6</v>
+        <v>11.8</v>
       </c>
       <c r="H72" t="n">
-        <v>58.5</v>
+        <v>62.4</v>
       </c>
       <c r="I72" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>130.96</v>
+        <v>-223.23</v>
       </c>
       <c r="K72" t="n">
-        <v>213.95</v>
+        <v>-62.47</v>
       </c>
       <c r="L72" t="n">
-        <v>250.85</v>
+        <v>231.8</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:46:18</t>
+          <t>07:31:45</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="F73" t="n">
-        <v>6.68</v>
+        <v>6.32</v>
       </c>
       <c r="G73" t="n">
-        <v>11.8</v>
+        <v>14.8</v>
       </c>
       <c r="H73" t="n">
-        <v>13.8</v>
+        <v>25.8</v>
       </c>
       <c r="I73" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J73" t="n">
-        <v>216.75</v>
+        <v>-61.36</v>
       </c>
       <c r="K73" t="n">
-        <v>-116.06</v>
+        <v>-174.04</v>
       </c>
       <c r="L73" t="n">
-        <v>245.86</v>
+        <v>184.54</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:55:10</t>
+          <t>07:39:43</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>3.34</v>
+        <v>3.61</v>
       </c>
       <c r="F74" t="n">
         <v>9.539999999999999</v>
       </c>
       <c r="G74" t="n">
-        <v>8.300000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="H74" t="n">
-        <v>26.8</v>
+        <v>44.1</v>
       </c>
       <c r="I74" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J74" t="n">
-        <v>-60.24</v>
+        <v>-68.39</v>
       </c>
       <c r="K74" t="n">
-        <v>6.39</v>
+        <v>26.67</v>
       </c>
       <c r="L74" t="n">
-        <v>60.58</v>
+        <v>73.40000000000001</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:57:14</t>
+          <t>07:40:42</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="F75" t="n">
-        <v>8.15</v>
+        <v>6.4</v>
       </c>
       <c r="G75" t="n">
-        <v>6.5</v>
+        <v>26</v>
       </c>
       <c r="H75" t="n">
-        <v>16.1</v>
+        <v>17</v>
       </c>
       <c r="I75" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J75" t="n">
-        <v>20.88</v>
+        <v>36.66</v>
       </c>
       <c r="K75" t="n">
-        <v>49.09</v>
+        <v>-56.06</v>
       </c>
       <c r="L75" t="n">
-        <v>53.34</v>
+        <v>66.98999999999999</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:58:06</t>
+          <t>07:42:42</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.22</v>
+        <v>3.03</v>
       </c>
       <c r="F76" t="n">
         <v>9.539999999999999</v>
       </c>
       <c r="G76" t="n">
-        <v>10.9</v>
+        <v>20.6</v>
       </c>
       <c r="H76" t="n">
-        <v>46.6</v>
+        <v>68.5</v>
       </c>
       <c r="I76" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J76" t="n">
-        <v>-45.19</v>
+        <v>25.44</v>
       </c>
       <c r="K76" t="n">
-        <v>44.54</v>
+        <v>45.87</v>
       </c>
       <c r="L76" t="n">
-        <v>63.46</v>
+        <v>52.46</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>08:02:29</t>
+          <t>07:45:53</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.57</v>
+        <v>3.52</v>
       </c>
       <c r="F77" t="n">
-        <v>8.25</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G77" t="n">
-        <v>15.7</v>
+        <v>7.1</v>
       </c>
       <c r="H77" t="n">
-        <v>66.40000000000001</v>
+        <v>18.1</v>
       </c>
       <c r="I77" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="J77" t="n">
-        <v>24.01</v>
+        <v>-56.89</v>
       </c>
       <c r="K77" t="n">
-        <v>98.33</v>
+        <v>-41.07</v>
       </c>
       <c r="L77" t="n">
-        <v>101.22</v>
+        <v>70.17</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>08:03:28</t>
+          <t>07:47:41</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.72</v>
+        <v>3.61</v>
       </c>
       <c r="F78" t="n">
-        <v>6.6</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G78" t="n">
-        <v>16.3</v>
+        <v>7.9</v>
       </c>
       <c r="H78" t="n">
-        <v>35.1</v>
+        <v>40.5</v>
       </c>
       <c r="I78" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="J78" t="n">
-        <v>-70.22</v>
+        <v>-89.58</v>
       </c>
       <c r="K78" t="n">
-        <v>-6.2</v>
+        <v>36.81</v>
       </c>
       <c r="L78" t="n">
-        <v>70.5</v>
+        <v>96.84999999999999</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>08:05:05</t>
+          <t>07:48:30</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.89</v>
+        <v>3.34</v>
       </c>
       <c r="F79" t="n">
-        <v>9.539999999999999</v>
+        <v>8.56</v>
       </c>
       <c r="G79" t="n">
-        <v>3.6</v>
+        <v>10.3</v>
       </c>
       <c r="H79" t="n">
-        <v>16</v>
+        <v>53.8</v>
       </c>
       <c r="I79" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>-57.74</v>
+        <v>49.84</v>
       </c>
       <c r="K79" t="n">
-        <v>-55.62</v>
+        <v>-102.41</v>
       </c>
       <c r="L79" t="n">
-        <v>80.17</v>
+        <v>113.9</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:09:55</t>
+          <t>07:53:24</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.13</v>
+        <v>3.26</v>
       </c>
       <c r="F80" t="n">
-        <v>8.48</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G80" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="H80" t="n">
-        <v>29.6</v>
+        <v>40.2</v>
       </c>
       <c r="I80" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>-24.35</v>
+        <v>88.42</v>
       </c>
       <c r="K80" t="n">
-        <v>72.75</v>
+        <v>-17.23</v>
       </c>
       <c r="L80" t="n">
-        <v>76.70999999999999</v>
+        <v>90.09</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:11:46</t>
+          <t>07:54:11</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.23</v>
+        <v>3.55</v>
       </c>
       <c r="F81" t="n">
-        <v>9.539999999999999</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="G81" t="n">
-        <v>6.4</v>
+        <v>24</v>
       </c>
       <c r="H81" t="n">
-        <v>43.2</v>
+        <v>34.3</v>
       </c>
       <c r="I81" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J81" t="n">
-        <v>-89.12</v>
+        <v>-47.88</v>
       </c>
       <c r="K81" t="n">
-        <v>-3.29</v>
+        <v>59.07</v>
       </c>
       <c r="L81" t="n">
-        <v>89.18000000000001</v>
+        <v>76.04000000000001</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:12:52</t>
+          <t>07:56:15</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.57</v>
+        <v>3.43</v>
       </c>
       <c r="F82" t="n">
-        <v>9.539999999999999</v>
+        <v>7.64</v>
       </c>
       <c r="G82" t="n">
-        <v>12.8</v>
+        <v>15.8</v>
       </c>
       <c r="H82" t="n">
-        <v>24</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I82" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>28.91</v>
+        <v>96.75</v>
       </c>
       <c r="K82" t="n">
-        <v>88.61</v>
+        <v>-24.82</v>
       </c>
       <c r="L82" t="n">
-        <v>93.20999999999999</v>
+        <v>99.88</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:19:19</t>
+          <t>08:00:48</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>3.16</v>
+        <v>2.47</v>
       </c>
       <c r="F83" t="n">
-        <v>7.02</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="G83" t="n">
-        <v>15.9</v>
+        <v>19.7</v>
       </c>
       <c r="H83" t="n">
-        <v>56.6</v>
+        <v>67.5</v>
       </c>
       <c r="I83" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J83" t="n">
-        <v>-192.33</v>
+        <v>128.97</v>
       </c>
       <c r="K83" t="n">
-        <v>-34.81</v>
+        <v>19.95</v>
       </c>
       <c r="L83" t="n">
-        <v>195.45</v>
+        <v>130.51</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:20:55</t>
+          <t>08:02:19</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>3.12</v>
+        <v>3.31</v>
       </c>
       <c r="F84" t="n">
-        <v>9.539999999999999</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="G84" t="n">
-        <v>7.3</v>
+        <v>3.2</v>
       </c>
       <c r="H84" t="n">
-        <v>22.1</v>
+        <v>56.5</v>
       </c>
       <c r="I84" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J84" t="n">
-        <v>-4.95</v>
+        <v>-131.92</v>
       </c>
       <c r="K84" t="n">
-        <v>-192.59</v>
+        <v>-152.97</v>
       </c>
       <c r="L84" t="n">
-        <v>192.65</v>
+        <v>202</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:21:51</t>
+          <t>08:02:45</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>3.33</v>
+        <v>2.73</v>
       </c>
       <c r="F85" t="n">
-        <v>9.539999999999999</v>
+        <v>9.43</v>
       </c>
       <c r="G85" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="H85" t="n">
-        <v>38.4</v>
+        <v>17.5</v>
       </c>
       <c r="I85" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>-91.47</v>
+        <v>-64.53</v>
       </c>
       <c r="K85" t="n">
-        <v>108.25</v>
+        <v>-172.79</v>
       </c>
       <c r="L85" t="n">
-        <v>141.72</v>
+        <v>184.45</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:26:25</t>
+          <t>08:07:20</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3.89</v>
+        <v>3.2</v>
       </c>
       <c r="F86" t="n">
-        <v>9.539999999999999</v>
+        <v>9.19</v>
       </c>
       <c r="G86" t="n">
-        <v>18.4</v>
+        <v>359.8</v>
       </c>
       <c r="H86" t="n">
-        <v>68.2</v>
+        <v>51.2</v>
       </c>
       <c r="I86" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J86" t="n">
-        <v>-13.75</v>
+        <v>-190.43</v>
       </c>
       <c r="K86" t="n">
-        <v>-276.53</v>
+        <v>-151.12</v>
       </c>
       <c r="L86" t="n">
-        <v>276.87</v>
+        <v>243.11</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:27:11</t>
+          <t>08:08:49</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>3.24</v>
+        <v>2.84</v>
       </c>
       <c r="F87" t="n">
         <v>9.539999999999999</v>
       </c>
       <c r="G87" t="n">
-        <v>9</v>
+        <v>11.8</v>
       </c>
       <c r="H87" t="n">
-        <v>69.40000000000001</v>
+        <v>26.5</v>
       </c>
       <c r="I87" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J87" t="n">
-        <v>10.17</v>
+        <v>219.48</v>
       </c>
       <c r="K87" t="n">
-        <v>217.3</v>
+        <v>33.92</v>
       </c>
       <c r="L87" t="n">
-        <v>217.54</v>
+        <v>222.08</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:28:57</t>
+          <t>08:10:24</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.87</v>
+        <v>2.83</v>
       </c>
       <c r="F88" t="n">
-        <v>9.460000000000001</v>
+        <v>9.15</v>
       </c>
       <c r="G88" t="n">
-        <v>24.2</v>
+        <v>4.1</v>
       </c>
       <c r="H88" t="n">
-        <v>28.6</v>
+        <v>56.2</v>
       </c>
       <c r="I88" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>-185.33</v>
+        <v>201.4</v>
       </c>
       <c r="K88" t="n">
-        <v>-173.99</v>
+        <v>2.26</v>
       </c>
       <c r="L88" t="n">
-        <v>254.2</v>
+        <v>201.41</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-10.xlsx
+++ b/output/2024-07-10.xlsx
@@ -640,13 +640,13 @@
         <v>30</v>
       </c>
       <c r="J14" t="n">
-        <v>-34.36</v>
+        <v>-35.87</v>
       </c>
       <c r="K14" t="n">
-        <v>-24.84</v>
+        <v>-25.93</v>
       </c>
       <c r="L14" t="n">
-        <v>42.4</v>
+        <v>44.26</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>30</v>
       </c>
       <c r="J15" t="n">
-        <v>55.02</v>
+        <v>51.21</v>
       </c>
       <c r="K15" t="n">
-        <v>44.3</v>
+        <v>41.23</v>
       </c>
       <c r="L15" t="n">
-        <v>70.64</v>
+        <v>65.73999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>-40.8</v>
+        <v>-41.53</v>
       </c>
       <c r="K16" t="n">
-        <v>-7.34</v>
+        <v>-7.47</v>
       </c>
       <c r="L16" t="n">
-        <v>41.46</v>
+        <v>42.19</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>-56.44</v>
+        <v>-58.3</v>
       </c>
       <c r="K17" t="n">
-        <v>-34.39</v>
+        <v>-35.52</v>
       </c>
       <c r="L17" t="n">
-        <v>66.09</v>
+        <v>68.27</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>-37.45</v>
+        <v>-39.21</v>
       </c>
       <c r="K18" t="n">
-        <v>45.39</v>
+        <v>47.52</v>
       </c>
       <c r="L18" t="n">
-        <v>58.85</v>
+        <v>61.61</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>29</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.75</v>
+        <v>-4.09</v>
       </c>
       <c r="K19" t="n">
-        <v>-45.67</v>
+        <v>-49.76</v>
       </c>
       <c r="L19" t="n">
-        <v>45.82</v>
+        <v>49.93</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>-79.03</v>
+        <v>-88.2</v>
       </c>
       <c r="K20" t="n">
-        <v>-38.06</v>
+        <v>-42.48</v>
       </c>
       <c r="L20" t="n">
-        <v>87.72</v>
+        <v>97.89</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>27</v>
       </c>
       <c r="J21" t="n">
-        <v>29.69</v>
+        <v>32.9</v>
       </c>
       <c r="K21" t="n">
-        <v>-69.48</v>
+        <v>-76.98999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>75.55</v>
+        <v>83.73</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>30</v>
       </c>
       <c r="J22" t="n">
-        <v>-33.93</v>
+        <v>-38.42</v>
       </c>
       <c r="K22" t="n">
-        <v>-59.54</v>
+        <v>-67.41</v>
       </c>
       <c r="L22" t="n">
-        <v>68.53</v>
+        <v>77.59</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>30</v>
       </c>
       <c r="J23" t="n">
-        <v>96.18000000000001</v>
+        <v>109.08</v>
       </c>
       <c r="K23" t="n">
-        <v>-53.69</v>
+        <v>-60.89</v>
       </c>
       <c r="L23" t="n">
-        <v>110.16</v>
+        <v>124.92</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>28</v>
       </c>
       <c r="J24" t="n">
-        <v>93.29000000000001</v>
+        <v>101.65</v>
       </c>
       <c r="K24" t="n">
-        <v>82.48999999999999</v>
+        <v>89.88</v>
       </c>
       <c r="L24" t="n">
-        <v>124.53</v>
+        <v>135.68</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>-124.97</v>
+        <v>-135.23</v>
       </c>
       <c r="K25" t="n">
-        <v>-62.26</v>
+        <v>-67.37</v>
       </c>
       <c r="L25" t="n">
-        <v>139.62</v>
+        <v>151.08</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>30</v>
       </c>
       <c r="J26" t="n">
-        <v>132.26</v>
+        <v>151.74</v>
       </c>
       <c r="K26" t="n">
-        <v>82.91</v>
+        <v>95.12</v>
       </c>
       <c r="L26" t="n">
-        <v>156.1</v>
+        <v>179.09</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>-8.85</v>
+        <v>-11.14</v>
       </c>
       <c r="K27" t="n">
-        <v>-137.55</v>
+        <v>-173.27</v>
       </c>
       <c r="L27" t="n">
-        <v>137.84</v>
+        <v>173.63</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>29</v>
       </c>
       <c r="J28" t="n">
-        <v>-74.89</v>
+        <v>-83.63</v>
       </c>
       <c r="K28" t="n">
-        <v>156.69</v>
+        <v>174.98</v>
       </c>
       <c r="L28" t="n">
-        <v>173.67</v>
+        <v>193.94</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>-56.07</v>
+        <v>-54.53</v>
       </c>
       <c r="K29" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="L29" t="n">
-        <v>56.1</v>
+        <v>54.56</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>29</v>
       </c>
       <c r="J30" t="n">
-        <v>-3.68</v>
+        <v>-3.81</v>
       </c>
       <c r="K30" t="n">
-        <v>-44.91</v>
+        <v>-46.55</v>
       </c>
       <c r="L30" t="n">
-        <v>45.06</v>
+        <v>46.71</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>5.94</v>
+        <v>6.21</v>
       </c>
       <c r="K31" t="n">
-        <v>-49.88</v>
+        <v>-52.14</v>
       </c>
       <c r="L31" t="n">
-        <v>50.23</v>
+        <v>52.51</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>29</v>
       </c>
       <c r="J32" t="n">
-        <v>-26.08</v>
+        <v>-29.04</v>
       </c>
       <c r="K32" t="n">
-        <v>-39.24</v>
+        <v>-43.69</v>
       </c>
       <c r="L32" t="n">
-        <v>47.11</v>
+        <v>52.45</v>
       </c>
     </row>
     <row r="33">
@@ -1441,10 +1441,10 @@
         <v>-0.59</v>
       </c>
       <c r="K33" t="n">
-        <v>74.38</v>
+        <v>75.22</v>
       </c>
       <c r="L33" t="n">
-        <v>74.39</v>
+        <v>75.22</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>27</v>
       </c>
       <c r="J34" t="n">
-        <v>51.65</v>
+        <v>53.33</v>
       </c>
       <c r="K34" t="n">
-        <v>23.94</v>
+        <v>24.72</v>
       </c>
       <c r="L34" t="n">
-        <v>56.93</v>
+        <v>58.78</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>25</v>
       </c>
       <c r="J35" t="n">
-        <v>-94.39</v>
+        <v>-102.02</v>
       </c>
       <c r="K35" t="n">
-        <v>21.91</v>
+        <v>23.67</v>
       </c>
       <c r="L35" t="n">
-        <v>96.90000000000001</v>
+        <v>104.73</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>116.11</v>
+        <v>117.61</v>
       </c>
       <c r="K36" t="n">
-        <v>48.41</v>
+        <v>49.04</v>
       </c>
       <c r="L36" t="n">
-        <v>125.79</v>
+        <v>127.43</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>24</v>
       </c>
       <c r="J37" t="n">
-        <v>-139.62</v>
+        <v>-138.7</v>
       </c>
       <c r="K37" t="n">
-        <v>73.79000000000001</v>
+        <v>73.31</v>
       </c>
       <c r="L37" t="n">
-        <v>157.92</v>
+        <v>156.88</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>28</v>
       </c>
       <c r="J38" t="n">
-        <v>42.43</v>
+        <v>46.33</v>
       </c>
       <c r="K38" t="n">
-        <v>-128.66</v>
+        <v>-140.5</v>
       </c>
       <c r="L38" t="n">
-        <v>135.47</v>
+        <v>147.95</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>28</v>
       </c>
       <c r="J39" t="n">
-        <v>-67.23999999999999</v>
+        <v>-78.61</v>
       </c>
       <c r="K39" t="n">
-        <v>76.23999999999999</v>
+        <v>89.14</v>
       </c>
       <c r="L39" t="n">
-        <v>101.66</v>
+        <v>118.85</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>25</v>
       </c>
       <c r="J40" t="n">
-        <v>117.51</v>
+        <v>122.78</v>
       </c>
       <c r="K40" t="n">
-        <v>129.18</v>
+        <v>134.98</v>
       </c>
       <c r="L40" t="n">
-        <v>174.63</v>
+        <v>182.47</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>24</v>
       </c>
       <c r="J41" t="n">
-        <v>-133.85</v>
+        <v>-166.26</v>
       </c>
       <c r="K41" t="n">
-        <v>27.85</v>
+        <v>34.6</v>
       </c>
       <c r="L41" t="n">
-        <v>136.71</v>
+        <v>169.82</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>27</v>
       </c>
       <c r="J42" t="n">
-        <v>105.31</v>
+        <v>123.97</v>
       </c>
       <c r="K42" t="n">
-        <v>120.56</v>
+        <v>141.92</v>
       </c>
       <c r="L42" t="n">
-        <v>160.08</v>
+        <v>188.44</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>30</v>
       </c>
       <c r="J43" t="n">
-        <v>-109.17</v>
+        <v>-119.07</v>
       </c>
       <c r="K43" t="n">
-        <v>155.22</v>
+        <v>169.3</v>
       </c>
       <c r="L43" t="n">
-        <v>189.77</v>
+        <v>206.97</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>29</v>
       </c>
       <c r="J44" t="n">
-        <v>60.95</v>
+        <v>56.47</v>
       </c>
       <c r="K44" t="n">
-        <v>-49.11</v>
+        <v>-45.5</v>
       </c>
       <c r="L44" t="n">
-        <v>78.27</v>
+        <v>72.51000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>28</v>
       </c>
       <c r="J45" t="n">
-        <v>-69.81999999999999</v>
+        <v>-64.34</v>
       </c>
       <c r="K45" t="n">
-        <v>-33</v>
+        <v>-30.41</v>
       </c>
       <c r="L45" t="n">
-        <v>77.23</v>
+        <v>71.17</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>50.79</v>
+        <v>49.36</v>
       </c>
       <c r="K46" t="n">
-        <v>62.83</v>
+        <v>61.07</v>
       </c>
       <c r="L46" t="n">
-        <v>80.79000000000001</v>
+        <v>78.53</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>29</v>
       </c>
       <c r="J47" t="n">
-        <v>2.63</v>
+        <v>2.93</v>
       </c>
       <c r="K47" t="n">
-        <v>12.54</v>
+        <v>14.01</v>
       </c>
       <c r="L47" t="n">
-        <v>12.82</v>
+        <v>14.32</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>66.98</v>
+        <v>63.99</v>
       </c>
       <c r="K48" t="n">
-        <v>-76.59999999999999</v>
+        <v>-73.18000000000001</v>
       </c>
       <c r="L48" t="n">
-        <v>101.76</v>
+        <v>97.20999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>-56.86</v>
+        <v>-61.88</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.19</v>
+        <v>-0.2</v>
       </c>
       <c r="L49" t="n">
-        <v>56.86</v>
+        <v>61.88</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>28</v>
       </c>
       <c r="J50" t="n">
-        <v>-104.21</v>
+        <v>-107.52</v>
       </c>
       <c r="K50" t="n">
-        <v>27.23</v>
+        <v>28.09</v>
       </c>
       <c r="L50" t="n">
-        <v>107.71</v>
+        <v>111.13</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>29</v>
       </c>
       <c r="J51" t="n">
-        <v>12.21</v>
+        <v>12.88</v>
       </c>
       <c r="K51" t="n">
-        <v>-96.95</v>
+        <v>-102.27</v>
       </c>
       <c r="L51" t="n">
-        <v>97.72</v>
+        <v>103.08</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>28</v>
       </c>
       <c r="J52" t="n">
-        <v>0.72</v>
+        <v>0.78</v>
       </c>
       <c r="K52" t="n">
-        <v>-88.26000000000001</v>
+        <v>-95.05</v>
       </c>
       <c r="L52" t="n">
-        <v>88.26000000000001</v>
+        <v>95.05</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>30</v>
       </c>
       <c r="J53" t="n">
-        <v>65.66</v>
+        <v>73.2</v>
       </c>
       <c r="K53" t="n">
-        <v>111.29</v>
+        <v>124.08</v>
       </c>
       <c r="L53" t="n">
-        <v>129.21</v>
+        <v>144.06</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>32.22</v>
+        <v>40.12</v>
       </c>
       <c r="K54" t="n">
-        <v>80.84</v>
+        <v>100.67</v>
       </c>
       <c r="L54" t="n">
-        <v>87.03</v>
+        <v>108.38</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>-55.44</v>
+        <v>-60.48</v>
       </c>
       <c r="K55" t="n">
-        <v>-149.74</v>
+        <v>-163.35</v>
       </c>
       <c r="L55" t="n">
-        <v>159.68</v>
+        <v>174.19</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>29</v>
       </c>
       <c r="J56" t="n">
-        <v>-60.06</v>
+        <v>-69.41</v>
       </c>
       <c r="K56" t="n">
-        <v>-156.5</v>
+        <v>-180.86</v>
       </c>
       <c r="L56" t="n">
-        <v>167.63</v>
+        <v>193.73</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>29</v>
       </c>
       <c r="J57" t="n">
-        <v>139.24</v>
+        <v>168.91</v>
       </c>
       <c r="K57" t="n">
-        <v>-28.37</v>
+        <v>-34.41</v>
       </c>
       <c r="L57" t="n">
-        <v>142.1</v>
+        <v>172.38</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>26</v>
       </c>
       <c r="J58" t="n">
-        <v>155.67</v>
+        <v>173.58</v>
       </c>
       <c r="K58" t="n">
-        <v>-139.14</v>
+        <v>-155.15</v>
       </c>
       <c r="L58" t="n">
-        <v>208.79</v>
+        <v>232.81</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>22.72</v>
+        <v>22.84</v>
       </c>
       <c r="K59" t="n">
-        <v>-42.16</v>
+        <v>-42.39</v>
       </c>
       <c r="L59" t="n">
-        <v>47.89</v>
+        <v>48.15</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>29</v>
       </c>
       <c r="J60" t="n">
-        <v>39.95</v>
+        <v>43.23</v>
       </c>
       <c r="K60" t="n">
-        <v>0.95</v>
+        <v>1.03</v>
       </c>
       <c r="L60" t="n">
-        <v>39.97</v>
+        <v>43.25</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>29</v>
       </c>
       <c r="J61" t="n">
-        <v>-42.69</v>
+        <v>-45.14</v>
       </c>
       <c r="K61" t="n">
-        <v>-14.88</v>
+        <v>-15.73</v>
       </c>
       <c r="L61" t="n">
-        <v>45.21</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>-29.16</v>
+        <v>-31.76</v>
       </c>
       <c r="K62" t="n">
-        <v>47.43</v>
+        <v>51.65</v>
       </c>
       <c r="L62" t="n">
-        <v>55.68</v>
+        <v>60.63</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>29</v>
       </c>
       <c r="J63" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="K63" t="n">
-        <v>63.57</v>
+        <v>65.41</v>
       </c>
       <c r="L63" t="n">
-        <v>63.59</v>
+        <v>65.43000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>28</v>
       </c>
       <c r="J64" t="n">
-        <v>-12.53</v>
+        <v>-11.92</v>
       </c>
       <c r="K64" t="n">
-        <v>-90.26000000000001</v>
+        <v>-85.81999999999999</v>
       </c>
       <c r="L64" t="n">
-        <v>91.12</v>
+        <v>86.65000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>27</v>
       </c>
       <c r="J65" t="n">
-        <v>-74.92</v>
+        <v>-81.54000000000001</v>
       </c>
       <c r="K65" t="n">
-        <v>28.69</v>
+        <v>31.22</v>
       </c>
       <c r="L65" t="n">
-        <v>80.23</v>
+        <v>87.31999999999999</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-64.5</v>
+        <v>-70.70999999999999</v>
       </c>
       <c r="K66" t="n">
-        <v>-62.1</v>
+        <v>-68.08</v>
       </c>
       <c r="L66" t="n">
-        <v>89.53</v>
+        <v>98.15000000000001</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>27</v>
       </c>
       <c r="J67" t="n">
-        <v>88.23999999999999</v>
+        <v>93.95</v>
       </c>
       <c r="K67" t="n">
-        <v>-51.42</v>
+        <v>-54.74</v>
       </c>
       <c r="L67" t="n">
-        <v>102.13</v>
+        <v>108.73</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>118.74</v>
+        <v>140.03</v>
       </c>
       <c r="K68" t="n">
-        <v>-7.61</v>
+        <v>-8.98</v>
       </c>
       <c r="L68" t="n">
-        <v>118.98</v>
+        <v>140.32</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>-49.52</v>
+        <v>-61.22</v>
       </c>
       <c r="K69" t="n">
-        <v>70.8</v>
+        <v>87.52</v>
       </c>
       <c r="L69" t="n">
-        <v>86.40000000000001</v>
+        <v>106.8</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>28</v>
       </c>
       <c r="J70" t="n">
-        <v>88.16</v>
+        <v>99.66</v>
       </c>
       <c r="K70" t="n">
-        <v>139.53</v>
+        <v>157.74</v>
       </c>
       <c r="L70" t="n">
-        <v>165.05</v>
+        <v>186.58</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>-43.21</v>
+        <v>-48.67</v>
       </c>
       <c r="K71" t="n">
-        <v>-224.14</v>
+        <v>-252.46</v>
       </c>
       <c r="L71" t="n">
-        <v>228.26</v>
+        <v>257.11</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>24</v>
       </c>
       <c r="J72" t="n">
-        <v>-182.92</v>
+        <v>-214.84</v>
       </c>
       <c r="K72" t="n">
-        <v>57.94</v>
+        <v>68.05</v>
       </c>
       <c r="L72" t="n">
-        <v>191.88</v>
+        <v>225.36</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>30</v>
       </c>
       <c r="J73" t="n">
-        <v>67.59</v>
+        <v>74.89</v>
       </c>
       <c r="K73" t="n">
-        <v>197.86</v>
+        <v>219.22</v>
       </c>
       <c r="L73" t="n">
-        <v>209.08</v>
+        <v>231.66</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>25.45</v>
+        <v>27.18</v>
       </c>
       <c r="K74" t="n">
-        <v>-36.5</v>
+        <v>-38.99</v>
       </c>
       <c r="L74" t="n">
-        <v>44.5</v>
+        <v>47.53</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>63.72</v>
+        <v>62.34</v>
       </c>
       <c r="K75" t="n">
-        <v>13.75</v>
+        <v>13.45</v>
       </c>
       <c r="L75" t="n">
-        <v>65.19</v>
+        <v>63.78</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>28</v>
       </c>
       <c r="J76" t="n">
-        <v>-51.76</v>
+        <v>-50.56</v>
       </c>
       <c r="K76" t="n">
-        <v>-36.97</v>
+        <v>-36.12</v>
       </c>
       <c r="L76" t="n">
-        <v>63.61</v>
+        <v>62.14</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>26</v>
       </c>
       <c r="J77" t="n">
-        <v>-66.20999999999999</v>
+        <v>-67.28</v>
       </c>
       <c r="K77" t="n">
-        <v>14.5</v>
+        <v>14.74</v>
       </c>
       <c r="L77" t="n">
-        <v>67.78</v>
+        <v>68.87</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>29</v>
       </c>
       <c r="J78" t="n">
-        <v>-42.69</v>
+        <v>-46.19</v>
       </c>
       <c r="K78" t="n">
-        <v>37.37</v>
+        <v>40.44</v>
       </c>
       <c r="L78" t="n">
-        <v>56.73</v>
+        <v>61.39</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>-55.62</v>
+        <v>-60.91</v>
       </c>
       <c r="K79" t="n">
-        <v>-11.51</v>
+        <v>-12.61</v>
       </c>
       <c r="L79" t="n">
-        <v>56.79</v>
+        <v>62.2</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>-96.65000000000001</v>
+        <v>-99.54000000000001</v>
       </c>
       <c r="K80" t="n">
-        <v>-69.16</v>
+        <v>-71.23</v>
       </c>
       <c r="L80" t="n">
-        <v>118.85</v>
+        <v>122.4</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>80.61</v>
+        <v>89.8</v>
       </c>
       <c r="K81" t="n">
-        <v>-11.41</v>
+        <v>-12.71</v>
       </c>
       <c r="L81" t="n">
-        <v>81.42</v>
+        <v>90.69</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>26</v>
       </c>
       <c r="J82" t="n">
-        <v>-46.96</v>
+        <v>-54.14</v>
       </c>
       <c r="K82" t="n">
-        <v>57.19</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="L82" t="n">
-        <v>74</v>
+        <v>85.31</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>30</v>
       </c>
       <c r="J83" t="n">
-        <v>91.76000000000001</v>
+        <v>98.48999999999999</v>
       </c>
       <c r="K83" t="n">
-        <v>93.29000000000001</v>
+        <v>100.14</v>
       </c>
       <c r="L83" t="n">
-        <v>130.85</v>
+        <v>140.46</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>29</v>
       </c>
       <c r="J84" t="n">
-        <v>-111.98</v>
+        <v>-129.62</v>
       </c>
       <c r="K84" t="n">
-        <v>-20.99</v>
+        <v>-24.29</v>
       </c>
       <c r="L84" t="n">
-        <v>113.93</v>
+        <v>131.88</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>-88.66</v>
+        <v>-98.48</v>
       </c>
       <c r="K85" t="n">
-        <v>-120.29</v>
+        <v>-133.62</v>
       </c>
       <c r="L85" t="n">
-        <v>149.44</v>
+        <v>165.99</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>120.48</v>
+        <v>132.95</v>
       </c>
       <c r="K86" t="n">
-        <v>189.58</v>
+        <v>209.2</v>
       </c>
       <c r="L86" t="n">
-        <v>224.63</v>
+        <v>247.87</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>-51.19</v>
+        <v>-63.64</v>
       </c>
       <c r="K87" t="n">
-        <v>125.93</v>
+        <v>156.56</v>
       </c>
       <c r="L87" t="n">
-        <v>135.93</v>
+        <v>169</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>28</v>
       </c>
       <c r="J88" t="n">
-        <v>135.65</v>
+        <v>156.91</v>
       </c>
       <c r="K88" t="n">
-        <v>91.40000000000001</v>
+        <v>105.72</v>
       </c>
       <c r="L88" t="n">
-        <v>163.57</v>
+        <v>189.2</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-10.xlsx
+++ b/output/2024-07-10.xlsx
@@ -1438,13 +1438,13 @@
         <v>29</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.59</v>
+        <v>-0.61</v>
       </c>
       <c r="K33" t="n">
-        <v>75.22</v>
+        <v>77.12</v>
       </c>
       <c r="L33" t="n">
-        <v>75.22</v>
+        <v>77.12</v>
       </c>
     </row>
     <row r="34">
@@ -1984,13 +1984,13 @@
         <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>49.36</v>
+        <v>50.08</v>
       </c>
       <c r="K46" t="n">
-        <v>61.07</v>
+        <v>61.96</v>
       </c>
       <c r="L46" t="n">
-        <v>78.53</v>
+        <v>79.67</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>29</v>
       </c>
       <c r="J47" t="n">
-        <v>2.93</v>
+        <v>3.01</v>
       </c>
       <c r="K47" t="n">
-        <v>14.01</v>
+        <v>14.37</v>
       </c>
       <c r="L47" t="n">
-        <v>14.32</v>
+        <v>14.68</v>
       </c>
     </row>
     <row r="48">
@@ -2614,13 +2614,13 @@
         <v>29</v>
       </c>
       <c r="J61" t="n">
-        <v>-45.14</v>
+        <v>-45.46</v>
       </c>
       <c r="K61" t="n">
-        <v>-15.73</v>
+        <v>-15.84</v>
       </c>
       <c r="L61" t="n">
-        <v>47.8</v>
+        <v>48.14</v>
       </c>
     </row>
     <row r="62">
@@ -2740,13 +2740,13 @@
         <v>28</v>
       </c>
       <c r="J64" t="n">
-        <v>-11.92</v>
+        <v>-11.96</v>
       </c>
       <c r="K64" t="n">
-        <v>-85.81999999999999</v>
+        <v>-86.17</v>
       </c>
       <c r="L64" t="n">
-        <v>86.65000000000001</v>
+        <v>87</v>
       </c>
     </row>
     <row r="65">
@@ -3328,13 +3328,13 @@
         <v>29</v>
       </c>
       <c r="J78" t="n">
-        <v>-46.19</v>
+        <v>-49.36</v>
       </c>
       <c r="K78" t="n">
-        <v>40.44</v>
+        <v>43.21</v>
       </c>
       <c r="L78" t="n">
-        <v>61.39</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="79">
